--- a/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
+++ b/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP464"/>
+  <dimension ref="A1:AQ464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,11 @@
           <t>predmine2l_z2</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>pred2mine2l_z2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -760,6 +765,9 @@
       <c r="AP2" t="n">
         <v>22.60509300231934</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>22.43636131286621</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +898,9 @@
       <c r="AP3" t="n">
         <v>22.60509300231934</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>22.43636131286621</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1029,9 @@
       <c r="AP4" t="n">
         <v>22.60509300231934</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>22.43636131286621</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1166,9 @@
       <c r="AP5" t="n">
         <v>22.7152042388916</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>22.48161888122559</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1297,9 @@
       <c r="AP6" t="n">
         <v>23.01073837280273</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>22.69892883300781</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1416,6 +1436,9 @@
       <c r="AP7" t="n">
         <v>23.01073837280273</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>22.69892883300781</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1552,6 +1575,9 @@
       <c r="AP8" t="n">
         <v>23.57598876953125</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>23.3166675567627</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1706,9 @@
       <c r="AP9" t="n">
         <v>23.83519554138184</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>23.60137939453125</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1814,6 +1843,9 @@
       <c r="AP10" t="n">
         <v>24.05981636047363</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>23.83181762695312</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1948,6 +1980,9 @@
       <c r="AP11" t="n">
         <v>24.40985107421875</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>24.29356956481934</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2076,6 +2111,9 @@
       <c r="AP12" t="n">
         <v>24.93929100036621</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>24.88991165161133</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2210,6 +2248,9 @@
       <c r="AP13" t="n">
         <v>24.93929100036621</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>24.88991165161133</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2344,6 +2385,9 @@
       <c r="AP14" t="n">
         <v>27.11027717590332</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>27.06662559509277</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2472,6 +2516,9 @@
       <c r="AP15" t="n">
         <v>28.98266410827637</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>29.05513954162598</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2606,6 +2653,9 @@
       <c r="AP16" t="n">
         <v>28.98266410827637</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>29.05513954162598</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2740,6 +2790,9 @@
       <c r="AP17" t="n">
         <v>29.84463310241699</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>29.83145713806152</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2874,6 +2927,9 @@
       <c r="AP18" t="n">
         <v>30.02440643310547</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>30.04994964599609</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3006,6 +3062,9 @@
       <c r="AP19" t="n">
         <v>30.07987403869629</v>
       </c>
+      <c r="AQ19" t="n">
+        <v>30.09794235229492</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3132,6 +3191,9 @@
       <c r="AP20" t="n">
         <v>30.07987403869629</v>
       </c>
+      <c r="AQ20" t="n">
+        <v>30.09794235229492</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3268,6 +3330,9 @@
       <c r="AP21" t="n">
         <v>23.65892791748047</v>
       </c>
+      <c r="AQ21" t="n">
+        <v>23.64029312133789</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3396,6 +3461,9 @@
       <c r="AP22" t="n">
         <v>23.65892791748047</v>
       </c>
+      <c r="AQ22" t="n">
+        <v>23.64029312133789</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3530,6 +3598,9 @@
       <c r="AP23" t="n">
         <v>23.68990135192871</v>
       </c>
+      <c r="AQ23" t="n">
+        <v>23.67545700073242</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3666,6 +3737,9 @@
       <c r="AP24" t="n">
         <v>23.73702430725098</v>
       </c>
+      <c r="AQ24" t="n">
+        <v>23.72985076904297</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3794,6 +3868,9 @@
       <c r="AP25" t="n">
         <v>23.73702430725098</v>
       </c>
+      <c r="AQ25" t="n">
+        <v>23.72985076904297</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3930,6 +4007,9 @@
       <c r="AP26" t="n">
         <v>23.83745002746582</v>
       </c>
+      <c r="AQ26" t="n">
+        <v>23.82114028930664</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4058,6 +4138,9 @@
       <c r="AP27" t="n">
         <v>23.87926864624023</v>
       </c>
+      <c r="AQ27" t="n">
+        <v>23.85807418823242</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4192,6 +4275,9 @@
       <c r="AP28" t="n">
         <v>23.91097259521484</v>
       </c>
+      <c r="AQ28" t="n">
+        <v>23.89603614807129</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4326,6 +4412,9 @@
       <c r="AP29" t="n">
         <v>23.9921989440918</v>
       </c>
+      <c r="AQ29" t="n">
+        <v>23.99274826049805</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4454,6 +4543,9 @@
       <c r="AP30" t="n">
         <v>24.07450103759766</v>
       </c>
+      <c r="AQ30" t="n">
+        <v>24.09142112731934</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4588,6 +4680,9 @@
       <c r="AP31" t="n">
         <v>24.07450103759766</v>
       </c>
+      <c r="AQ31" t="n">
+        <v>24.09142112731934</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4722,6 +4817,9 @@
       <c r="AP32" t="n">
         <v>24.21527862548828</v>
       </c>
+      <c r="AQ32" t="n">
+        <v>24.22990226745605</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4856,6 +4954,9 @@
       <c r="AP33" t="n">
         <v>24.37784385681152</v>
       </c>
+      <c r="AQ33" t="n">
+        <v>24.38776588439941</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4984,6 +5085,9 @@
       <c r="AP34" t="n">
         <v>24.37860488891602</v>
       </c>
+      <c r="AQ34" t="n">
+        <v>24.38850212097168</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5118,6 +5222,9 @@
       <c r="AP35" t="n">
         <v>24.55521965026855</v>
       </c>
+      <c r="AQ35" t="n">
+        <v>24.55635452270508</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5248,6 +5355,9 @@
       <c r="AP36" t="n">
         <v>24.21762084960938</v>
       </c>
+      <c r="AQ36" t="n">
+        <v>24.29000854492188</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5382,6 +5492,9 @@
       <c r="AP37" t="n">
         <v>24.21762084960938</v>
       </c>
+      <c r="AQ37" t="n">
+        <v>24.29000854492188</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5516,6 +5629,9 @@
       <c r="AP38" t="n">
         <v>24.21127700805664</v>
       </c>
+      <c r="AQ38" t="n">
+        <v>24.27465438842773</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5652,6 +5768,9 @@
       <c r="AP39" t="n">
         <v>24.19906806945801</v>
       </c>
+      <c r="AQ39" t="n">
+        <v>24.25114440917969</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5788,6 +5907,9 @@
       <c r="AP40" t="n">
         <v>24.17510795593262</v>
       </c>
+      <c r="AQ40" t="n">
+        <v>24.21247291564941</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5922,6 +6044,9 @@
       <c r="AP41" t="n">
         <v>24.15445709228516</v>
       </c>
+      <c r="AQ41" t="n">
+        <v>24.17782592773438</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6056,6 +6181,9 @@
       <c r="AP42" t="n">
         <v>24.13837051391602</v>
       </c>
+      <c r="AQ42" t="n">
+        <v>24.14359092712402</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6190,6 +6318,9 @@
       <c r="AP43" t="n">
         <v>24.12679100036621</v>
       </c>
+      <c r="AQ43" t="n">
+        <v>24.12019729614258</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6324,6 +6455,9 @@
       <c r="AP44" t="n">
         <v>24.10993194580078</v>
       </c>
+      <c r="AQ44" t="n">
+        <v>24.10380554199219</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6458,6 +6592,9 @@
       <c r="AP45" t="n">
         <v>24.11180686950684</v>
       </c>
+      <c r="AQ45" t="n">
+        <v>24.10420417785645</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6592,6 +6729,9 @@
       <c r="AP46" t="n">
         <v>24.13449478149414</v>
       </c>
+      <c r="AQ46" t="n">
+        <v>24.13065147399902</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6726,6 +6866,9 @@
       <c r="AP47" t="n">
         <v>24.16125297546387</v>
       </c>
+      <c r="AQ47" t="n">
+        <v>24.15222930908203</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6860,6 +7003,9 @@
       <c r="AP48" t="n">
         <v>24.19256019592285</v>
       </c>
+      <c r="AQ48" t="n">
+        <v>24.1871223449707</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6992,6 +7138,9 @@
       <c r="AP49" t="n">
         <v>24.19700813293457</v>
       </c>
+      <c r="AQ49" t="n">
+        <v>24.19433784484863</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7124,6 +7273,9 @@
       <c r="AP50" t="n">
         <v>24.19700813293457</v>
       </c>
+      <c r="AQ50" t="n">
+        <v>24.19433784484863</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7254,6 +7406,9 @@
       <c r="AP51" t="n">
         <v>22.58310699462891</v>
       </c>
+      <c r="AQ51" t="n">
+        <v>22.44287490844727</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7384,6 +7539,9 @@
       <c r="AP52" t="n">
         <v>23.68725776672363</v>
       </c>
+      <c r="AQ52" t="n">
+        <v>23.59730911254883</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7514,6 +7672,9 @@
       <c r="AP53" t="n">
         <v>24.56348609924316</v>
       </c>
+      <c r="AQ53" t="n">
+        <v>24.55478477478027</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7650,6 +7811,9 @@
       <c r="AP54" t="n">
         <v>21.54222297668457</v>
       </c>
+      <c r="AQ54" t="n">
+        <v>21.41876411437988</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7784,6 +7948,9 @@
       <c r="AP55" t="n">
         <v>22.56101226806641</v>
       </c>
+      <c r="AQ55" t="n">
+        <v>22.64809417724609</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7920,6 +8087,9 @@
       <c r="AP56" t="n">
         <v>24.42629623413086</v>
       </c>
+      <c r="AQ56" t="n">
+        <v>24.49677848815918</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8056,6 +8226,9 @@
       <c r="AP57" t="n">
         <v>25.76655197143555</v>
       </c>
+      <c r="AQ57" t="n">
+        <v>25.78945350646973</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8190,6 +8363,9 @@
       <c r="AP58" t="n">
         <v>26.59926605224609</v>
       </c>
+      <c r="AQ58" t="n">
+        <v>26.63006401062012</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8324,6 +8500,9 @@
       <c r="AP59" t="n">
         <v>26.97010803222656</v>
       </c>
+      <c r="AQ59" t="n">
+        <v>26.97157287597656</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8458,6 +8637,9 @@
       <c r="AP60" t="n">
         <v>27.16198921203613</v>
       </c>
+      <c r="AQ60" t="n">
+        <v>27.16524887084961</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8592,6 +8774,9 @@
       <c r="AP61" t="n">
         <v>27.39993667602539</v>
       </c>
+      <c r="AQ61" t="n">
+        <v>27.40969467163086</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8726,6 +8911,9 @@
       <c r="AP62" t="n">
         <v>27.65251159667969</v>
       </c>
+      <c r="AQ62" t="n">
+        <v>27.65495491027832</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8860,6 +9048,9 @@
       <c r="AP63" t="n">
         <v>27.92378616333008</v>
       </c>
+      <c r="AQ63" t="n">
+        <v>27.92228317260742</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8994,6 +9185,9 @@
       <c r="AP64" t="n">
         <v>28.03949356079102</v>
       </c>
+      <c r="AQ64" t="n">
+        <v>28.03413772583008</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9128,6 +9322,9 @@
       <c r="AP65" t="n">
         <v>28.26576042175293</v>
       </c>
+      <c r="AQ65" t="n">
+        <v>28.26225852966309</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9262,6 +9459,9 @@
       <c r="AP66" t="n">
         <v>28.59863662719727</v>
       </c>
+      <c r="AQ66" t="n">
+        <v>28.59826278686523</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9392,6 +9592,9 @@
       <c r="AP67" t="n">
         <v>28.84382438659668</v>
       </c>
+      <c r="AQ67" t="n">
+        <v>28.84344863891602</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9526,6 +9729,9 @@
       <c r="AP68" t="n">
         <v>28.90445518493652</v>
       </c>
+      <c r="AQ68" t="n">
+        <v>28.90419578552246</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9658,6 +9864,9 @@
       <c r="AP69" t="n">
         <v>28.90839767456055</v>
       </c>
+      <c r="AQ69" t="n">
+        <v>28.90805816650391</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9782,6 +9991,9 @@
       <c r="AP70" t="n">
         <v>17.97045707702637</v>
       </c>
+      <c r="AQ70" t="n">
+        <v>17.62956237792969</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9912,6 +10124,9 @@
       <c r="AP71" t="n">
         <v>17.97045707702637</v>
       </c>
+      <c r="AQ71" t="n">
+        <v>17.62956237792969</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10040,6 +10255,9 @@
       <c r="AP72" t="n">
         <v>20.92201805114746</v>
       </c>
+      <c r="AQ72" t="n">
+        <v>20.44615173339844</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10170,6 +10388,9 @@
       <c r="AP73" t="n">
         <v>24.5825309753418</v>
       </c>
+      <c r="AQ73" t="n">
+        <v>24.51637840270996</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10294,6 +10515,9 @@
       <c r="AP74" t="n">
         <v>24.5825309753418</v>
       </c>
+      <c r="AQ74" t="n">
+        <v>24.51637840270996</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10424,6 +10648,9 @@
       <c r="AP75" t="n">
         <v>26.1601390838623</v>
       </c>
+      <c r="AQ75" t="n">
+        <v>26.15978050231934</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10548,6 +10775,9 @@
       <c r="AP76" t="n">
         <v>26.63070487976074</v>
       </c>
+      <c r="AQ76" t="n">
+        <v>26.60834693908691</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10676,6 +10906,9 @@
       <c r="AP77" t="n">
         <v>26.83911323547363</v>
       </c>
+      <c r="AQ77" t="n">
+        <v>26.87260818481445</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10804,6 +11037,9 @@
       <c r="AP78" t="n">
         <v>27.11980438232422</v>
       </c>
+      <c r="AQ78" t="n">
+        <v>27.15390205383301</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10928,6 +11164,9 @@
       <c r="AP79" t="n">
         <v>27.2030200958252</v>
       </c>
+      <c r="AQ79" t="n">
+        <v>27.18051719665527</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11056,6 +11295,9 @@
       <c r="AP80" t="n">
         <v>27.2030200958252</v>
       </c>
+      <c r="AQ80" t="n">
+        <v>27.18051719665527</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11184,6 +11426,9 @@
       <c r="AP81" t="n">
         <v>26.04983520507812</v>
       </c>
+      <c r="AQ81" t="n">
+        <v>25.81042289733887</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11312,6 +11557,9 @@
       <c r="AP82" t="n">
         <v>26.20744895935059</v>
       </c>
+      <c r="AQ82" t="n">
+        <v>26.17525291442871</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11436,6 +11684,9 @@
       <c r="AP83" t="n">
         <v>26.20744895935059</v>
       </c>
+      <c r="AQ83" t="n">
+        <v>26.17525291442871</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11564,6 +11815,9 @@
       <c r="AP84" t="n">
         <v>28.34077072143555</v>
       </c>
+      <c r="AQ84" t="n">
+        <v>28.32012367248535</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11688,6 +11942,9 @@
       <c r="AP85" t="n">
         <v>28.73340034484863</v>
       </c>
+      <c r="AQ85" t="n">
+        <v>28.72781372070312</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11816,6 +12073,9 @@
       <c r="AP86" t="n">
         <v>28.73417663574219</v>
       </c>
+      <c r="AQ86" t="n">
+        <v>28.72869682312012</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11952,6 +12212,9 @@
       <c r="AP87" t="n">
         <v>16.0826244354248</v>
       </c>
+      <c r="AQ87" t="n">
+        <v>15.90183448791504</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12086,6 +12349,9 @@
       <c r="AP88" t="n">
         <v>17.76689147949219</v>
       </c>
+      <c r="AQ88" t="n">
+        <v>17.57133483886719</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12222,6 +12488,9 @@
       <c r="AP89" t="n">
         <v>19.92592430114746</v>
       </c>
+      <c r="AQ89" t="n">
+        <v>19.84147644042969</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12358,6 +12627,9 @@
       <c r="AP90" t="n">
         <v>23.68996620178223</v>
       </c>
+      <c r="AQ90" t="n">
+        <v>23.69522476196289</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12492,6 +12764,9 @@
       <c r="AP91" t="n">
         <v>26.20230102539062</v>
       </c>
+      <c r="AQ91" t="n">
+        <v>26.21978569030762</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12626,6 +12901,9 @@
       <c r="AP92" t="n">
         <v>26.60074424743652</v>
       </c>
+      <c r="AQ92" t="n">
+        <v>26.62049293518066</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12760,6 +13038,9 @@
       <c r="AP93" t="n">
         <v>26.55803298950195</v>
       </c>
+      <c r="AQ93" t="n">
+        <v>26.57134628295898</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12894,6 +13175,9 @@
       <c r="AP94" t="n">
         <v>26.61731147766113</v>
       </c>
+      <c r="AQ94" t="n">
+        <v>26.61965179443359</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13028,6 +13312,9 @@
       <c r="AP95" t="n">
         <v>27.39571952819824</v>
       </c>
+      <c r="AQ95" t="n">
+        <v>27.38665580749512</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13162,6 +13449,9 @@
       <c r="AP96" t="n">
         <v>28.24206352233887</v>
       </c>
+      <c r="AQ96" t="n">
+        <v>28.23541069030762</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13296,6 +13586,9 @@
       <c r="AP97" t="n">
         <v>28.58320999145508</v>
       </c>
+      <c r="AQ97" t="n">
+        <v>28.58251571655273</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13430,6 +13723,9 @@
       <c r="AP98" t="n">
         <v>28.67277717590332</v>
       </c>
+      <c r="AQ98" t="n">
+        <v>28.66877746582031</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13564,6 +13860,9 @@
       <c r="AP99" t="n">
         <v>28.96212768554688</v>
       </c>
+      <c r="AQ99" t="n">
+        <v>28.96045684814453</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13698,6 +13997,9 @@
       <c r="AP100" t="n">
         <v>28.96502685546875</v>
       </c>
+      <c r="AQ100" t="n">
+        <v>28.9649715423584</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13832,6 +14134,9 @@
       <c r="AP101" t="n">
         <v>28.93527030944824</v>
       </c>
+      <c r="AQ101" t="n">
+        <v>28.93512344360352</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13964,6 +14269,9 @@
       <c r="AP102" t="n">
         <v>28.92139625549316</v>
       </c>
+      <c r="AQ102" t="n">
+        <v>28.92127227783203</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14100,6 +14408,9 @@
       <c r="AP103" t="n">
         <v>14.99204635620117</v>
       </c>
+      <c r="AQ103" t="n">
+        <v>14.65914440155029</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14234,6 +14545,9 @@
       <c r="AP104" t="n">
         <v>16.00351715087891</v>
       </c>
+      <c r="AQ104" t="n">
+        <v>15.72530841827393</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14370,6 +14684,9 @@
       <c r="AP105" t="n">
         <v>19.29881477355957</v>
       </c>
+      <c r="AQ105" t="n">
+        <v>19.20228385925293</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14506,6 +14823,9 @@
       <c r="AP106" t="n">
         <v>25.07693481445312</v>
       </c>
+      <c r="AQ106" t="n">
+        <v>25.07301712036133</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14640,6 +14960,9 @@
       <c r="AP107" t="n">
         <v>26.65122032165527</v>
       </c>
+      <c r="AQ107" t="n">
+        <v>26.65420532226562</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14774,6 +15097,9 @@
       <c r="AP108" t="n">
         <v>27.20112037658691</v>
       </c>
+      <c r="AQ108" t="n">
+        <v>27.19811820983887</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14908,6 +15234,9 @@
       <c r="AP109" t="n">
         <v>27.48216819763184</v>
       </c>
+      <c r="AQ109" t="n">
+        <v>27.48202896118164</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15042,6 +15371,9 @@
       <c r="AP110" t="n">
         <v>27.7672119140625</v>
       </c>
+      <c r="AQ110" t="n">
+        <v>27.7675895690918</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15176,6 +15508,9 @@
       <c r="AP111" t="n">
         <v>28.00290107727051</v>
       </c>
+      <c r="AQ111" t="n">
+        <v>28.00334167480469</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15310,6 +15645,9 @@
       <c r="AP112" t="n">
         <v>28.42508506774902</v>
       </c>
+      <c r="AQ112" t="n">
+        <v>28.42632293701172</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15444,6 +15782,9 @@
       <c r="AP113" t="n">
         <v>28.69111824035645</v>
       </c>
+      <c r="AQ113" t="n">
+        <v>28.69116592407227</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15578,6 +15919,9 @@
       <c r="AP114" t="n">
         <v>28.82267761230469</v>
       </c>
+      <c r="AQ114" t="n">
+        <v>28.8226203918457</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15712,6 +16056,9 @@
       <c r="AP115" t="n">
         <v>28.91908264160156</v>
       </c>
+      <c r="AQ115" t="n">
+        <v>28.91921234130859</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15846,6 +16193,9 @@
       <c r="AP116" t="n">
         <v>28.97583770751953</v>
       </c>
+      <c r="AQ116" t="n">
+        <v>28.97601127624512</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15982,6 +16332,9 @@
       <c r="AP117" t="n">
         <v>19.95744132995605</v>
       </c>
+      <c r="AQ117" t="n">
+        <v>19.85209274291992</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16116,6 +16469,9 @@
       <c r="AP118" t="n">
         <v>20.12243270874023</v>
       </c>
+      <c r="AQ118" t="n">
+        <v>19.95232772827148</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16252,6 +16608,9 @@
       <c r="AP119" t="n">
         <v>20.32966041564941</v>
       </c>
+      <c r="AQ119" t="n">
+        <v>20.10055160522461</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16388,6 +16747,9 @@
       <c r="AP120" t="n">
         <v>20.55065536499023</v>
       </c>
+      <c r="AQ120" t="n">
+        <v>20.35651588439941</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16522,6 +16884,9 @@
       <c r="AP121" t="n">
         <v>20.7506160736084</v>
       </c>
+      <c r="AQ121" t="n">
+        <v>20.57992362976074</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16656,6 +17021,9 @@
       <c r="AP122" t="n">
         <v>20.98286437988281</v>
       </c>
+      <c r="AQ122" t="n">
+        <v>20.89484596252441</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16790,6 +17158,9 @@
       <c r="AP123" t="n">
         <v>21.21303176879883</v>
       </c>
+      <c r="AQ123" t="n">
+        <v>21.16396331787109</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16924,6 +17295,9 @@
       <c r="AP124" t="n">
         <v>21.81401062011719</v>
       </c>
+      <c r="AQ124" t="n">
+        <v>21.69884300231934</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17058,6 +17432,9 @@
       <c r="AP125" t="n">
         <v>22.18077659606934</v>
       </c>
+      <c r="AQ125" t="n">
+        <v>22.07812690734863</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17192,6 +17569,9 @@
       <c r="AP126" t="n">
         <v>22.47382545471191</v>
       </c>
+      <c r="AQ126" t="n">
+        <v>22.37998962402344</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17326,6 +17706,9 @@
       <c r="AP127" t="n">
         <v>22.77356147766113</v>
       </c>
+      <c r="AQ127" t="n">
+        <v>22.65036010742188</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17460,6 +17843,9 @@
       <c r="AP128" t="n">
         <v>23.01389503479004</v>
       </c>
+      <c r="AQ128" t="n">
+        <v>22.84718894958496</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17594,6 +17980,9 @@
       <c r="AP129" t="n">
         <v>23.25879287719727</v>
       </c>
+      <c r="AQ129" t="n">
+        <v>23.06948471069336</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17730,6 +18119,9 @@
       <c r="AP130" t="n">
         <v>21.74999046325684</v>
       </c>
+      <c r="AQ130" t="n">
+        <v>21.49900245666504</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17864,6 +18256,9 @@
       <c r="AP131" t="n">
         <v>21.90071487426758</v>
       </c>
+      <c r="AQ131" t="n">
+        <v>21.66473197937012</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18000,6 +18395,9 @@
       <c r="AP132" t="n">
         <v>22.16171646118164</v>
       </c>
+      <c r="AQ132" t="n">
+        <v>21.91749954223633</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18136,6 +18534,9 @@
       <c r="AP133" t="n">
         <v>22.693115234375</v>
       </c>
+      <c r="AQ133" t="n">
+        <v>22.49143981933594</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18270,6 +18671,9 @@
       <c r="AP134" t="n">
         <v>23.17220497131348</v>
       </c>
+      <c r="AQ134" t="n">
+        <v>22.97998428344727</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18404,6 +18808,9 @@
       <c r="AP135" t="n">
         <v>23.57629203796387</v>
       </c>
+      <c r="AQ135" t="n">
+        <v>23.3029670715332</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18538,6 +18945,9 @@
       <c r="AP136" t="n">
         <v>24.03838157653809</v>
       </c>
+      <c r="AQ136" t="n">
+        <v>23.73383331298828</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18672,6 +19082,9 @@
       <c r="AP137" t="n">
         <v>26.51002883911133</v>
       </c>
+      <c r="AQ137" t="n">
+        <v>26.24082374572754</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18806,6 +19219,9 @@
       <c r="AP138" t="n">
         <v>29.24599456787109</v>
       </c>
+      <c r="AQ138" t="n">
+        <v>29.25329399108887</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18940,6 +19356,9 @@
       <c r="AP139" t="n">
         <v>30.26201820373535</v>
       </c>
+      <c r="AQ139" t="n">
+        <v>30.24240303039551</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19074,6 +19493,9 @@
       <c r="AP140" t="n">
         <v>30.49836730957031</v>
       </c>
+      <c r="AQ140" t="n">
+        <v>30.51158142089844</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19206,6 +19628,9 @@
       <c r="AP141" t="n">
         <v>30.5579776763916</v>
       </c>
+      <c r="AQ141" t="n">
+        <v>30.59122848510742</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19340,6 +19765,9 @@
       <c r="AP142" t="n">
         <v>21.16700553894043</v>
       </c>
+      <c r="AQ142" t="n">
+        <v>20.99753570556641</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -19474,6 +19902,9 @@
       <c r="AP143" t="n">
         <v>21.16700553894043</v>
       </c>
+      <c r="AQ143" t="n">
+        <v>20.99753570556641</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -19610,6 +20041,9 @@
       <c r="AP144" t="n">
         <v>21.31734657287598</v>
       </c>
+      <c r="AQ144" t="n">
+        <v>21.2316951751709</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19746,6 +20180,9 @@
       <c r="AP145" t="n">
         <v>21.60828971862793</v>
       </c>
+      <c r="AQ145" t="n">
+        <v>21.65328788757324</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -19880,6 +20317,9 @@
       <c r="AP146" t="n">
         <v>22.46656608581543</v>
       </c>
+      <c r="AQ146" t="n">
+        <v>22.34049415588379</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -20014,6 +20454,9 @@
       <c r="AP147" t="n">
         <v>22.96754264831543</v>
       </c>
+      <c r="AQ147" t="n">
+        <v>22.76232528686523</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -20148,6 +20591,9 @@
       <c r="AP148" t="n">
         <v>23.36099624633789</v>
       </c>
+      <c r="AQ148" t="n">
+        <v>23.12858772277832</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -20282,6 +20728,9 @@
       <c r="AP149" t="n">
         <v>23.92204856872559</v>
       </c>
+      <c r="AQ149" t="n">
+        <v>23.64399337768555</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -20416,6 +20865,9 @@
       <c r="AP150" t="n">
         <v>26.21205139160156</v>
       </c>
+      <c r="AQ150" t="n">
+        <v>25.9908275604248</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -20550,6 +21002,9 @@
       <c r="AP151" t="n">
         <v>28.96707725524902</v>
       </c>
+      <c r="AQ151" t="n">
+        <v>28.84749412536621</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -20684,6 +21139,9 @@
       <c r="AP152" t="n">
         <v>30.92221641540527</v>
       </c>
+      <c r="AQ152" t="n">
+        <v>30.91207885742188</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -20818,6 +21276,9 @@
       <c r="AP153" t="n">
         <v>31.44609832763672</v>
       </c>
+      <c r="AQ153" t="n">
+        <v>31.43169975280762</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -20950,6 +21411,9 @@
       <c r="AP154" t="n">
         <v>31.54781723022461</v>
       </c>
+      <c r="AQ154" t="n">
+        <v>31.52877426147461</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -21082,6 +21546,9 @@
       <c r="AP155" t="n">
         <v>31.54781723022461</v>
       </c>
+      <c r="AQ155" t="n">
+        <v>31.52877426147461</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -21218,6 +21685,9 @@
       <c r="AP156" t="n">
         <v>20.58075714111328</v>
       </c>
+      <c r="AQ156" t="n">
+        <v>20.36337852478027</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -21352,6 +21822,9 @@
       <c r="AP157" t="n">
         <v>20.7786808013916</v>
       </c>
+      <c r="AQ157" t="n">
+        <v>20.5545825958252</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -21488,6 +21961,9 @@
       <c r="AP158" t="n">
         <v>21.08114242553711</v>
       </c>
+      <c r="AQ158" t="n">
+        <v>20.8983211517334</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -21624,6 +22100,9 @@
       <c r="AP159" t="n">
         <v>21.68379974365234</v>
       </c>
+      <c r="AQ159" t="n">
+        <v>21.50336456298828</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -21758,6 +22237,9 @@
       <c r="AP160" t="n">
         <v>22.25454521179199</v>
       </c>
+      <c r="AQ160" t="n">
+        <v>22.07012939453125</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -21886,6 +22368,9 @@
       <c r="AP161" t="n">
         <v>23.30684852600098</v>
       </c>
+      <c r="AQ161" t="n">
+        <v>23.15775871276855</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -22020,6 +22505,9 @@
       <c r="AP162" t="n">
         <v>24.38343620300293</v>
       </c>
+      <c r="AQ162" t="n">
+        <v>24.20733642578125</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -22154,6 +22642,9 @@
       <c r="AP163" t="n">
         <v>26.70638847351074</v>
       </c>
+      <c r="AQ163" t="n">
+        <v>26.51087760925293</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -22288,6 +22779,9 @@
       <c r="AP164" t="n">
         <v>27.67970657348633</v>
       </c>
+      <c r="AQ164" t="n">
+        <v>27.60127449035645</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -22418,6 +22912,9 @@
       <c r="AP165" t="n">
         <v>27.77696990966797</v>
       </c>
+      <c r="AQ165" t="n">
+        <v>27.67102432250977</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -22554,6 +23051,9 @@
       <c r="AP166" t="n">
         <v>19.8510627746582</v>
       </c>
+      <c r="AQ166" t="n">
+        <v>19.62225914001465</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -22688,6 +23188,9 @@
       <c r="AP167" t="n">
         <v>19.88980102539062</v>
       </c>
+      <c r="AQ167" t="n">
+        <v>19.66095733642578</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -22824,6 +23327,9 @@
       <c r="AP168" t="n">
         <v>20.05911445617676</v>
       </c>
+      <c r="AQ168" t="n">
+        <v>19.7941780090332</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -22960,6 +23466,9 @@
       <c r="AP169" t="n">
         <v>20.73590087890625</v>
       </c>
+      <c r="AQ169" t="n">
+        <v>20.51756477355957</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -23094,6 +23603,9 @@
       <c r="AP170" t="n">
         <v>21.68586349487305</v>
       </c>
+      <c r="AQ170" t="n">
+        <v>21.44605445861816</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -23228,6 +23740,9 @@
       <c r="AP171" t="n">
         <v>22.59723281860352</v>
       </c>
+      <c r="AQ171" t="n">
+        <v>22.34055519104004</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -23362,6 +23877,9 @@
       <c r="AP172" t="n">
         <v>23.28303146362305</v>
       </c>
+      <c r="AQ172" t="n">
+        <v>23.03812408447266</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -23496,6 +24014,9 @@
       <c r="AP173" t="n">
         <v>25.43633270263672</v>
       </c>
+      <c r="AQ173" t="n">
+        <v>25.35152816772461</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -23630,6 +24151,9 @@
       <c r="AP174" t="n">
         <v>26.73467063903809</v>
       </c>
+      <c r="AQ174" t="n">
+        <v>26.70055389404297</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -23764,6 +24288,9 @@
       <c r="AP175" t="n">
         <v>27.09262657165527</v>
       </c>
+      <c r="AQ175" t="n">
+        <v>27.00031280517578</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -23900,6 +24427,9 @@
       <c r="AP176" t="n">
         <v>20.83284378051758</v>
       </c>
+      <c r="AQ176" t="n">
+        <v>20.63822937011719</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -24034,6 +24564,9 @@
       <c r="AP177" t="n">
         <v>20.89352226257324</v>
       </c>
+      <c r="AQ177" t="n">
+        <v>20.6913890838623</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -24170,6 +24703,9 @@
       <c r="AP178" t="n">
         <v>21.00314903259277</v>
       </c>
+      <c r="AQ178" t="n">
+        <v>20.77734565734863</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -24306,6 +24842,9 @@
       <c r="AP179" t="n">
         <v>21.21645545959473</v>
       </c>
+      <c r="AQ179" t="n">
+        <v>21.00918579101562</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -24440,6 +24979,9 @@
       <c r="AP180" t="n">
         <v>21.38533973693848</v>
       </c>
+      <c r="AQ180" t="n">
+        <v>21.16812515258789</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -24574,6 +25116,9 @@
       <c r="AP181" t="n">
         <v>21.52907752990723</v>
       </c>
+      <c r="AQ181" t="n">
+        <v>21.33024406433105</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -24708,6 +25253,9 @@
       <c r="AP182" t="n">
         <v>21.63620376586914</v>
       </c>
+      <c r="AQ182" t="n">
+        <v>21.47179412841797</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -24842,6 +25390,9 @@
       <c r="AP183" t="n">
         <v>21.80751037597656</v>
       </c>
+      <c r="AQ183" t="n">
+        <v>21.69080924987793</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -24976,6 +25527,9 @@
       <c r="AP184" t="n">
         <v>22.04888153076172</v>
       </c>
+      <c r="AQ184" t="n">
+        <v>21.96330642700195</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -25110,6 +25664,9 @@
       <c r="AP185" t="n">
         <v>22.27935600280762</v>
       </c>
+      <c r="AQ185" t="n">
+        <v>22.1417293548584</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -25238,6 +25795,9 @@
       <c r="AP186" t="n">
         <v>22.45258712768555</v>
       </c>
+      <c r="AQ186" t="n">
+        <v>22.31901741027832</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -25372,6 +25932,9 @@
       <c r="AP187" t="n">
         <v>22.56395530700684</v>
       </c>
+      <c r="AQ187" t="n">
+        <v>22.45622634887695</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -25504,6 +26067,9 @@
       <c r="AP188" t="n">
         <v>22.60544013977051</v>
       </c>
+      <c r="AQ188" t="n">
+        <v>22.48510932922363</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -25640,6 +26206,9 @@
       <c r="AP189" t="n">
         <v>18.80859756469727</v>
       </c>
+      <c r="AQ189" t="n">
+        <v>18.58720207214355</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -25774,6 +26343,9 @@
       <c r="AP190" t="n">
         <v>18.98468017578125</v>
       </c>
+      <c r="AQ190" t="n">
+        <v>18.80278778076172</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -25910,6 +26482,9 @@
       <c r="AP191" t="n">
         <v>19.8814754486084</v>
       </c>
+      <c r="AQ191" t="n">
+        <v>19.65059089660645</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -26046,6 +26621,9 @@
       <c r="AP192" t="n">
         <v>21.28012657165527</v>
       </c>
+      <c r="AQ192" t="n">
+        <v>20.81158256530762</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -26180,6 +26758,9 @@
       <c r="AP193" t="n">
         <v>21.79277992248535</v>
       </c>
+      <c r="AQ193" t="n">
+        <v>21.39556884765625</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -26314,6 +26895,9 @@
       <c r="AP194" t="n">
         <v>22.17621612548828</v>
       </c>
+      <c r="AQ194" t="n">
+        <v>21.94051933288574</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -26448,6 +27032,9 @@
       <c r="AP195" t="n">
         <v>22.41104125976562</v>
       </c>
+      <c r="AQ195" t="n">
+        <v>22.28800964355469</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -26582,6 +27169,9 @@
       <c r="AP196" t="n">
         <v>22.95381546020508</v>
       </c>
+      <c r="AQ196" t="n">
+        <v>22.92724418640137</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -26716,6 +27306,9 @@
       <c r="AP197" t="n">
         <v>23.90926742553711</v>
       </c>
+      <c r="AQ197" t="n">
+        <v>23.67417335510254</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -26850,6 +27443,9 @@
       <c r="AP198" t="n">
         <v>24.77096366882324</v>
       </c>
+      <c r="AQ198" t="n">
+        <v>24.85447311401367</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -26984,6 +27580,9 @@
       <c r="AP199" t="n">
         <v>26.45696449279785</v>
       </c>
+      <c r="AQ199" t="n">
+        <v>26.24236679077148</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -27116,6 +27715,9 @@
       <c r="AP200" t="n">
         <v>26.76004600524902</v>
       </c>
+      <c r="AQ200" t="n">
+        <v>26.66815376281738</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -27252,6 +27854,9 @@
       <c r="AP201" t="n">
         <v>10.75395774841309</v>
       </c>
+      <c r="AQ201" t="n">
+        <v>10.39869117736816</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -27386,6 +27991,9 @@
       <c r="AP202" t="n">
         <v>11.1250467300415</v>
       </c>
+      <c r="AQ202" t="n">
+        <v>10.61744785308838</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -27522,6 +28130,9 @@
       <c r="AP203" t="n">
         <v>15.30619335174561</v>
       </c>
+      <c r="AQ203" t="n">
+        <v>13.29244327545166</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -27658,6 +28269,9 @@
       <c r="AP204" t="n">
         <v>23.45927238464355</v>
       </c>
+      <c r="AQ204" t="n">
+        <v>23.46282005310059</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -27792,6 +28406,9 @@
       <c r="AP205" t="n">
         <v>24.66963768005371</v>
       </c>
+      <c r="AQ205" t="n">
+        <v>24.93439483642578</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -27926,6 +28543,9 @@
       <c r="AP206" t="n">
         <v>24.2293643951416</v>
       </c>
+      <c r="AQ206" t="n">
+        <v>25.15958786010742</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -28060,6 +28680,9 @@
       <c r="AP207" t="n">
         <v>23.6139030456543</v>
       </c>
+      <c r="AQ207" t="n">
+        <v>24.68145179748535</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -28194,6 +28817,9 @@
       <c r="AP208" t="n">
         <v>23.09456062316895</v>
       </c>
+      <c r="AQ208" t="n">
+        <v>23.91292572021484</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -28328,6 +28954,9 @@
       <c r="AP209" t="n">
         <v>23.85412216186523</v>
       </c>
+      <c r="AQ209" t="n">
+        <v>25.0840015411377</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -28462,6 +29091,9 @@
       <c r="AP210" t="n">
         <v>25.8476676940918</v>
       </c>
+      <c r="AQ210" t="n">
+        <v>26.19154167175293</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -28596,6 +29228,9 @@
       <c r="AP211" t="n">
         <v>26.65204620361328</v>
       </c>
+      <c r="AQ211" t="n">
+        <v>26.68475532531738</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -28728,6 +29363,9 @@
       <c r="AP212" t="n">
         <v>27.54660034179688</v>
       </c>
+      <c r="AQ212" t="n">
+        <v>27.39163970947266</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -28862,6 +29500,9 @@
       <c r="AP213" t="n">
         <v>28.07014465332031</v>
       </c>
+      <c r="AQ213" t="n">
+        <v>27.90624618530273</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -28996,6 +29637,9 @@
       <c r="AP214" t="n">
         <v>28.60207748413086</v>
       </c>
+      <c r="AQ214" t="n">
+        <v>28.46711540222168</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -29130,6 +29774,9 @@
       <c r="AP215" t="n">
         <v>28.7528133392334</v>
       </c>
+      <c r="AQ215" t="n">
+        <v>28.70810699462891</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -29262,6 +29909,9 @@
       <c r="AP216" t="n">
         <v>28.76277542114258</v>
       </c>
+      <c r="AQ216" t="n">
+        <v>28.73069000244141</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -29398,6 +30048,9 @@
       <c r="AP217" t="n">
         <v>11.97141933441162</v>
       </c>
+      <c r="AQ217" t="n">
+        <v>17.93804550170898</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -29532,6 +30185,9 @@
       <c r="AP218" t="n">
         <v>14.03553867340088</v>
       </c>
+      <c r="AQ218" t="n">
+        <v>19.88368797302246</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -29668,6 +30324,9 @@
       <c r="AP219" t="n">
         <v>19.55330657958984</v>
       </c>
+      <c r="AQ219" t="n">
+        <v>20.81304550170898</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -29804,6 +30463,9 @@
       <c r="AP220" t="n">
         <v>22.70114135742188</v>
       </c>
+      <c r="AQ220" t="n">
+        <v>23.39485740661621</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -29932,6 +30594,9 @@
       <c r="AP221" t="n">
         <v>25.33250999450684</v>
       </c>
+      <c r="AQ221" t="n">
+        <v>25.65460968017578</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -30066,6 +30731,9 @@
       <c r="AP222" t="n">
         <v>26.25546073913574</v>
       </c>
+      <c r="AQ222" t="n">
+        <v>26.42144584655762</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -30194,6 +30862,9 @@
       <c r="AP223" t="n">
         <v>26.78714942932129</v>
       </c>
+      <c r="AQ223" t="n">
+        <v>26.91451263427734</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -30328,6 +30999,9 @@
       <c r="AP224" t="n">
         <v>27.0864429473877</v>
       </c>
+      <c r="AQ224" t="n">
+        <v>26.88815307617188</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -30462,6 +31136,9 @@
       <c r="AP225" t="n">
         <v>26.89774894714355</v>
       </c>
+      <c r="AQ225" t="n">
+        <v>26.68624305725098</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -30596,6 +31273,9 @@
       <c r="AP226" t="n">
         <v>26.48870086669922</v>
       </c>
+      <c r="AQ226" t="n">
+        <v>26.4976921081543</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -30730,6 +31410,9 @@
       <c r="AP227" t="n">
         <v>26.76494216918945</v>
       </c>
+      <c r="AQ227" t="n">
+        <v>26.87140464782715</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -30864,6 +31547,9 @@
       <c r="AP228" t="n">
         <v>26.94260787963867</v>
       </c>
+      <c r="AQ228" t="n">
+        <v>27.08657073974609</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -30998,6 +31684,9 @@
       <c r="AP229" t="n">
         <v>27.20621871948242</v>
       </c>
+      <c r="AQ229" t="n">
+        <v>27.22974395751953</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -31132,6 +31821,9 @@
       <c r="AP230" t="n">
         <v>28.02906608581543</v>
       </c>
+      <c r="AQ230" t="n">
+        <v>28.10054206848145</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -31266,6 +31958,9 @@
       <c r="AP231" t="n">
         <v>28.77643013000488</v>
       </c>
+      <c r="AQ231" t="n">
+        <v>28.75100898742676</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -31400,6 +32095,9 @@
       <c r="AP232" t="n">
         <v>28.93014907836914</v>
       </c>
+      <c r="AQ232" t="n">
+        <v>28.92733383178711</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -31531,6 +32229,9 @@
       </c>
       <c r="AP233" t="n">
         <v>28.93733406066895</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>28.93276786804199</v>
       </c>
     </row>
     <row r="234">
@@ -31654,6 +32355,9 @@
       <c r="AP234" t="n">
         <v>10.43475914001465</v>
       </c>
+      <c r="AQ234" t="n">
+        <v>8.281889915466309</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -31776,6 +32480,9 @@
       <c r="AP235" t="n">
         <v>21.13913345336914</v>
       </c>
+      <c r="AQ235" t="n">
+        <v>19.55489158630371</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -31898,6 +32605,9 @@
       <c r="AP236" t="n">
         <v>24.25534057617188</v>
       </c>
+      <c r="AQ236" t="n">
+        <v>23.53064346313477</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -32034,6 +32744,9 @@
       <c r="AP237" t="n">
         <v>8.634519577026367</v>
       </c>
+      <c r="AQ237" t="n">
+        <v>9.333398818969727</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -32168,6 +32881,9 @@
       <c r="AP238" t="n">
         <v>10.21075248718262</v>
       </c>
+      <c r="AQ238" t="n">
+        <v>10.81204605102539</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -32304,6 +33020,9 @@
       <c r="AP239" t="n">
         <v>12.98558139801025</v>
       </c>
+      <c r="AQ239" t="n">
+        <v>15.10553932189941</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -32440,6 +33159,9 @@
       <c r="AP240" t="n">
         <v>21.61032295227051</v>
       </c>
+      <c r="AQ240" t="n">
+        <v>24.05141830444336</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -32574,6 +33296,9 @@
       <c r="AP241" t="n">
         <v>26.00990104675293</v>
       </c>
+      <c r="AQ241" t="n">
+        <v>26.69393539428711</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -32708,6 +33433,9 @@
       <c r="AP242" t="n">
         <v>26.82104301452637</v>
       </c>
+      <c r="AQ242" t="n">
+        <v>27.26567840576172</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -32842,6 +33570,9 @@
       <c r="AP243" t="n">
         <v>27.03969955444336</v>
       </c>
+      <c r="AQ243" t="n">
+        <v>27.37546539306641</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -32976,6 +33707,9 @@
       <c r="AP244" t="n">
         <v>27.07707977294922</v>
       </c>
+      <c r="AQ244" t="n">
+        <v>27.17772674560547</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -33110,6 +33844,9 @@
       <c r="AP245" t="n">
         <v>26.65500450134277</v>
       </c>
+      <c r="AQ245" t="n">
+        <v>26.88192749023438</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -33244,6 +33981,9 @@
       <c r="AP246" t="n">
         <v>26.9429931640625</v>
       </c>
+      <c r="AQ246" t="n">
+        <v>26.95013236999512</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -33378,6 +34118,9 @@
       <c r="AP247" t="n">
         <v>27.12340354919434</v>
       </c>
+      <c r="AQ247" t="n">
+        <v>27.1968994140625</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -33512,6 +34255,9 @@
       <c r="AP248" t="n">
         <v>27.84230804443359</v>
       </c>
+      <c r="AQ248" t="n">
+        <v>27.80367279052734</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -33646,6 +34392,9 @@
       <c r="AP249" t="n">
         <v>28.59903717041016</v>
       </c>
+      <c r="AQ249" t="n">
+        <v>28.54760932922363</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -33780,6 +34529,9 @@
       <c r="AP250" t="n">
         <v>28.96484565734863</v>
       </c>
+      <c r="AQ250" t="n">
+        <v>28.95224571228027</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -33914,6 +34666,9 @@
       <c r="AP251" t="n">
         <v>28.97648239135742</v>
       </c>
+      <c r="AQ251" t="n">
+        <v>28.96767234802246</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -34048,6 +34803,9 @@
       <c r="AP252" t="n">
         <v>28.96253967285156</v>
       </c>
+      <c r="AQ252" t="n">
+        <v>28.95707321166992</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -34178,6 +34936,9 @@
       <c r="AP253" t="n">
         <v>4.518453121185303</v>
       </c>
+      <c r="AQ253" t="n">
+        <v>9.265677452087402</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -34308,6 +35069,9 @@
       <c r="AP254" t="n">
         <v>9.812420845031738</v>
       </c>
+      <c r="AQ254" t="n">
+        <v>15.26477527618408</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -34438,6 +35202,9 @@
       <c r="AP255" t="n">
         <v>22.28061676025391</v>
       </c>
+      <c r="AQ255" t="n">
+        <v>21.39492416381836</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -34574,6 +35341,9 @@
       <c r="AP256" t="n">
         <v>5.724323749542236</v>
       </c>
+      <c r="AQ256" t="n">
+        <v>13.58145523071289</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -34708,6 +35478,9 @@
       <c r="AP257" t="n">
         <v>8.978351593017578</v>
       </c>
+      <c r="AQ257" t="n">
+        <v>15.59268665313721</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -34844,6 +35617,9 @@
       <c r="AP258" t="n">
         <v>16.34438896179199</v>
       </c>
+      <c r="AQ258" t="n">
+        <v>17.70902442932129</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -34980,6 +35756,9 @@
       <c r="AP259" t="n">
         <v>20.62477684020996</v>
       </c>
+      <c r="AQ259" t="n">
+        <v>21.66425514221191</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -35114,6 +35893,9 @@
       <c r="AP260" t="n">
         <v>24.10742378234863</v>
       </c>
+      <c r="AQ260" t="n">
+        <v>24.70704078674316</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -35248,6 +36030,9 @@
       <c r="AP261" t="n">
         <v>26.99142265319824</v>
       </c>
+      <c r="AQ261" t="n">
+        <v>26.6652717590332</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -35382,6 +36167,9 @@
       <c r="AP262" t="n">
         <v>27.76307106018066</v>
       </c>
+      <c r="AQ262" t="n">
+        <v>27.64896392822266</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -35516,6 +36304,9 @@
       <c r="AP263" t="n">
         <v>27.96491050720215</v>
       </c>
+      <c r="AQ263" t="n">
+        <v>27.86395835876465</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -35650,6 +36441,9 @@
       <c r="AP264" t="n">
         <v>27.62674903869629</v>
       </c>
+      <c r="AQ264" t="n">
+        <v>27.66209983825684</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -35780,6 +36574,9 @@
       <c r="AP265" t="n">
         <v>27.55487823486328</v>
       </c>
+      <c r="AQ265" t="n">
+        <v>27.65321159362793</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -35914,6 +36711,9 @@
       <c r="AP266" t="n">
         <v>27.89262580871582</v>
       </c>
+      <c r="AQ266" t="n">
+        <v>27.88377952575684</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -36048,6 +36848,9 @@
       <c r="AP267" t="n">
         <v>28.33523368835449</v>
       </c>
+      <c r="AQ267" t="n">
+        <v>28.0670108795166</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -36182,6 +36985,9 @@
       <c r="AP268" t="n">
         <v>28.63783073425293</v>
       </c>
+      <c r="AQ268" t="n">
+        <v>28.5823917388916</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -36316,6 +37122,9 @@
       <c r="AP269" t="n">
         <v>28.94750785827637</v>
       </c>
+      <c r="AQ269" t="n">
+        <v>28.95543670654297</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -36450,6 +37259,9 @@
       <c r="AP270" t="n">
         <v>28.98990821838379</v>
       </c>
+      <c r="AQ270" t="n">
+        <v>28.99483489990234</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -36578,6 +37390,9 @@
       <c r="AP271" t="n">
         <v>6.933248043060303</v>
       </c>
+      <c r="AQ271" t="n">
+        <v>6.212727069854736</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -36706,6 +37521,9 @@
       <c r="AP272" t="n">
         <v>8.700922012329102</v>
       </c>
+      <c r="AQ272" t="n">
+        <v>8.400172233581543</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -36834,6 +37652,9 @@
       <c r="AP273" t="n">
         <v>9.608349800109863</v>
       </c>
+      <c r="AQ273" t="n">
+        <v>9.904959678649902</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -36964,6 +37785,9 @@
       <c r="AP274" t="n">
         <v>15.72074890136719</v>
       </c>
+      <c r="AQ274" t="n">
+        <v>17.74823188781738</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -37094,6 +37918,9 @@
       <c r="AP275" t="n">
         <v>16.20865631103516</v>
       </c>
+      <c r="AQ275" t="n">
+        <v>17.74395179748535</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -37224,6 +38051,9 @@
       <c r="AP276" t="n">
         <v>18.54309463500977</v>
       </c>
+      <c r="AQ276" t="n">
+        <v>19.35729598999023</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -37360,6 +38190,9 @@
       <c r="AP277" t="n">
         <v>21.78083229064941</v>
       </c>
+      <c r="AQ277" t="n">
+        <v>21.39465713500977</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -37492,6 +38325,9 @@
       <c r="AP278" t="n">
         <v>21.92269897460938</v>
       </c>
+      <c r="AQ278" t="n">
+        <v>21.49865913391113</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -37628,6 +38464,9 @@
       <c r="AP279" t="n">
         <v>22.25599670410156</v>
       </c>
+      <c r="AQ279" t="n">
+        <v>21.75945091247559</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -37762,6 +38601,9 @@
       <c r="AP280" t="n">
         <v>22.97852897644043</v>
       </c>
+      <c r="AQ280" t="n">
+        <v>22.24102973937988</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -37896,6 +38738,9 @@
       <c r="AP281" t="n">
         <v>23.42512893676758</v>
       </c>
+      <c r="AQ281" t="n">
+        <v>22.64977645874023</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -38030,6 +38875,9 @@
       <c r="AP282" t="n">
         <v>23.7718505859375</v>
       </c>
+      <c r="AQ282" t="n">
+        <v>23.11606216430664</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -38164,6 +39012,9 @@
       <c r="AP283" t="n">
         <v>24.17226600646973</v>
       </c>
+      <c r="AQ283" t="n">
+        <v>23.63935089111328</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -38298,6 +39149,9 @@
       <c r="AP284" t="n">
         <v>25.52911758422852</v>
       </c>
+      <c r="AQ284" t="n">
+        <v>25.32576370239258</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -38432,6 +39286,9 @@
       <c r="AP285" t="n">
         <v>26.56990432739258</v>
       </c>
+      <c r="AQ285" t="n">
+        <v>26.34713554382324</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -38566,6 +39423,9 @@
       <c r="AP286" t="n">
         <v>27.61722755432129</v>
       </c>
+      <c r="AQ286" t="n">
+        <v>27.6147575378418</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -38698,6 +39558,9 @@
       <c r="AP287" t="n">
         <v>28.0460033416748</v>
       </c>
+      <c r="AQ287" t="n">
+        <v>28.15756225585938</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -38834,6 +39697,9 @@
       <c r="AP288" t="n">
         <v>15.59114456176758</v>
       </c>
+      <c r="AQ288" t="n">
+        <v>21.02042770385742</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -38968,6 +39834,9 @@
       <c r="AP289" t="n">
         <v>16.17171859741211</v>
       </c>
+      <c r="AQ289" t="n">
+        <v>21.05565452575684</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -39104,6 +39973,9 @@
       <c r="AP290" t="n">
         <v>18.23917961120605</v>
       </c>
+      <c r="AQ290" t="n">
+        <v>21.13389015197754</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -39240,6 +40112,9 @@
       <c r="AP291" t="n">
         <v>20.98245811462402</v>
       </c>
+      <c r="AQ291" t="n">
+        <v>21.6538028717041</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -39374,6 +40249,9 @@
       <c r="AP292" t="n">
         <v>22.23787689208984</v>
       </c>
+      <c r="AQ292" t="n">
+        <v>22.43695259094238</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -39506,6 +40384,9 @@
       <c r="AP293" t="n">
         <v>23.07780838012695</v>
       </c>
+      <c r="AQ293" t="n">
+        <v>23.15833282470703</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -39640,6 +40521,9 @@
       <c r="AP294" t="n">
         <v>23.53498649597168</v>
       </c>
+      <c r="AQ294" t="n">
+        <v>23.67590713500977</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -39774,6 +40658,9 @@
       <c r="AP295" t="n">
         <v>25.20747375488281</v>
       </c>
+      <c r="AQ295" t="n">
+        <v>25.21731948852539</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -39908,6 +40795,9 @@
       <c r="AP296" t="n">
         <v>27.35130500793457</v>
       </c>
+      <c r="AQ296" t="n">
+        <v>27.73063468933105</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -40042,6 +40932,9 @@
       <c r="AP297" t="n">
         <v>28.25246238708496</v>
       </c>
+      <c r="AQ297" t="n">
+        <v>28.43346405029297</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -40176,6 +41069,9 @@
       <c r="AP298" t="n">
         <v>28.51635932922363</v>
       </c>
+      <c r="AQ298" t="n">
+        <v>28.53670501708984</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -40310,6 +41206,9 @@
       <c r="AP299" t="n">
         <v>28.60180282592773</v>
       </c>
+      <c r="AQ299" t="n">
+        <v>28.61967086791992</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -40444,6 +41343,9 @@
       <c r="AP300" t="n">
         <v>28.69684600830078</v>
       </c>
+      <c r="AQ300" t="n">
+        <v>28.69346046447754</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -40578,6 +41480,9 @@
       <c r="AP301" t="n">
         <v>28.80920028686523</v>
       </c>
+      <c r="AQ301" t="n">
+        <v>28.81461715698242</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -40710,6 +41615,9 @@
       <c r="AP302" t="n">
         <v>28.8707332611084</v>
       </c>
+      <c r="AQ302" t="n">
+        <v>28.87404632568359</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -40846,6 +41754,9 @@
       <c r="AP303" t="n">
         <v>18.74532890319824</v>
       </c>
+      <c r="AQ303" t="n">
+        <v>15.12353038787842</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -40980,6 +41891,9 @@
       <c r="AP304" t="n">
         <v>19.09414291381836</v>
       </c>
+      <c r="AQ304" t="n">
+        <v>15.59210205078125</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -41116,6 +42030,9 @@
       <c r="AP305" t="n">
         <v>19.56747245788574</v>
       </c>
+      <c r="AQ305" t="n">
+        <v>16.80072784423828</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -41252,6 +42169,9 @@
       <c r="AP306" t="n">
         <v>20.12062072753906</v>
       </c>
+      <c r="AQ306" t="n">
+        <v>18.2678165435791</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -41386,6 +42306,9 @@
       <c r="AP307" t="n">
         <v>20.65975379943848</v>
       </c>
+      <c r="AQ307" t="n">
+        <v>19.83960342407227</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -41520,6 +42443,9 @@
       <c r="AP308" t="n">
         <v>23.69414520263672</v>
       </c>
+      <c r="AQ308" t="n">
+        <v>23.61900901794434</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -41654,6 +42580,9 @@
       <c r="AP309" t="n">
         <v>25.99255180358887</v>
       </c>
+      <c r="AQ309" t="n">
+        <v>25.39970588684082</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -41788,6 +42717,9 @@
       <c r="AP310" t="n">
         <v>27.76527786254883</v>
       </c>
+      <c r="AQ310" t="n">
+        <v>27.29756927490234</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -41922,6 +42854,9 @@
       <c r="AP311" t="n">
         <v>28.03589820861816</v>
       </c>
+      <c r="AQ311" t="n">
+        <v>27.7185230255127</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -42056,6 +42991,9 @@
       <c r="AP312" t="n">
         <v>28.3977108001709</v>
       </c>
+      <c r="AQ312" t="n">
+        <v>28.11559104919434</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -42190,6 +43128,9 @@
       <c r="AP313" t="n">
         <v>28.64402198791504</v>
       </c>
+      <c r="AQ313" t="n">
+        <v>28.48004341125488</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -42324,6 +43265,9 @@
       <c r="AP314" t="n">
         <v>28.70356559753418</v>
       </c>
+      <c r="AQ314" t="n">
+        <v>28.70376205444336</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -42458,6 +43402,9 @@
       <c r="AP315" t="n">
         <v>28.69138526916504</v>
       </c>
+      <c r="AQ315" t="n">
+        <v>28.7060489654541</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -42592,6 +43539,9 @@
       <c r="AP316" t="n">
         <v>28.78466796875</v>
       </c>
+      <c r="AQ316" t="n">
+        <v>28.79061698913574</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -42726,6 +43676,9 @@
       <c r="AP317" t="n">
         <v>28.93505859375</v>
       </c>
+      <c r="AQ317" t="n">
+        <v>28.93698120117188</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -42860,6 +43813,9 @@
       <c r="AP318" t="n">
         <v>29.01452445983887</v>
       </c>
+      <c r="AQ318" t="n">
+        <v>29.01161766052246</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -42996,6 +43952,9 @@
       <c r="AP319" t="n">
         <v>21.220947265625</v>
       </c>
+      <c r="AQ319" t="n">
+        <v>19.76103973388672</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -43130,6 +44089,9 @@
       <c r="AP320" t="n">
         <v>21.55160903930664</v>
       </c>
+      <c r="AQ320" t="n">
+        <v>19.85703468322754</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -43266,6 +44228,9 @@
       <c r="AP321" t="n">
         <v>22.71562004089355</v>
       </c>
+      <c r="AQ321" t="n">
+        <v>20.55337905883789</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -43402,6 +44367,9 @@
       <c r="AP322" t="n">
         <v>23.85483741760254</v>
       </c>
+      <c r="AQ322" t="n">
+        <v>23.41160011291504</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -43536,6 +44504,9 @@
       <c r="AP323" t="n">
         <v>24.46016693115234</v>
       </c>
+      <c r="AQ323" t="n">
+        <v>24.28715133666992</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -43670,6 +44641,9 @@
       <c r="AP324" t="n">
         <v>24.85470771789551</v>
       </c>
+      <c r="AQ324" t="n">
+        <v>24.54206466674805</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -43804,6 +44778,9 @@
       <c r="AP325" t="n">
         <v>25.29052352905273</v>
       </c>
+      <c r="AQ325" t="n">
+        <v>24.90316390991211</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -43938,6 +44915,9 @@
       <c r="AP326" t="n">
         <v>27.3022632598877</v>
       </c>
+      <c r="AQ326" t="n">
+        <v>26.76376724243164</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -44072,6 +45052,9 @@
       <c r="AP327" t="n">
         <v>27.92728996276855</v>
       </c>
+      <c r="AQ327" t="n">
+        <v>27.78141593933105</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -44206,6 +45189,9 @@
       <c r="AP328" t="n">
         <v>28.35651588439941</v>
       </c>
+      <c r="AQ328" t="n">
+        <v>28.25734519958496</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -44340,6 +45326,9 @@
       <c r="AP329" t="n">
         <v>28.71444892883301</v>
       </c>
+      <c r="AQ329" t="n">
+        <v>28.73231315612793</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -44474,6 +45463,9 @@
       <c r="AP330" t="n">
         <v>28.80207633972168</v>
       </c>
+      <c r="AQ330" t="n">
+        <v>28.80237770080566</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -44610,6 +45602,9 @@
       <c r="AP331" t="n">
         <v>15.26345062255859</v>
       </c>
+      <c r="AQ331" t="n">
+        <v>21.30819320678711</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -44744,6 +45739,9 @@
       <c r="AP332" t="n">
         <v>15.66305923461914</v>
       </c>
+      <c r="AQ332" t="n">
+        <v>21.52836608886719</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -44880,6 +45878,9 @@
       <c r="AP333" t="n">
         <v>17.30778884887695</v>
       </c>
+      <c r="AQ333" t="n">
+        <v>22.06849479675293</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -45016,6 +46017,9 @@
       <c r="AP334" t="n">
         <v>20.86422538757324</v>
       </c>
+      <c r="AQ334" t="n">
+        <v>23.51060676574707</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -45150,6 +46154,9 @@
       <c r="AP335" t="n">
         <v>23.21659660339355</v>
       </c>
+      <c r="AQ335" t="n">
+        <v>25.19290733337402</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -45284,6 +46291,9 @@
       <c r="AP336" t="n">
         <v>25.3267765045166</v>
       </c>
+      <c r="AQ336" t="n">
+        <v>26.27070808410645</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -45418,6 +46428,9 @@
       <c r="AP337" t="n">
         <v>26.54763984680176</v>
       </c>
+      <c r="AQ337" t="n">
+        <v>26.85146903991699</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -45552,6 +46565,9 @@
       <c r="AP338" t="n">
         <v>28.06034660339355</v>
       </c>
+      <c r="AQ338" t="n">
+        <v>27.83628273010254</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -45686,6 +46702,9 @@
       <c r="AP339" t="n">
         <v>28.25774765014648</v>
       </c>
+      <c r="AQ339" t="n">
+        <v>28.26343154907227</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -45820,6 +46839,9 @@
       <c r="AP340" t="n">
         <v>28.40781021118164</v>
       </c>
+      <c r="AQ340" t="n">
+        <v>28.44806289672852</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -45954,6 +46976,9 @@
       <c r="AP341" t="n">
         <v>28.58976173400879</v>
       </c>
+      <c r="AQ341" t="n">
+        <v>28.63133430480957</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -46088,6 +47113,9 @@
       <c r="AP342" t="n">
         <v>28.67561531066895</v>
       </c>
+      <c r="AQ342" t="n">
+        <v>28.69498825073242</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -46222,6 +47250,9 @@
       <c r="AP343" t="n">
         <v>28.6075439453125</v>
       </c>
+      <c r="AQ343" t="n">
+        <v>28.65005683898926</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -46358,6 +47389,9 @@
       <c r="AP344" t="n">
         <v>10.22426414489746</v>
       </c>
+      <c r="AQ344" t="n">
+        <v>16.6060676574707</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -46492,6 +47526,9 @@
       <c r="AP345" t="n">
         <v>12.26615715026855</v>
       </c>
+      <c r="AQ345" t="n">
+        <v>17.06382179260254</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -46628,6 +47665,9 @@
       <c r="AP346" t="n">
         <v>18.67545127868652</v>
       </c>
+      <c r="AQ346" t="n">
+        <v>18.35939598083496</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -46764,6 +47804,9 @@
       <c r="AP347" t="n">
         <v>22.56273460388184</v>
       </c>
+      <c r="AQ347" t="n">
+        <v>21.87009239196777</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -46898,6 +47941,9 @@
       <c r="AP348" t="n">
         <v>24.54242324829102</v>
       </c>
+      <c r="AQ348" t="n">
+        <v>24.34609413146973</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -47032,6 +48078,9 @@
       <c r="AP349" t="n">
         <v>25.83646202087402</v>
       </c>
+      <c r="AQ349" t="n">
+        <v>26.26150894165039</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -47166,6 +48215,9 @@
       <c r="AP350" t="n">
         <v>26.52907752990723</v>
       </c>
+      <c r="AQ350" t="n">
+        <v>27.15086555480957</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -47300,6 +48352,9 @@
       <c r="AP351" t="n">
         <v>27.89325141906738</v>
       </c>
+      <c r="AQ351" t="n">
+        <v>27.89726638793945</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -47434,6 +48489,9 @@
       <c r="AP352" t="n">
         <v>28.1793212890625</v>
       </c>
+      <c r="AQ352" t="n">
+        <v>28.15860748291016</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -47568,6 +48626,9 @@
       <c r="AP353" t="n">
         <v>28.16195869445801</v>
       </c>
+      <c r="AQ353" t="n">
+        <v>28.08459281921387</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -47702,6 +48763,9 @@
       <c r="AP354" t="n">
         <v>28.11186599731445</v>
       </c>
+      <c r="AQ354" t="n">
+        <v>28.14052200317383</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -47836,6 +48900,9 @@
       <c r="AP355" t="n">
         <v>28.33147048950195</v>
       </c>
+      <c r="AQ355" t="n">
+        <v>28.56832313537598</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -47970,6 +49037,9 @@
       <c r="AP356" t="n">
         <v>28.71297645568848</v>
       </c>
+      <c r="AQ356" t="n">
+        <v>28.77165603637695</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -48104,6 +49174,9 @@
       <c r="AP357" t="n">
         <v>29.00062370300293</v>
       </c>
+      <c r="AQ357" t="n">
+        <v>29.00105476379395</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -48238,6 +49311,9 @@
       <c r="AP358" t="n">
         <v>29.02669143676758</v>
       </c>
+      <c r="AQ358" t="n">
+        <v>29.02371978759766</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -48370,6 +49446,9 @@
       <c r="AP359" t="n">
         <v>29.02885437011719</v>
       </c>
+      <c r="AQ359" t="n">
+        <v>29.02586364746094</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -48506,6 +49585,9 @@
       <c r="AP360" t="n">
         <v>16.27379417419434</v>
       </c>
+      <c r="AQ360" t="n">
+        <v>16.06431198120117</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -48640,6 +49722,9 @@
       <c r="AP361" t="n">
         <v>19.13124084472656</v>
       </c>
+      <c r="AQ361" t="n">
+        <v>19.26398277282715</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -48776,6 +49861,9 @@
       <c r="AP362" t="n">
         <v>20.16716766357422</v>
       </c>
+      <c r="AQ362" t="n">
+        <v>19.89260101318359</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -48912,6 +50000,9 @@
       <c r="AP363" t="n">
         <v>21.54142189025879</v>
       </c>
+      <c r="AQ363" t="n">
+        <v>21.24045944213867</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -49046,6 +50137,9 @@
       <c r="AP364" t="n">
         <v>22.37004661560059</v>
       </c>
+      <c r="AQ364" t="n">
+        <v>21.99817276000977</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -49180,6 +50274,9 @@
       <c r="AP365" t="n">
         <v>23.06449317932129</v>
       </c>
+      <c r="AQ365" t="n">
+        <v>22.59972190856934</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -49314,6 +50411,9 @@
       <c r="AP366" t="n">
         <v>23.49189186096191</v>
       </c>
+      <c r="AQ366" t="n">
+        <v>23.02152633666992</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -49445,6 +50545,9 @@
       </c>
       <c r="AP367" t="n">
         <v>23.5559196472168</v>
+      </c>
+      <c r="AQ367" t="n">
+        <v>23.09042167663574</v>
       </c>
     </row>
     <row r="368">
@@ -49562,6 +50665,9 @@
       <c r="AP368" t="n">
         <v>14.98365783691406</v>
       </c>
+      <c r="AQ368" t="n">
+        <v>14.13706874847412</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -49678,6 +50784,9 @@
       <c r="AP369" t="n">
         <v>14.98365783691406</v>
       </c>
+      <c r="AQ369" t="n">
+        <v>14.13706874847412</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -49794,6 +50903,9 @@
       <c r="AP370" t="n">
         <v>14.98365783691406</v>
       </c>
+      <c r="AQ370" t="n">
+        <v>14.13706874847412</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -49910,6 +51022,9 @@
       <c r="AP371" t="n">
         <v>15.00094413757324</v>
       </c>
+      <c r="AQ371" t="n">
+        <v>14.15426731109619</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -50026,6 +51141,9 @@
       <c r="AP372" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ372" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -50142,6 +51260,9 @@
       <c r="AP373" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ373" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -50258,6 +51379,9 @@
       <c r="AP374" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ374" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -50374,6 +51498,9 @@
       <c r="AP375" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ375" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -50490,6 +51617,9 @@
       <c r="AP376" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ376" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -50606,6 +51736,9 @@
       <c r="AP377" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ377" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -50722,6 +51855,9 @@
       <c r="AP378" t="n">
         <v>15.01822948455811</v>
       </c>
+      <c r="AQ378" t="n">
+        <v>14.17146587371826</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -50838,6 +51974,9 @@
       <c r="AP379" t="n">
         <v>15.03551578521729</v>
       </c>
+      <c r="AQ379" t="n">
+        <v>14.18866443634033</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -50974,6 +52113,9 @@
       <c r="AP380" t="n">
         <v>10.50125789642334</v>
       </c>
+      <c r="AQ380" t="n">
+        <v>9.604800224304199</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -51110,6 +52252,9 @@
       <c r="AP381" t="n">
         <v>13.04025840759277</v>
       </c>
+      <c r="AQ381" t="n">
+        <v>12.1819953918457</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -51246,6 +52391,9 @@
       <c r="AP382" t="n">
         <v>14.75036811828613</v>
       </c>
+      <c r="AQ382" t="n">
+        <v>13.88852596282959</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -51382,6 +52530,9 @@
       <c r="AP383" t="n">
         <v>16.36970901489258</v>
       </c>
+      <c r="AQ383" t="n">
+        <v>15.56790447235107</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -51518,6 +52669,9 @@
       <c r="AP384" t="n">
         <v>17.5402660369873</v>
       </c>
+      <c r="AQ384" t="n">
+        <v>17.05747222900391</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -51652,6 +52806,9 @@
       <c r="AP385" t="n">
         <v>18.36733245849609</v>
       </c>
+      <c r="AQ385" t="n">
+        <v>17.8901538848877</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -51786,6 +52943,9 @@
       <c r="AP386" t="n">
         <v>19.60311889648438</v>
       </c>
+      <c r="AQ386" t="n">
+        <v>19.11563110351562</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -51920,6 +53080,9 @@
       <c r="AP387" t="n">
         <v>21.7869873046875</v>
       </c>
+      <c r="AQ387" t="n">
+        <v>21.47417068481445</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -52054,6 +53217,9 @@
       <c r="AP388" t="n">
         <v>23.29780006408691</v>
       </c>
+      <c r="AQ388" t="n">
+        <v>22.98392677307129</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -52190,6 +53356,9 @@
       <c r="AP389" t="n">
         <v>15.95233631134033</v>
       </c>
+      <c r="AQ389" t="n">
+        <v>15.0770959854126</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -52326,6 +53495,9 @@
       <c r="AP390" t="n">
         <v>17.29263305664062</v>
       </c>
+      <c r="AQ390" t="n">
+        <v>16.12882232666016</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -52462,6 +53634,9 @@
       <c r="AP391" t="n">
         <v>18.96387672424316</v>
       </c>
+      <c r="AQ391" t="n">
+        <v>18.57272338867188</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -52598,6 +53773,9 @@
       <c r="AP392" t="n">
         <v>20.34031295776367</v>
       </c>
+      <c r="AQ392" t="n">
+        <v>20.38833236694336</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -52734,6 +53912,9 @@
       <c r="AP393" t="n">
         <v>21.61468315124512</v>
       </c>
+      <c r="AQ393" t="n">
+        <v>21.75552940368652</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -52868,6 +54049,9 @@
       <c r="AP394" t="n">
         <v>23.28638076782227</v>
       </c>
+      <c r="AQ394" t="n">
+        <v>23.43425559997559</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -53002,6 +54186,9 @@
       <c r="AP395" t="n">
         <v>24.66761589050293</v>
       </c>
+      <c r="AQ395" t="n">
+        <v>24.74841499328613</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -53136,6 +54323,9 @@
       <c r="AP396" t="n">
         <v>28.33666610717773</v>
       </c>
+      <c r="AQ396" t="n">
+        <v>28.4445686340332</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -53270,6 +54460,9 @@
       <c r="AP397" t="n">
         <v>30.91989898681641</v>
       </c>
+      <c r="AQ397" t="n">
+        <v>30.93518257141113</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -53402,6 +54595,9 @@
       <c r="AP398" t="n">
         <v>32.2544059753418</v>
       </c>
+      <c r="AQ398" t="n">
+        <v>32.26997375488281</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -53538,6 +54734,9 @@
       <c r="AP399" t="n">
         <v>6.808199405670166</v>
       </c>
+      <c r="AQ399" t="n">
+        <v>5.643265724182129</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -53674,6 +54873,9 @@
       <c r="AP400" t="n">
         <v>11.05593681335449</v>
       </c>
+      <c r="AQ400" t="n">
+        <v>9.443052291870117</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -53810,6 +55012,9 @@
       <c r="AP401" t="n">
         <v>16.15055656433105</v>
       </c>
+      <c r="AQ401" t="n">
+        <v>14.87159538269043</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -53946,6 +55151,9 @@
       <c r="AP402" t="n">
         <v>20.67016792297363</v>
       </c>
+      <c r="AQ402" t="n">
+        <v>20.3464412689209</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -54082,6 +55290,9 @@
       <c r="AP403" t="n">
         <v>22.90536308288574</v>
       </c>
+      <c r="AQ403" t="n">
+        <v>22.5659122467041</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -54216,6 +55427,9 @@
       <c r="AP404" t="n">
         <v>24.0770206451416</v>
       </c>
+      <c r="AQ404" t="n">
+        <v>23.93642807006836</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -54350,6 +55564,9 @@
       <c r="AP405" t="n">
         <v>25.01283073425293</v>
       </c>
+      <c r="AQ405" t="n">
+        <v>25.06189155578613</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -54484,6 +55701,9 @@
       <c r="AP406" t="n">
         <v>26.62985992431641</v>
       </c>
+      <c r="AQ406" t="n">
+        <v>26.63214874267578</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -54618,6 +55838,9 @@
       <c r="AP407" t="n">
         <v>27.50965690612793</v>
       </c>
+      <c r="AQ407" t="n">
+        <v>27.52316284179688</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -54752,6 +55975,9 @@
       <c r="AP408" t="n">
         <v>28.0880012512207</v>
       </c>
+      <c r="AQ408" t="n">
+        <v>28.11582374572754</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -54884,6 +56110,9 @@
       <c r="AP409" t="n">
         <v>28.40382766723633</v>
       </c>
+      <c r="AQ409" t="n">
+        <v>28.47067451477051</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -55014,6 +56243,9 @@
       <c r="AP410" t="n">
         <v>11.51617431640625</v>
       </c>
+      <c r="AQ410" t="n">
+        <v>5.105861663818359</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -55144,6 +56376,9 @@
       <c r="AP411" t="n">
         <v>18.31122398376465</v>
       </c>
+      <c r="AQ411" t="n">
+        <v>16.25967407226562</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -55274,6 +56509,9 @@
       <c r="AP412" t="n">
         <v>21.21067047119141</v>
       </c>
+      <c r="AQ412" t="n">
+        <v>20.33977508544922</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -55408,6 +56646,9 @@
       <c r="AP413" t="n">
         <v>0.1977052092552185</v>
       </c>
+      <c r="AQ413" t="n">
+        <v>0.3946677148342133</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -55542,6 +56783,9 @@
       <c r="AP414" t="n">
         <v>4.079961776733398</v>
       </c>
+      <c r="AQ414" t="n">
+        <v>1.949566602706909</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -55678,6 +56922,9 @@
       <c r="AP415" t="n">
         <v>17.67835426330566</v>
       </c>
+      <c r="AQ415" t="n">
+        <v>17.53315162658691</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -55814,6 +57061,9 @@
       <c r="AP416" t="n">
         <v>29.40975952148438</v>
       </c>
+      <c r="AQ416" t="n">
+        <v>29.38474273681641</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -55944,6 +57194,9 @@
       <c r="AP417" t="n">
         <v>0.1047332212328911</v>
       </c>
+      <c r="AQ417" t="n">
+        <v>0.1949833482503891</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -56072,6 +57325,9 @@
       <c r="AP418" t="n">
         <v>0.3281152248382568</v>
       </c>
+      <c r="AQ418" t="n">
+        <v>0.3538044095039368</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -56202,6 +57458,9 @@
       <c r="AP419" t="n">
         <v>13.70923233032227</v>
       </c>
+      <c r="AQ419" t="n">
+        <v>14.40653324127197</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -56332,6 +57591,9 @@
       <c r="AP420" t="n">
         <v>0.1594775468111038</v>
       </c>
+      <c r="AQ420" t="n">
+        <v>0.2032881528139114</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -56462,6 +57724,9 @@
       <c r="AP421" t="n">
         <v>5.313482284545898</v>
       </c>
+      <c r="AQ421" t="n">
+        <v>0.7063271403312683</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -56592,6 +57857,9 @@
       <c r="AP422" t="n">
         <v>17.64399528503418</v>
       </c>
+      <c r="AQ422" t="n">
+        <v>17.61746215820312</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -56722,6 +57990,9 @@
       <c r="AP423" t="n">
         <v>1.110617876052856</v>
       </c>
+      <c r="AQ423" t="n">
+        <v>0.6850104331970215</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -56852,6 +58123,9 @@
       <c r="AP424" t="n">
         <v>1.542683005332947</v>
       </c>
+      <c r="AQ424" t="n">
+        <v>0.9700517058372498</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -56982,6 +58256,9 @@
       <c r="AP425" t="n">
         <v>18.10881805419922</v>
       </c>
+      <c r="AQ425" t="n">
+        <v>17.10086059570312</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -57118,6 +58395,9 @@
       <c r="AP426" t="n">
         <v>0.6803593039512634</v>
       </c>
+      <c r="AQ426" t="n">
+        <v>0.6844961643218994</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -57254,6 +58534,9 @@
       <c r="AP427" t="n">
         <v>0.4051626920700073</v>
       </c>
+      <c r="AQ427" t="n">
+        <v>0.3914735913276672</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -57390,6 +58673,9 @@
       <c r="AP428" t="n">
         <v>1.984001159667969</v>
       </c>
+      <c r="AQ428" t="n">
+        <v>0.7893977165222168</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -57526,6 +58812,9 @@
       <c r="AP429" t="n">
         <v>18.01482963562012</v>
       </c>
+      <c r="AQ429" t="n">
+        <v>17.53961944580078</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -57662,6 +58951,9 @@
       <c r="AP430" t="n">
         <v>24.69384574890137</v>
       </c>
+      <c r="AQ430" t="n">
+        <v>24.44275093078613</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -57796,6 +59088,9 @@
       <c r="AP431" t="n">
         <v>26.61535835266113</v>
       </c>
+      <c r="AQ431" t="n">
+        <v>26.28457069396973</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -57930,6 +59225,9 @@
       <c r="AP432" t="n">
         <v>27.92351341247559</v>
       </c>
+      <c r="AQ432" t="n">
+        <v>27.58999633789062</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -58064,6 +59362,9 @@
       <c r="AP433" t="n">
         <v>29.23624801635742</v>
       </c>
+      <c r="AQ433" t="n">
+        <v>28.79334259033203</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -58198,6 +59499,9 @@
       <c r="AP434" t="n">
         <v>29.46724128723145</v>
       </c>
+      <c r="AQ434" t="n">
+        <v>29.32671165466309</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -58332,6 +59636,9 @@
       <c r="AP435" t="n">
         <v>28.73771095275879</v>
       </c>
+      <c r="AQ435" t="n">
+        <v>28.69418716430664</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -58466,6 +59773,9 @@
       <c r="AP436" t="n">
         <v>29.35067558288574</v>
       </c>
+      <c r="AQ436" t="n">
+        <v>29.3402271270752</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -58596,6 +59906,9 @@
       <c r="AP437" t="n">
         <v>1.912530183792114</v>
       </c>
+      <c r="AQ437" t="n">
+        <v>1.51196277141571</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -58726,6 +60039,9 @@
       <c r="AP438" t="n">
         <v>4.809910297393799</v>
       </c>
+      <c r="AQ438" t="n">
+        <v>0.8891761302947998</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -58856,6 +60172,9 @@
       <c r="AP439" t="n">
         <v>18.78932762145996</v>
       </c>
+      <c r="AQ439" t="n">
+        <v>17.14955711364746</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -58992,6 +60311,9 @@
       <c r="AP440" t="n">
         <v>0.1652772724628448</v>
       </c>
+      <c r="AQ440" t="n">
+        <v>0.1923704594373703</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -59128,6 +60450,9 @@
       <c r="AP441" t="n">
         <v>0.1707722842693329</v>
       </c>
+      <c r="AQ441" t="n">
+        <v>0.292548656463623</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -59264,6 +60589,9 @@
       <c r="AP442" t="n">
         <v>1.214222550392151</v>
       </c>
+      <c r="AQ442" t="n">
+        <v>3.363633155822754</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -59400,6 +60728,9 @@
       <c r="AP443" t="n">
         <v>16.53204154968262</v>
       </c>
+      <c r="AQ443" t="n">
+        <v>19.42997169494629</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -59536,6 +60867,9 @@
       <c r="AP444" t="n">
         <v>23.74292373657227</v>
       </c>
+      <c r="AQ444" t="n">
+        <v>23.83941841125488</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -59670,6 +61004,9 @@
       <c r="AP445" t="n">
         <v>25.31774711608887</v>
       </c>
+      <c r="AQ445" t="n">
+        <v>25.11545562744141</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -59804,6 +61141,9 @@
       <c r="AP446" t="n">
         <v>25.90078163146973</v>
       </c>
+      <c r="AQ446" t="n">
+        <v>25.79257583618164</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -59938,6 +61278,9 @@
       <c r="AP447" t="n">
         <v>26.73548126220703</v>
       </c>
+      <c r="AQ447" t="n">
+        <v>26.41888427734375</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -60072,6 +61415,9 @@
       <c r="AP448" t="n">
         <v>27.07662391662598</v>
       </c>
+      <c r="AQ448" t="n">
+        <v>26.60810279846191</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -60206,6 +61552,9 @@
       <c r="AP449" t="n">
         <v>27.96506500244141</v>
       </c>
+      <c r="AQ449" t="n">
+        <v>27.88360977172852</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -60340,6 +61689,9 @@
       <c r="AP450" t="n">
         <v>29.16689300537109</v>
       </c>
+      <c r="AQ450" t="n">
+        <v>29.15511703491211</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -60470,6 +61822,9 @@
       <c r="AP451" t="n">
         <v>5.736687183380127</v>
       </c>
+      <c r="AQ451" t="n">
+        <v>3.673985481262207</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -60600,6 +61955,9 @@
       <c r="AP452" t="n">
         <v>7.037432193756104</v>
       </c>
+      <c r="AQ452" t="n">
+        <v>1.468786954879761</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -60730,6 +62088,9 @@
       <c r="AP453" t="n">
         <v>14.48148345947266</v>
       </c>
+      <c r="AQ453" t="n">
+        <v>9.719404220581055</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -60856,6 +62217,9 @@
       <c r="AP454" t="n">
         <v>3.712711334228516</v>
       </c>
+      <c r="AQ454" t="n">
+        <v>3.370521068572998</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -60986,6 +62350,9 @@
       <c r="AP455" t="n">
         <v>6.080631256103516</v>
       </c>
+      <c r="AQ455" t="n">
+        <v>3.080264806747437</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -61116,6 +62483,9 @@
       <c r="AP456" t="n">
         <v>8.426853179931641</v>
       </c>
+      <c r="AQ456" t="n">
+        <v>4.471447944641113</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -61246,6 +62616,9 @@
       <c r="AP457" t="n">
         <v>9.004777908325195</v>
       </c>
+      <c r="AQ457" t="n">
+        <v>13.07374000549316</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -61376,6 +62749,9 @@
       <c r="AP458" t="n">
         <v>18.83650970458984</v>
       </c>
+      <c r="AQ458" t="n">
+        <v>16.97361755371094</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -61504,6 +62880,9 @@
       <c r="AP459" t="n">
         <v>22.96933937072754</v>
       </c>
+      <c r="AQ459" t="n">
+        <v>19.97122573852539</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -61632,6 +63011,9 @@
       <c r="AP460" t="n">
         <v>24.64372253417969</v>
       </c>
+      <c r="AQ460" t="n">
+        <v>21.77870750427246</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -61760,6 +63142,9 @@
       <c r="AP461" t="n">
         <v>25.76840400695801</v>
       </c>
+      <c r="AQ461" t="n">
+        <v>23.29887771606445</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -61888,6 +63273,9 @@
       <c r="AP462" t="n">
         <v>25.01832962036133</v>
       </c>
+      <c r="AQ462" t="n">
+        <v>23.96614646911621</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -62016,6 +63404,9 @@
       <c r="AP463" t="n">
         <v>26.26592445373535</v>
       </c>
+      <c r="AQ463" t="n">
+        <v>26.34177017211914</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -62141,6 +63532,9 @@
       </c>
       <c r="AP464" t="n">
         <v>26.90317344665527</v>
+      </c>
+      <c r="AQ464" t="n">
+        <v>26.24178504943848</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
+++ b/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ464"/>
+  <dimension ref="A1:AR464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,6 +631,11 @@
           <t>pred2mine2l_z2</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>remin2l_z2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -768,6 +773,9 @@
       <c r="AQ2" t="n">
         <v>22.43636131286621</v>
       </c>
+      <c r="AR2" t="n">
+        <v>22.75328254699707</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +909,9 @@
       <c r="AQ3" t="n">
         <v>22.43636131286621</v>
       </c>
+      <c r="AR3" t="n">
+        <v>22.75328254699707</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1043,9 @@
       <c r="AQ4" t="n">
         <v>22.43636131286621</v>
       </c>
+      <c r="AR4" t="n">
+        <v>22.75328254699707</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1183,9 @@
       <c r="AQ5" t="n">
         <v>22.48161888122559</v>
       </c>
+      <c r="AR5" t="n">
+        <v>22.78958129882812</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1300,6 +1317,9 @@
       <c r="AQ6" t="n">
         <v>22.69892883300781</v>
       </c>
+      <c r="AR6" t="n">
+        <v>22.9162540435791</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1439,6 +1459,9 @@
       <c r="AQ7" t="n">
         <v>22.69892883300781</v>
       </c>
+      <c r="AR7" t="n">
+        <v>22.9162540435791</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1578,6 +1601,9 @@
       <c r="AQ8" t="n">
         <v>23.3166675567627</v>
       </c>
+      <c r="AR8" t="n">
+        <v>23.35495567321777</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1709,6 +1735,9 @@
       <c r="AQ9" t="n">
         <v>23.60137939453125</v>
       </c>
+      <c r="AR9" t="n">
+        <v>23.64489936828613</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1846,6 +1875,9 @@
       <c r="AQ10" t="n">
         <v>23.83181762695312</v>
       </c>
+      <c r="AR10" t="n">
+        <v>23.8386058807373</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1983,6 +2015,9 @@
       <c r="AQ11" t="n">
         <v>24.29356956481934</v>
       </c>
+      <c r="AR11" t="n">
+        <v>24.32829284667969</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2114,6 +2149,9 @@
       <c r="AQ12" t="n">
         <v>24.88991165161133</v>
       </c>
+      <c r="AR12" t="n">
+        <v>24.86928176879883</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2251,6 +2289,9 @@
       <c r="AQ13" t="n">
         <v>24.88991165161133</v>
       </c>
+      <c r="AR13" t="n">
+        <v>24.86928176879883</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2388,6 +2429,9 @@
       <c r="AQ14" t="n">
         <v>27.06662559509277</v>
       </c>
+      <c r="AR14" t="n">
+        <v>27.09538078308105</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2519,6 +2563,9 @@
       <c r="AQ15" t="n">
         <v>29.05513954162598</v>
       </c>
+      <c r="AR15" t="n">
+        <v>28.99318695068359</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2656,6 +2703,9 @@
       <c r="AQ16" t="n">
         <v>29.05513954162598</v>
       </c>
+      <c r="AR16" t="n">
+        <v>28.99318695068359</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2793,6 +2843,9 @@
       <c r="AQ17" t="n">
         <v>29.83145713806152</v>
       </c>
+      <c r="AR17" t="n">
+        <v>29.84993553161621</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2930,6 +2983,9 @@
       <c r="AQ18" t="n">
         <v>30.04994964599609</v>
       </c>
+      <c r="AR18" t="n">
+        <v>30.04936408996582</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3065,6 +3121,9 @@
       <c r="AQ19" t="n">
         <v>30.09794235229492</v>
       </c>
+      <c r="AR19" t="n">
+        <v>30.10688591003418</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3194,6 +3253,9 @@
       <c r="AQ20" t="n">
         <v>30.09794235229492</v>
       </c>
+      <c r="AR20" t="n">
+        <v>30.10688591003418</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3333,6 +3395,9 @@
       <c r="AQ21" t="n">
         <v>23.64029312133789</v>
       </c>
+      <c r="AR21" t="n">
+        <v>23.65010452270508</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3464,6 +3529,9 @@
       <c r="AQ22" t="n">
         <v>23.64029312133789</v>
       </c>
+      <c r="AR22" t="n">
+        <v>23.65010452270508</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3601,6 +3669,9 @@
       <c r="AQ23" t="n">
         <v>23.67545700073242</v>
       </c>
+      <c r="AR23" t="n">
+        <v>23.68566703796387</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3740,6 +3811,9 @@
       <c r="AQ24" t="n">
         <v>23.72985076904297</v>
       </c>
+      <c r="AR24" t="n">
+        <v>23.74444770812988</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3871,6 +3945,9 @@
       <c r="AQ25" t="n">
         <v>23.72985076904297</v>
       </c>
+      <c r="AR25" t="n">
+        <v>23.74444770812988</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4010,6 +4087,9 @@
       <c r="AQ26" t="n">
         <v>23.82114028930664</v>
       </c>
+      <c r="AR26" t="n">
+        <v>23.84149551391602</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4141,6 +4221,9 @@
       <c r="AQ27" t="n">
         <v>23.85807418823242</v>
       </c>
+      <c r="AR27" t="n">
+        <v>23.88356971740723</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4278,6 +4361,9 @@
       <c r="AQ28" t="n">
         <v>23.89603614807129</v>
       </c>
+      <c r="AR28" t="n">
+        <v>23.92388153076172</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4415,6 +4501,9 @@
       <c r="AQ29" t="n">
         <v>23.99274826049805</v>
       </c>
+      <c r="AR29" t="n">
+        <v>24.01241493225098</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4546,6 +4635,9 @@
       <c r="AQ30" t="n">
         <v>24.09142112731934</v>
       </c>
+      <c r="AR30" t="n">
+        <v>24.0989818572998</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4683,6 +4775,9 @@
       <c r="AQ31" t="n">
         <v>24.09142112731934</v>
       </c>
+      <c r="AR31" t="n">
+        <v>24.0989818572998</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4820,6 +4915,9 @@
       <c r="AQ32" t="n">
         <v>24.22990226745605</v>
       </c>
+      <c r="AR32" t="n">
+        <v>24.2551212310791</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4957,6 +5055,9 @@
       <c r="AQ33" t="n">
         <v>24.38776588439941</v>
       </c>
+      <c r="AR33" t="n">
+        <v>24.39021873474121</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5088,6 +5189,9 @@
       <c r="AQ34" t="n">
         <v>24.38850212097168</v>
       </c>
+      <c r="AR34" t="n">
+        <v>24.39094161987305</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5225,6 +5329,9 @@
       <c r="AQ35" t="n">
         <v>24.55635452270508</v>
       </c>
+      <c r="AR35" t="n">
+        <v>24.55882263183594</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5358,6 +5465,9 @@
       <c r="AQ36" t="n">
         <v>24.29000854492188</v>
       </c>
+      <c r="AR36" t="n">
+        <v>24.2704906463623</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5495,6 +5605,9 @@
       <c r="AQ37" t="n">
         <v>24.29000854492188</v>
       </c>
+      <c r="AR37" t="n">
+        <v>24.2704906463623</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5632,6 +5745,9 @@
       <c r="AQ38" t="n">
         <v>24.27465438842773</v>
       </c>
+      <c r="AR38" t="n">
+        <v>24.25820922851562</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5771,6 +5887,9 @@
       <c r="AQ39" t="n">
         <v>24.25114440917969</v>
       </c>
+      <c r="AR39" t="n">
+        <v>24.23410415649414</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5910,6 +6029,9 @@
       <c r="AQ40" t="n">
         <v>24.21247291564941</v>
       </c>
+      <c r="AR40" t="n">
+        <v>24.19211769104004</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6047,6 +6169,9 @@
       <c r="AQ41" t="n">
         <v>24.17782592773438</v>
       </c>
+      <c r="AR41" t="n">
+        <v>24.15837478637695</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6184,6 +6309,9 @@
       <c r="AQ42" t="n">
         <v>24.14359092712402</v>
       </c>
+      <c r="AR42" t="n">
+        <v>24.13364601135254</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6321,6 +6449,9 @@
       <c r="AQ43" t="n">
         <v>24.12019729614258</v>
       </c>
+      <c r="AR43" t="n">
+        <v>24.11920547485352</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6458,6 +6589,9 @@
       <c r="AQ44" t="n">
         <v>24.10380554199219</v>
       </c>
+      <c r="AR44" t="n">
+        <v>24.10041809082031</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6595,6 +6729,9 @@
       <c r="AQ45" t="n">
         <v>24.10420417785645</v>
       </c>
+      <c r="AR45" t="n">
+        <v>24.10660362243652</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6732,6 +6869,9 @@
       <c r="AQ46" t="n">
         <v>24.13065147399902</v>
       </c>
+      <c r="AR46" t="n">
+        <v>24.12936592102051</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6869,6 +7009,9 @@
       <c r="AQ47" t="n">
         <v>24.15222930908203</v>
       </c>
+      <c r="AR47" t="n">
+        <v>24.15985298156738</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7006,6 +7149,9 @@
       <c r="AQ48" t="n">
         <v>24.1871223449707</v>
       </c>
+      <c r="AR48" t="n">
+        <v>24.19430923461914</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7141,6 +7287,9 @@
       <c r="AQ49" t="n">
         <v>24.19433784484863</v>
       </c>
+      <c r="AR49" t="n">
+        <v>24.2006721496582</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7276,6 +7425,9 @@
       <c r="AQ50" t="n">
         <v>24.19433784484863</v>
       </c>
+      <c r="AR50" t="n">
+        <v>24.2006721496582</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7409,6 +7561,9 @@
       <c r="AQ51" t="n">
         <v>22.44287490844727</v>
       </c>
+      <c r="AR51" t="n">
+        <v>22.45943832397461</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7542,6 +7697,9 @@
       <c r="AQ52" t="n">
         <v>23.59730911254883</v>
       </c>
+      <c r="AR52" t="n">
+        <v>23.57793998718262</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7675,6 +7833,9 @@
       <c r="AQ53" t="n">
         <v>24.55478477478027</v>
       </c>
+      <c r="AR53" t="n">
+        <v>24.60188102722168</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7814,6 +7975,9 @@
       <c r="AQ54" t="n">
         <v>21.41876411437988</v>
       </c>
+      <c r="AR54" t="n">
+        <v>21.53346633911133</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7951,6 +8115,9 @@
       <c r="AQ55" t="n">
         <v>22.64809417724609</v>
       </c>
+      <c r="AR55" t="n">
+        <v>22.59612846374512</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8090,6 +8257,9 @@
       <c r="AQ56" t="n">
         <v>24.49677848815918</v>
       </c>
+      <c r="AR56" t="n">
+        <v>24.35014152526855</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8229,6 +8399,9 @@
       <c r="AQ57" t="n">
         <v>25.78945350646973</v>
       </c>
+      <c r="AR57" t="n">
+        <v>25.77002143859863</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8366,6 +8539,9 @@
       <c r="AQ58" t="n">
         <v>26.63006401062012</v>
       </c>
+      <c r="AR58" t="n">
+        <v>26.65719223022461</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8503,6 +8679,9 @@
       <c r="AQ59" t="n">
         <v>26.97157287597656</v>
       </c>
+      <c r="AR59" t="n">
+        <v>26.96162986755371</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8640,6 +8819,9 @@
       <c r="AQ60" t="n">
         <v>27.16524887084961</v>
       </c>
+      <c r="AR60" t="n">
+        <v>27.15011978149414</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8777,6 +8959,9 @@
       <c r="AQ61" t="n">
         <v>27.40969467163086</v>
       </c>
+      <c r="AR61" t="n">
+        <v>27.39953231811523</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8914,6 +9099,9 @@
       <c r="AQ62" t="n">
         <v>27.65495491027832</v>
       </c>
+      <c r="AR62" t="n">
+        <v>27.66019630432129</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9051,6 +9239,9 @@
       <c r="AQ63" t="n">
         <v>27.92228317260742</v>
       </c>
+      <c r="AR63" t="n">
+        <v>27.92310905456543</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9188,6 +9379,9 @@
       <c r="AQ64" t="n">
         <v>28.03413772583008</v>
       </c>
+      <c r="AR64" t="n">
+        <v>28.04186630249023</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9325,6 +9519,9 @@
       <c r="AQ65" t="n">
         <v>28.26225852966309</v>
       </c>
+      <c r="AR65" t="n">
+        <v>28.2727108001709</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9462,6 +9659,9 @@
       <c r="AQ66" t="n">
         <v>28.59826278686523</v>
       </c>
+      <c r="AR66" t="n">
+        <v>28.59513854980469</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9595,6 +9795,9 @@
       <c r="AQ67" t="n">
         <v>28.84344863891602</v>
       </c>
+      <c r="AR67" t="n">
+        <v>28.84404182434082</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9732,6 +9935,9 @@
       <c r="AQ68" t="n">
         <v>28.90419578552246</v>
       </c>
+      <c r="AR68" t="n">
+        <v>28.90424919128418</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9867,6 +10073,9 @@
       <c r="AQ69" t="n">
         <v>28.90805816650391</v>
       </c>
+      <c r="AR69" t="n">
+        <v>28.90841293334961</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9994,6 +10203,9 @@
       <c r="AQ70" t="n">
         <v>17.62956237792969</v>
       </c>
+      <c r="AR70" t="n">
+        <v>17.9348201751709</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10127,6 +10339,9 @@
       <c r="AQ71" t="n">
         <v>17.62956237792969</v>
       </c>
+      <c r="AR71" t="n">
+        <v>17.9348201751709</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10258,6 +10473,9 @@
       <c r="AQ72" t="n">
         <v>20.44615173339844</v>
       </c>
+      <c r="AR72" t="n">
+        <v>20.50504875183105</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10391,6 +10609,9 @@
       <c r="AQ73" t="n">
         <v>24.51637840270996</v>
       </c>
+      <c r="AR73" t="n">
+        <v>24.61410713195801</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10518,6 +10739,9 @@
       <c r="AQ74" t="n">
         <v>24.51637840270996</v>
       </c>
+      <c r="AR74" t="n">
+        <v>24.61410713195801</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10651,6 +10875,9 @@
       <c r="AQ75" t="n">
         <v>26.15978050231934</v>
       </c>
+      <c r="AR75" t="n">
+        <v>26.18566513061523</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10778,6 +11005,9 @@
       <c r="AQ76" t="n">
         <v>26.60834693908691</v>
       </c>
+      <c r="AR76" t="n">
+        <v>26.67647743225098</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10909,6 +11139,9 @@
       <c r="AQ77" t="n">
         <v>26.87260818481445</v>
       </c>
+      <c r="AR77" t="n">
+        <v>26.90222549438477</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11040,6 +11273,9 @@
       <c r="AQ78" t="n">
         <v>27.15390205383301</v>
       </c>
+      <c r="AR78" t="n">
+        <v>27.1345329284668</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11167,6 +11403,9 @@
       <c r="AQ79" t="n">
         <v>27.18051719665527</v>
       </c>
+      <c r="AR79" t="n">
+        <v>27.15632629394531</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11298,6 +11537,9 @@
       <c r="AQ80" t="n">
         <v>27.18051719665527</v>
       </c>
+      <c r="AR80" t="n">
+        <v>27.15632629394531</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11429,6 +11671,9 @@
       <c r="AQ81" t="n">
         <v>25.81042289733887</v>
       </c>
+      <c r="AR81" t="n">
+        <v>25.81165885925293</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11560,6 +11805,9 @@
       <c r="AQ82" t="n">
         <v>26.17525291442871</v>
       </c>
+      <c r="AR82" t="n">
+        <v>26.13022613525391</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11687,6 +11935,9 @@
       <c r="AQ83" t="n">
         <v>26.17525291442871</v>
       </c>
+      <c r="AR83" t="n">
+        <v>26.13022613525391</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11818,6 +12069,9 @@
       <c r="AQ84" t="n">
         <v>28.32012367248535</v>
       </c>
+      <c r="AR84" t="n">
+        <v>28.32633972167969</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11945,6 +12199,9 @@
       <c r="AQ85" t="n">
         <v>28.72781372070312</v>
       </c>
+      <c r="AR85" t="n">
+        <v>28.73254203796387</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12076,6 +12333,9 @@
       <c r="AQ86" t="n">
         <v>28.72869682312012</v>
       </c>
+      <c r="AR86" t="n">
+        <v>28.7333869934082</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12215,6 +12475,9 @@
       <c r="AQ87" t="n">
         <v>15.90183448791504</v>
       </c>
+      <c r="AR87" t="n">
+        <v>16.09998893737793</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12352,6 +12615,9 @@
       <c r="AQ88" t="n">
         <v>17.57133483886719</v>
       </c>
+      <c r="AR88" t="n">
+        <v>17.71602058410645</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12491,6 +12757,9 @@
       <c r="AQ89" t="n">
         <v>19.84147644042969</v>
       </c>
+      <c r="AR89" t="n">
+        <v>19.98680114746094</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12630,6 +12899,9 @@
       <c r="AQ90" t="n">
         <v>23.69522476196289</v>
       </c>
+      <c r="AR90" t="n">
+        <v>23.73740577697754</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12767,6 +13039,9 @@
       <c r="AQ91" t="n">
         <v>26.21978569030762</v>
       </c>
+      <c r="AR91" t="n">
+        <v>26.2108154296875</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12904,6 +13179,9 @@
       <c r="AQ92" t="n">
         <v>26.62049293518066</v>
       </c>
+      <c r="AR92" t="n">
+        <v>26.61051177978516</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13041,6 +13319,9 @@
       <c r="AQ93" t="n">
         <v>26.57134628295898</v>
       </c>
+      <c r="AR93" t="n">
+        <v>26.56083679199219</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13178,6 +13459,9 @@
       <c r="AQ94" t="n">
         <v>26.61965179443359</v>
       </c>
+      <c r="AR94" t="n">
+        <v>26.61358261108398</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13315,6 +13599,9 @@
       <c r="AQ95" t="n">
         <v>27.38665580749512</v>
       </c>
+      <c r="AR95" t="n">
+        <v>27.39115333557129</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13452,6 +13739,9 @@
       <c r="AQ96" t="n">
         <v>28.23541069030762</v>
       </c>
+      <c r="AR96" t="n">
+        <v>28.23690414428711</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13589,6 +13879,9 @@
       <c r="AQ97" t="n">
         <v>28.58251571655273</v>
       </c>
+      <c r="AR97" t="n">
+        <v>28.5811653137207</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13726,6 +14019,9 @@
       <c r="AQ98" t="n">
         <v>28.66877746582031</v>
       </c>
+      <c r="AR98" t="n">
+        <v>28.66858863830566</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13863,6 +14159,9 @@
       <c r="AQ99" t="n">
         <v>28.96045684814453</v>
       </c>
+      <c r="AR99" t="n">
+        <v>28.96082496643066</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14000,6 +14299,9 @@
       <c r="AQ100" t="n">
         <v>28.9649715423584</v>
       </c>
+      <c r="AR100" t="n">
+        <v>28.96495246887207</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14137,6 +14439,9 @@
       <c r="AQ101" t="n">
         <v>28.93512344360352</v>
       </c>
+      <c r="AR101" t="n">
+        <v>28.93520545959473</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14272,6 +14577,9 @@
       <c r="AQ102" t="n">
         <v>28.92127227783203</v>
       </c>
+      <c r="AR102" t="n">
+        <v>28.92132568359375</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14411,6 +14719,9 @@
       <c r="AQ103" t="n">
         <v>14.65914440155029</v>
       </c>
+      <c r="AR103" t="n">
+        <v>14.8942403793335</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14548,6 +14859,9 @@
       <c r="AQ104" t="n">
         <v>15.72530841827393</v>
       </c>
+      <c r="AR104" t="n">
+        <v>15.95005989074707</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14687,6 +15001,9 @@
       <c r="AQ105" t="n">
         <v>19.20228385925293</v>
       </c>
+      <c r="AR105" t="n">
+        <v>19.24592971801758</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14826,6 +15143,9 @@
       <c r="AQ106" t="n">
         <v>25.07301712036133</v>
       </c>
+      <c r="AR106" t="n">
+        <v>25.07344055175781</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14963,6 +15283,9 @@
       <c r="AQ107" t="n">
         <v>26.65420532226562</v>
       </c>
+      <c r="AR107" t="n">
+        <v>26.65196228027344</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -15100,6 +15423,9 @@
       <c r="AQ108" t="n">
         <v>27.19811820983887</v>
       </c>
+      <c r="AR108" t="n">
+        <v>27.19455146789551</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15237,6 +15563,9 @@
       <c r="AQ109" t="n">
         <v>27.48202896118164</v>
       </c>
+      <c r="AR109" t="n">
+        <v>27.47851181030273</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15374,6 +15703,9 @@
       <c r="AQ110" t="n">
         <v>27.7675895690918</v>
       </c>
+      <c r="AR110" t="n">
+        <v>27.76840972900391</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15511,6 +15843,9 @@
       <c r="AQ111" t="n">
         <v>28.00334167480469</v>
       </c>
+      <c r="AR111" t="n">
+        <v>28.00324058532715</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15648,6 +15983,9 @@
       <c r="AQ112" t="n">
         <v>28.42632293701172</v>
       </c>
+      <c r="AR112" t="n">
+        <v>28.42557525634766</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15785,6 +16123,9 @@
       <c r="AQ113" t="n">
         <v>28.69116592407227</v>
       </c>
+      <c r="AR113" t="n">
+        <v>28.69045257568359</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15922,6 +16263,9 @@
       <c r="AQ114" t="n">
         <v>28.8226203918457</v>
       </c>
+      <c r="AR114" t="n">
+        <v>28.82217025756836</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16059,6 +16403,9 @@
       <c r="AQ115" t="n">
         <v>28.91921234130859</v>
       </c>
+      <c r="AR115" t="n">
+        <v>28.91896820068359</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16196,6 +16543,9 @@
       <c r="AQ116" t="n">
         <v>28.97601127624512</v>
       </c>
+      <c r="AR116" t="n">
+        <v>28.97578811645508</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16335,6 +16685,9 @@
       <c r="AQ117" t="n">
         <v>19.85209274291992</v>
       </c>
+      <c r="AR117" t="n">
+        <v>20.0175666809082</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16472,6 +16825,9 @@
       <c r="AQ118" t="n">
         <v>19.95232772827148</v>
       </c>
+      <c r="AR118" t="n">
+        <v>20.10251235961914</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16611,6 +16967,9 @@
       <c r="AQ119" t="n">
         <v>20.10055160522461</v>
       </c>
+      <c r="AR119" t="n">
+        <v>20.27568626403809</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16750,6 +17109,9 @@
       <c r="AQ120" t="n">
         <v>20.35651588439941</v>
       </c>
+      <c r="AR120" t="n">
+        <v>20.52360153198242</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16887,6 +17249,9 @@
       <c r="AQ121" t="n">
         <v>20.57992362976074</v>
       </c>
+      <c r="AR121" t="n">
+        <v>20.72831535339355</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17024,6 +17389,9 @@
       <c r="AQ122" t="n">
         <v>20.89484596252441</v>
       </c>
+      <c r="AR122" t="n">
+        <v>20.97711753845215</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -17161,6 +17529,9 @@
       <c r="AQ123" t="n">
         <v>21.16396331787109</v>
       </c>
+      <c r="AR123" t="n">
+        <v>21.23835182189941</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17298,6 +17669,9 @@
       <c r="AQ124" t="n">
         <v>21.69884300231934</v>
       </c>
+      <c r="AR124" t="n">
+        <v>21.79372596740723</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17435,6 +17809,9 @@
       <c r="AQ125" t="n">
         <v>22.07812690734863</v>
       </c>
+      <c r="AR125" t="n">
+        <v>22.14472961425781</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17572,6 +17949,9 @@
       <c r="AQ126" t="n">
         <v>22.37998962402344</v>
       </c>
+      <c r="AR126" t="n">
+        <v>22.43406677246094</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17709,6 +18089,9 @@
       <c r="AQ127" t="n">
         <v>22.65036010742188</v>
       </c>
+      <c r="AR127" t="n">
+        <v>22.68891143798828</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17846,6 +18229,9 @@
       <c r="AQ128" t="n">
         <v>22.84718894958496</v>
       </c>
+      <c r="AR128" t="n">
+        <v>22.94872856140137</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17983,6 +18369,9 @@
       <c r="AQ129" t="n">
         <v>23.06948471069336</v>
       </c>
+      <c r="AR129" t="n">
+        <v>23.1647834777832</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -18122,6 +18511,9 @@
       <c r="AQ130" t="n">
         <v>21.49900245666504</v>
       </c>
+      <c r="AR130" t="n">
+        <v>21.59270668029785</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -18259,6 +18651,9 @@
       <c r="AQ131" t="n">
         <v>21.66473197937012</v>
       </c>
+      <c r="AR131" t="n">
+        <v>21.71119689941406</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18398,6 +18793,9 @@
       <c r="AQ132" t="n">
         <v>21.91749954223633</v>
       </c>
+      <c r="AR132" t="n">
+        <v>21.96151161193848</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18537,6 +18935,9 @@
       <c r="AQ133" t="n">
         <v>22.49143981933594</v>
       </c>
+      <c r="AR133" t="n">
+        <v>22.61440467834473</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18674,6 +19075,9 @@
       <c r="AQ134" t="n">
         <v>22.97998428344727</v>
       </c>
+      <c r="AR134" t="n">
+        <v>23.17134094238281</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18811,6 +19215,9 @@
       <c r="AQ135" t="n">
         <v>23.3029670715332</v>
       </c>
+      <c r="AR135" t="n">
+        <v>23.48544692993164</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18948,6 +19355,9 @@
       <c r="AQ136" t="n">
         <v>23.73383331298828</v>
       </c>
+      <c r="AR136" t="n">
+        <v>23.88263702392578</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -19085,6 +19495,9 @@
       <c r="AQ137" t="n">
         <v>26.24082374572754</v>
       </c>
+      <c r="AR137" t="n">
+        <v>26.1425952911377</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -19222,6 +19635,9 @@
       <c r="AQ138" t="n">
         <v>29.25329399108887</v>
       </c>
+      <c r="AR138" t="n">
+        <v>29.11562538146973</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -19359,6 +19775,9 @@
       <c r="AQ139" t="n">
         <v>30.24240303039551</v>
       </c>
+      <c r="AR139" t="n">
+        <v>30.26792907714844</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19496,6 +19915,9 @@
       <c r="AQ140" t="n">
         <v>30.51158142089844</v>
       </c>
+      <c r="AR140" t="n">
+        <v>30.50845718383789</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19631,6 +20053,9 @@
       <c r="AQ141" t="n">
         <v>30.59122848510742</v>
       </c>
+      <c r="AR141" t="n">
+        <v>30.57632637023926</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19768,6 +20193,9 @@
       <c r="AQ142" t="n">
         <v>20.99753570556641</v>
       </c>
+      <c r="AR142" t="n">
+        <v>19.84826278686523</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -19905,6 +20333,9 @@
       <c r="AQ143" t="n">
         <v>20.99753570556641</v>
       </c>
+      <c r="AR143" t="n">
+        <v>19.84826278686523</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -20044,6 +20475,9 @@
       <c r="AQ144" t="n">
         <v>21.2316951751709</v>
       </c>
+      <c r="AR144" t="n">
+        <v>20.17424964904785</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -20183,6 +20617,9 @@
       <c r="AQ145" t="n">
         <v>21.65328788757324</v>
       </c>
+      <c r="AR145" t="n">
+        <v>20.78697967529297</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -20320,6 +20757,9 @@
       <c r="AQ146" t="n">
         <v>22.34049415588379</v>
       </c>
+      <c r="AR146" t="n">
+        <v>22.16703987121582</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -20457,6 +20897,9 @@
       <c r="AQ147" t="n">
         <v>22.76232528686523</v>
       </c>
+      <c r="AR147" t="n">
+        <v>22.6712818145752</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -20594,6 +21037,9 @@
       <c r="AQ148" t="n">
         <v>23.12858772277832</v>
       </c>
+      <c r="AR148" t="n">
+        <v>23.04530143737793</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -20731,6 +21177,9 @@
       <c r="AQ149" t="n">
         <v>23.64399337768555</v>
       </c>
+      <c r="AR149" t="n">
+        <v>23.73536109924316</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -20868,6 +21317,9 @@
       <c r="AQ150" t="n">
         <v>25.9908275604248</v>
       </c>
+      <c r="AR150" t="n">
+        <v>26.29140853881836</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -21005,6 +21457,9 @@
       <c r="AQ151" t="n">
         <v>28.84749412536621</v>
       </c>
+      <c r="AR151" t="n">
+        <v>28.98785018920898</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -21142,6 +21597,9 @@
       <c r="AQ152" t="n">
         <v>30.91207885742188</v>
       </c>
+      <c r="AR152" t="n">
+        <v>30.92365074157715</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -21279,6 +21737,9 @@
       <c r="AQ153" t="n">
         <v>31.43169975280762</v>
       </c>
+      <c r="AR153" t="n">
+        <v>31.40225028991699</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -21414,6 +21875,9 @@
       <c r="AQ154" t="n">
         <v>31.52877426147461</v>
       </c>
+      <c r="AR154" t="n">
+        <v>31.50172424316406</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -21549,6 +22013,9 @@
       <c r="AQ155" t="n">
         <v>31.52877426147461</v>
       </c>
+      <c r="AR155" t="n">
+        <v>31.50172424316406</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -21688,6 +22155,9 @@
       <c r="AQ156" t="n">
         <v>20.36337852478027</v>
       </c>
+      <c r="AR156" t="n">
+        <v>20.45420265197754</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -21825,6 +22295,9 @@
       <c r="AQ157" t="n">
         <v>20.5545825958252</v>
       </c>
+      <c r="AR157" t="n">
+        <v>20.61775207519531</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -21964,6 +22437,9 @@
       <c r="AQ158" t="n">
         <v>20.8983211517334</v>
       </c>
+      <c r="AR158" t="n">
+        <v>20.91645622253418</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -22103,6 +22579,9 @@
       <c r="AQ159" t="n">
         <v>21.50336456298828</v>
       </c>
+      <c r="AR159" t="n">
+        <v>21.58509826660156</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -22240,6 +22719,9 @@
       <c r="AQ160" t="n">
         <v>22.07012939453125</v>
       </c>
+      <c r="AR160" t="n">
+        <v>22.19605827331543</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -22371,6 +22853,9 @@
       <c r="AQ161" t="n">
         <v>23.15775871276855</v>
       </c>
+      <c r="AR161" t="n">
+        <v>23.31867027282715</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -22508,6 +22993,9 @@
       <c r="AQ162" t="n">
         <v>24.20733642578125</v>
       </c>
+      <c r="AR162" t="n">
+        <v>24.36017799377441</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -22645,6 +23133,9 @@
       <c r="AQ163" t="n">
         <v>26.51087760925293</v>
       </c>
+      <c r="AR163" t="n">
+        <v>26.63624000549316</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -22782,6 +23273,9 @@
       <c r="AQ164" t="n">
         <v>27.60127449035645</v>
       </c>
+      <c r="AR164" t="n">
+        <v>27.59258079528809</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -22915,6 +23409,9 @@
       <c r="AQ165" t="n">
         <v>27.67102432250977</v>
       </c>
+      <c r="AR165" t="n">
+        <v>27.70675849914551</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -23054,6 +23551,9 @@
       <c r="AQ166" t="n">
         <v>19.62225914001465</v>
       </c>
+      <c r="AR166" t="n">
+        <v>19.76165962219238</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -23191,6 +23691,9 @@
       <c r="AQ167" t="n">
         <v>19.66095733642578</v>
       </c>
+      <c r="AR167" t="n">
+        <v>19.80722808837891</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -23330,6 +23833,9 @@
       <c r="AQ168" t="n">
         <v>19.7941780090332</v>
       </c>
+      <c r="AR168" t="n">
+        <v>19.96520614624023</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -23469,6 +23975,9 @@
       <c r="AQ169" t="n">
         <v>20.51756477355957</v>
       </c>
+      <c r="AR169" t="n">
+        <v>20.64373397827148</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -23606,6 +24115,9 @@
       <c r="AQ170" t="n">
         <v>21.44605445861816</v>
       </c>
+      <c r="AR170" t="n">
+        <v>21.61241340637207</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -23743,6 +24255,9 @@
       <c r="AQ171" t="n">
         <v>22.34055519104004</v>
       </c>
+      <c r="AR171" t="n">
+        <v>22.4568042755127</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -23880,6 +24395,9 @@
       <c r="AQ172" t="n">
         <v>23.03812408447266</v>
       </c>
+      <c r="AR172" t="n">
+        <v>23.15120124816895</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -24017,6 +24535,9 @@
       <c r="AQ173" t="n">
         <v>25.35152816772461</v>
       </c>
+      <c r="AR173" t="n">
+        <v>25.381591796875</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -24154,6 +24675,9 @@
       <c r="AQ174" t="n">
         <v>26.70055389404297</v>
       </c>
+      <c r="AR174" t="n">
+        <v>26.74572563171387</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -24291,6 +24815,9 @@
       <c r="AQ175" t="n">
         <v>27.00031280517578</v>
       </c>
+      <c r="AR175" t="n">
+        <v>27.03853988647461</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -24430,6 +24957,9 @@
       <c r="AQ176" t="n">
         <v>20.63822937011719</v>
       </c>
+      <c r="AR176" t="n">
+        <v>20.77776527404785</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -24567,6 +25097,9 @@
       <c r="AQ177" t="n">
         <v>20.6913890838623</v>
       </c>
+      <c r="AR177" t="n">
+        <v>20.83094215393066</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -24706,6 +25239,9 @@
       <c r="AQ178" t="n">
         <v>20.77734565734863</v>
       </c>
+      <c r="AR178" t="n">
+        <v>20.95253372192383</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -24845,6 +25381,9 @@
       <c r="AQ179" t="n">
         <v>21.00918579101562</v>
       </c>
+      <c r="AR179" t="n">
+        <v>21.19582366943359</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -24982,6 +25521,9 @@
       <c r="AQ180" t="n">
         <v>21.16812515258789</v>
       </c>
+      <c r="AR180" t="n">
+        <v>21.36877059936523</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -25119,6 +25661,9 @@
       <c r="AQ181" t="n">
         <v>21.33024406433105</v>
       </c>
+      <c r="AR181" t="n">
+        <v>21.51827812194824</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -25256,6 +25801,9 @@
       <c r="AQ182" t="n">
         <v>21.47179412841797</v>
       </c>
+      <c r="AR182" t="n">
+        <v>21.63014602661133</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -25393,6 +25941,9 @@
       <c r="AQ183" t="n">
         <v>21.69080924987793</v>
       </c>
+      <c r="AR183" t="n">
+        <v>21.81686210632324</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -25530,6 +26081,9 @@
       <c r="AQ184" t="n">
         <v>21.96330642700195</v>
       </c>
+      <c r="AR184" t="n">
+        <v>22.10865783691406</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -25667,6 +26221,9 @@
       <c r="AQ185" t="n">
         <v>22.1417293548584</v>
       </c>
+      <c r="AR185" t="n">
+        <v>22.27150917053223</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -25798,6 +26355,9 @@
       <c r="AQ186" t="n">
         <v>22.31901741027832</v>
       </c>
+      <c r="AR186" t="n">
+        <v>22.44016647338867</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -25935,6 +26495,9 @@
       <c r="AQ187" t="n">
         <v>22.45622634887695</v>
       </c>
+      <c r="AR187" t="n">
+        <v>22.53686714172363</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -26070,6 +26633,9 @@
       <c r="AQ188" t="n">
         <v>22.48510932922363</v>
       </c>
+      <c r="AR188" t="n">
+        <v>22.55825042724609</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -26209,6 +26775,9 @@
       <c r="AQ189" t="n">
         <v>18.58720207214355</v>
       </c>
+      <c r="AR189" t="n">
+        <v>19.06708526611328</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -26346,6 +26915,9 @@
       <c r="AQ190" t="n">
         <v>18.80278778076172</v>
       </c>
+      <c r="AR190" t="n">
+        <v>19.08579444885254</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -26485,6 +27057,9 @@
       <c r="AQ191" t="n">
         <v>19.65059089660645</v>
       </c>
+      <c r="AR191" t="n">
+        <v>19.74838066101074</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -26624,6 +27199,9 @@
       <c r="AQ192" t="n">
         <v>20.81158256530762</v>
       </c>
+      <c r="AR192" t="n">
+        <v>21.35251998901367</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -26761,6 +27339,9 @@
       <c r="AQ193" t="n">
         <v>21.39556884765625</v>
       </c>
+      <c r="AR193" t="n">
+        <v>21.82449531555176</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -26898,6 +27479,9 @@
       <c r="AQ194" t="n">
         <v>21.94051933288574</v>
       </c>
+      <c r="AR194" t="n">
+        <v>22.11066627502441</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -27035,6 +27619,9 @@
       <c r="AQ195" t="n">
         <v>22.28800964355469</v>
       </c>
+      <c r="AR195" t="n">
+        <v>22.31545066833496</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -27172,6 +27759,9 @@
       <c r="AQ196" t="n">
         <v>22.92724418640137</v>
       </c>
+      <c r="AR196" t="n">
+        <v>22.93797874450684</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -27309,6 +27899,9 @@
       <c r="AQ197" t="n">
         <v>23.67417335510254</v>
       </c>
+      <c r="AR197" t="n">
+        <v>23.91695022583008</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -27446,6 +28039,9 @@
       <c r="AQ198" t="n">
         <v>24.85447311401367</v>
       </c>
+      <c r="AR198" t="n">
+        <v>25.14284706115723</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -27583,6 +28179,9 @@
       <c r="AQ199" t="n">
         <v>26.24236679077148</v>
       </c>
+      <c r="AR199" t="n">
+        <v>26.48683738708496</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -27718,6 +28317,9 @@
       <c r="AQ200" t="n">
         <v>26.66815376281738</v>
       </c>
+      <c r="AR200" t="n">
+        <v>26.8785285949707</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -27857,6 +28459,9 @@
       <c r="AQ201" t="n">
         <v>10.39869117736816</v>
       </c>
+      <c r="AR201" t="n">
+        <v>10.86268138885498</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -27994,6 +28599,9 @@
       <c r="AQ202" t="n">
         <v>10.61744785308838</v>
       </c>
+      <c r="AR202" t="n">
+        <v>10.89494037628174</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -28133,6 +28741,9 @@
       <c r="AQ203" t="n">
         <v>13.29244327545166</v>
       </c>
+      <c r="AR203" t="n">
+        <v>17.23537445068359</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -28272,6 +28883,9 @@
       <c r="AQ204" t="n">
         <v>23.46282005310059</v>
       </c>
+      <c r="AR204" t="n">
+        <v>23.75841331481934</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -28409,6 +29023,9 @@
       <c r="AQ205" t="n">
         <v>24.93439483642578</v>
       </c>
+      <c r="AR205" t="n">
+        <v>26.01395988464355</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -28546,6 +29163,9 @@
       <c r="AQ206" t="n">
         <v>25.15958786010742</v>
       </c>
+      <c r="AR206" t="n">
+        <v>26.16933059692383</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -28683,6 +29303,9 @@
       <c r="AQ207" t="n">
         <v>24.68145179748535</v>
       </c>
+      <c r="AR207" t="n">
+        <v>25.94502449035645</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -28820,6 +29443,9 @@
       <c r="AQ208" t="n">
         <v>23.91292572021484</v>
       </c>
+      <c r="AR208" t="n">
+        <v>24.92868995666504</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -28957,6 +29583,9 @@
       <c r="AQ209" t="n">
         <v>25.0840015411377</v>
       </c>
+      <c r="AR209" t="n">
+        <v>25.28367042541504</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -29094,6 +29723,9 @@
       <c r="AQ210" t="n">
         <v>26.19154167175293</v>
       </c>
+      <c r="AR210" t="n">
+        <v>26.1038990020752</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -29231,6 +29863,9 @@
       <c r="AQ211" t="n">
         <v>26.68475532531738</v>
       </c>
+      <c r="AR211" t="n">
+        <v>26.71178817749023</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -29366,6 +30001,9 @@
       <c r="AQ212" t="n">
         <v>27.39163970947266</v>
       </c>
+      <c r="AR212" t="n">
+        <v>27.4033031463623</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -29503,6 +30141,9 @@
       <c r="AQ213" t="n">
         <v>27.90624618530273</v>
       </c>
+      <c r="AR213" t="n">
+        <v>28.08604431152344</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -29640,6 +30281,9 @@
       <c r="AQ214" t="n">
         <v>28.46711540222168</v>
       </c>
+      <c r="AR214" t="n">
+        <v>28.61275672912598</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -29777,6 +30421,9 @@
       <c r="AQ215" t="n">
         <v>28.70810699462891</v>
       </c>
+      <c r="AR215" t="n">
+        <v>28.80655097961426</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -29912,6 +30559,9 @@
       <c r="AQ216" t="n">
         <v>28.73069000244141</v>
       </c>
+      <c r="AR216" t="n">
+        <v>28.82231521606445</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -30051,6 +30701,9 @@
       <c r="AQ217" t="n">
         <v>17.93804550170898</v>
       </c>
+      <c r="AR217" t="n">
+        <v>19.73898506164551</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -30188,6 +30841,9 @@
       <c r="AQ218" t="n">
         <v>19.88368797302246</v>
       </c>
+      <c r="AR218" t="n">
+        <v>20.83019638061523</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -30327,6 +30983,9 @@
       <c r="AQ219" t="n">
         <v>20.81304550170898</v>
       </c>
+      <c r="AR219" t="n">
+        <v>21.66334342956543</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -30466,6 +31125,9 @@
       <c r="AQ220" t="n">
         <v>23.39485740661621</v>
       </c>
+      <c r="AR220" t="n">
+        <v>22.94942283630371</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -30597,6 +31259,9 @@
       <c r="AQ221" t="n">
         <v>25.65460968017578</v>
       </c>
+      <c r="AR221" t="n">
+        <v>25.15693283081055</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -30734,6 +31399,9 @@
       <c r="AQ222" t="n">
         <v>26.42144584655762</v>
       </c>
+      <c r="AR222" t="n">
+        <v>26.29336547851562</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -30865,6 +31533,9 @@
       <c r="AQ223" t="n">
         <v>26.91451263427734</v>
       </c>
+      <c r="AR223" t="n">
+        <v>26.84167098999023</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -31002,6 +31673,9 @@
       <c r="AQ224" t="n">
         <v>26.88815307617188</v>
       </c>
+      <c r="AR224" t="n">
+        <v>26.94168853759766</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -31139,6 +31813,9 @@
       <c r="AQ225" t="n">
         <v>26.68624305725098</v>
       </c>
+      <c r="AR225" t="n">
+        <v>26.62338066101074</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -31276,6 +31953,9 @@
       <c r="AQ226" t="n">
         <v>26.4976921081543</v>
       </c>
+      <c r="AR226" t="n">
+        <v>26.45084571838379</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -31413,6 +32093,9 @@
       <c r="AQ227" t="n">
         <v>26.87140464782715</v>
       </c>
+      <c r="AR227" t="n">
+        <v>26.81219100952148</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -31550,6 +32233,9 @@
       <c r="AQ228" t="n">
         <v>27.08657073974609</v>
       </c>
+      <c r="AR228" t="n">
+        <v>27.05036163330078</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -31687,6 +32373,9 @@
       <c r="AQ229" t="n">
         <v>27.22974395751953</v>
       </c>
+      <c r="AR229" t="n">
+        <v>27.25403022766113</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -31824,6 +32513,9 @@
       <c r="AQ230" t="n">
         <v>28.10054206848145</v>
       </c>
+      <c r="AR230" t="n">
+        <v>27.85015869140625</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -31961,6 +32653,9 @@
       <c r="AQ231" t="n">
         <v>28.75100898742676</v>
       </c>
+      <c r="AR231" t="n">
+        <v>28.75038146972656</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -32098,6 +32793,9 @@
       <c r="AQ232" t="n">
         <v>28.92733383178711</v>
       </c>
+      <c r="AR232" t="n">
+        <v>28.93895530700684</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -32232,6 +32930,9 @@
       </c>
       <c r="AQ233" t="n">
         <v>28.93276786804199</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>28.94395065307617</v>
       </c>
     </row>
     <row r="234">
@@ -32358,6 +33059,9 @@
       <c r="AQ234" t="n">
         <v>8.281889915466309</v>
       </c>
+      <c r="AR234" t="n">
+        <v>7.085296630859375</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -32483,6 +33187,9 @@
       <c r="AQ235" t="n">
         <v>19.55489158630371</v>
       </c>
+      <c r="AR235" t="n">
+        <v>17.5417366027832</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -32608,6 +33315,9 @@
       <c r="AQ236" t="n">
         <v>23.53064346313477</v>
       </c>
+      <c r="AR236" t="n">
+        <v>25.04595947265625</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -32747,6 +33457,9 @@
       <c r="AQ237" t="n">
         <v>9.333398818969727</v>
       </c>
+      <c r="AR237" t="n">
+        <v>6.17535924911499</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -32884,6 +33597,9 @@
       <c r="AQ238" t="n">
         <v>10.81204605102539</v>
       </c>
+      <c r="AR238" t="n">
+        <v>6.308191299438477</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -33023,6 +33739,9 @@
       <c r="AQ239" t="n">
         <v>15.10553932189941</v>
       </c>
+      <c r="AR239" t="n">
+        <v>7.66474437713623</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -33162,6 +33881,9 @@
       <c r="AQ240" t="n">
         <v>24.05141830444336</v>
       </c>
+      <c r="AR240" t="n">
+        <v>22.06073570251465</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -33299,6 +34021,9 @@
       <c r="AQ241" t="n">
         <v>26.69393539428711</v>
       </c>
+      <c r="AR241" t="n">
+        <v>25.18575668334961</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -33436,6 +34161,9 @@
       <c r="AQ242" t="n">
         <v>27.26567840576172</v>
       </c>
+      <c r="AR242" t="n">
+        <v>26.61536026000977</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -33573,6 +34301,9 @@
       <c r="AQ243" t="n">
         <v>27.37546539306641</v>
       </c>
+      <c r="AR243" t="n">
+        <v>27.26764297485352</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -33710,6 +34441,9 @@
       <c r="AQ244" t="n">
         <v>27.17772674560547</v>
       </c>
+      <c r="AR244" t="n">
+        <v>27.38669586181641</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -33847,6 +34581,9 @@
       <c r="AQ245" t="n">
         <v>26.88192749023438</v>
       </c>
+      <c r="AR245" t="n">
+        <v>27.23006057739258</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -33984,6 +34721,9 @@
       <c r="AQ246" t="n">
         <v>26.95013236999512</v>
       </c>
+      <c r="AR246" t="n">
+        <v>27.35849571228027</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -34121,6 +34861,9 @@
       <c r="AQ247" t="n">
         <v>27.1968994140625</v>
       </c>
+      <c r="AR247" t="n">
+        <v>27.62787437438965</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -34258,6 +35001,9 @@
       <c r="AQ248" t="n">
         <v>27.80367279052734</v>
       </c>
+      <c r="AR248" t="n">
+        <v>28.23693656921387</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -34395,6 +35141,9 @@
       <c r="AQ249" t="n">
         <v>28.54760932922363</v>
       </c>
+      <c r="AR249" t="n">
+        <v>28.6979808807373</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -34532,6 +35281,9 @@
       <c r="AQ250" t="n">
         <v>28.95224571228027</v>
       </c>
+      <c r="AR250" t="n">
+        <v>28.9337329864502</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -34669,6 +35421,9 @@
       <c r="AQ251" t="n">
         <v>28.96767234802246</v>
       </c>
+      <c r="AR251" t="n">
+        <v>28.95605278015137</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -34806,6 +35561,9 @@
       <c r="AQ252" t="n">
         <v>28.95707321166992</v>
       </c>
+      <c r="AR252" t="n">
+        <v>28.9558048248291</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -34939,6 +35697,9 @@
       <c r="AQ253" t="n">
         <v>9.265677452087402</v>
       </c>
+      <c r="AR253" t="n">
+        <v>5.115707874298096</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -35072,6 +35833,9 @@
       <c r="AQ254" t="n">
         <v>15.26477527618408</v>
       </c>
+      <c r="AR254" t="n">
+        <v>9.41081714630127</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -35205,6 +35969,9 @@
       <c r="AQ255" t="n">
         <v>21.39492416381836</v>
       </c>
+      <c r="AR255" t="n">
+        <v>20.47307205200195</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -35344,6 +36111,9 @@
       <c r="AQ256" t="n">
         <v>13.58145523071289</v>
       </c>
+      <c r="AR256" t="n">
+        <v>9.162424087524414</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -35481,6 +36251,9 @@
       <c r="AQ257" t="n">
         <v>15.59268665313721</v>
       </c>
+      <c r="AR257" t="n">
+        <v>14.10024452209473</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -35620,6 +36393,9 @@
       <c r="AQ258" t="n">
         <v>17.70902442932129</v>
       </c>
+      <c r="AR258" t="n">
+        <v>20.58547973632812</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -35759,6 +36535,9 @@
       <c r="AQ259" t="n">
         <v>21.66425514221191</v>
       </c>
+      <c r="AR259" t="n">
+        <v>22.7480525970459</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -35896,6 +36675,9 @@
       <c r="AQ260" t="n">
         <v>24.70704078674316</v>
       </c>
+      <c r="AR260" t="n">
+        <v>23.88590812683105</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -36033,6 +36815,9 @@
       <c r="AQ261" t="n">
         <v>26.6652717590332</v>
       </c>
+      <c r="AR261" t="n">
+        <v>26.06771087646484</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -36170,6 +36955,9 @@
       <c r="AQ262" t="n">
         <v>27.64896392822266</v>
       </c>
+      <c r="AR262" t="n">
+        <v>27.49083137512207</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -36307,6 +37095,9 @@
       <c r="AQ263" t="n">
         <v>27.86395835876465</v>
       </c>
+      <c r="AR263" t="n">
+        <v>27.93557548522949</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -36444,6 +37235,9 @@
       <c r="AQ264" t="n">
         <v>27.66209983825684</v>
       </c>
+      <c r="AR264" t="n">
+        <v>27.69440460205078</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -36577,6 +37371,9 @@
       <c r="AQ265" t="n">
         <v>27.65321159362793</v>
       </c>
+      <c r="AR265" t="n">
+        <v>27.60641860961914</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -36714,6 +37511,9 @@
       <c r="AQ266" t="n">
         <v>27.88377952575684</v>
       </c>
+      <c r="AR266" t="n">
+        <v>27.97199821472168</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -36851,6 +37651,9 @@
       <c r="AQ267" t="n">
         <v>28.0670108795166</v>
       </c>
+      <c r="AR267" t="n">
+        <v>28.26223564147949</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -36988,6 +37791,9 @@
       <c r="AQ268" t="n">
         <v>28.5823917388916</v>
       </c>
+      <c r="AR268" t="n">
+        <v>28.57455635070801</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -37125,6 +37931,9 @@
       <c r="AQ269" t="n">
         <v>28.95543670654297</v>
       </c>
+      <c r="AR269" t="n">
+        <v>28.93342208862305</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -37262,6 +38071,9 @@
       <c r="AQ270" t="n">
         <v>28.99483489990234</v>
       </c>
+      <c r="AR270" t="n">
+        <v>28.98138236999512</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -37393,6 +38205,9 @@
       <c r="AQ271" t="n">
         <v>6.212727069854736</v>
       </c>
+      <c r="AR271" t="n">
+        <v>6.440130233764648</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -37524,6 +38339,9 @@
       <c r="AQ272" t="n">
         <v>8.400172233581543</v>
       </c>
+      <c r="AR272" t="n">
+        <v>8.592650413513184</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -37655,6 +38473,9 @@
       <c r="AQ273" t="n">
         <v>9.904959678649902</v>
       </c>
+      <c r="AR273" t="n">
+        <v>9.970112800598145</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -37788,6 +38609,9 @@
       <c r="AQ274" t="n">
         <v>17.74823188781738</v>
       </c>
+      <c r="AR274" t="n">
+        <v>16.80356407165527</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -37921,6 +38745,9 @@
       <c r="AQ275" t="n">
         <v>17.74395179748535</v>
       </c>
+      <c r="AR275" t="n">
+        <v>17.39723777770996</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -38054,6 +38881,9 @@
       <c r="AQ276" t="n">
         <v>19.35729598999023</v>
       </c>
+      <c r="AR276" t="n">
+        <v>19.20693206787109</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -38193,6 +39023,9 @@
       <c r="AQ277" t="n">
         <v>21.39465713500977</v>
       </c>
+      <c r="AR277" t="n">
+        <v>21.07559394836426</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -38328,6 +39161,9 @@
       <c r="AQ278" t="n">
         <v>21.49865913391113</v>
       </c>
+      <c r="AR278" t="n">
+        <v>20.90409088134766</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -38467,6 +39303,9 @@
       <c r="AQ279" t="n">
         <v>21.75945091247559</v>
       </c>
+      <c r="AR279" t="n">
+        <v>21.10702896118164</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -38604,6 +39443,9 @@
       <c r="AQ280" t="n">
         <v>22.24102973937988</v>
       </c>
+      <c r="AR280" t="n">
+        <v>22.11010360717773</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -38741,6 +39583,9 @@
       <c r="AQ281" t="n">
         <v>22.64977645874023</v>
       </c>
+      <c r="AR281" t="n">
+        <v>22.80722999572754</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -38878,6 +39723,9 @@
       <c r="AQ282" t="n">
         <v>23.11606216430664</v>
       </c>
+      <c r="AR282" t="n">
+        <v>23.3430347442627</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -39015,6 +39863,9 @@
       <c r="AQ283" t="n">
         <v>23.63935089111328</v>
       </c>
+      <c r="AR283" t="n">
+        <v>23.90115165710449</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -39152,6 +40003,9 @@
       <c r="AQ284" t="n">
         <v>25.32576370239258</v>
       </c>
+      <c r="AR284" t="n">
+        <v>25.30307960510254</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -39289,6 +40143,9 @@
       <c r="AQ285" t="n">
         <v>26.34713554382324</v>
       </c>
+      <c r="AR285" t="n">
+        <v>26.27021408081055</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -39426,6 +40283,9 @@
       <c r="AQ286" t="n">
         <v>27.6147575378418</v>
       </c>
+      <c r="AR286" t="n">
+        <v>27.59025764465332</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -39561,6 +40421,9 @@
       <c r="AQ287" t="n">
         <v>28.15756225585938</v>
       </c>
+      <c r="AR287" t="n">
+        <v>28.12608909606934</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -39700,6 +40563,9 @@
       <c r="AQ288" t="n">
         <v>21.02042770385742</v>
       </c>
+      <c r="AR288" t="n">
+        <v>18.41376113891602</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -39837,6 +40703,9 @@
       <c r="AQ289" t="n">
         <v>21.05565452575684</v>
       </c>
+      <c r="AR289" t="n">
+        <v>19.10119438171387</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -39976,6 +40845,9 @@
       <c r="AQ290" t="n">
         <v>21.13389015197754</v>
       </c>
+      <c r="AR290" t="n">
+        <v>20.28373908996582</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -40115,6 +40987,9 @@
       <c r="AQ291" t="n">
         <v>21.6538028717041</v>
       </c>
+      <c r="AR291" t="n">
+        <v>21.69460105895996</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -40252,6 +41127,9 @@
       <c r="AQ292" t="n">
         <v>22.43695259094238</v>
       </c>
+      <c r="AR292" t="n">
+        <v>22.65316009521484</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -40387,6 +41265,9 @@
       <c r="AQ293" t="n">
         <v>23.15833282470703</v>
       </c>
+      <c r="AR293" t="n">
+        <v>23.01544761657715</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -40524,6 +41405,9 @@
       <c r="AQ294" t="n">
         <v>23.67590713500977</v>
       </c>
+      <c r="AR294" t="n">
+        <v>23.40873527526855</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -40661,6 +41545,9 @@
       <c r="AQ295" t="n">
         <v>25.21731948852539</v>
       </c>
+      <c r="AR295" t="n">
+        <v>25.20565605163574</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -40798,6 +41685,9 @@
       <c r="AQ296" t="n">
         <v>27.73063468933105</v>
       </c>
+      <c r="AR296" t="n">
+        <v>27.77385520935059</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -40935,6 +41825,9 @@
       <c r="AQ297" t="n">
         <v>28.43346405029297</v>
       </c>
+      <c r="AR297" t="n">
+        <v>28.53417778015137</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -41072,6 +41965,9 @@
       <c r="AQ298" t="n">
         <v>28.53670501708984</v>
       </c>
+      <c r="AR298" t="n">
+        <v>28.68112564086914</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -41209,6 +42105,9 @@
       <c r="AQ299" t="n">
         <v>28.61967086791992</v>
       </c>
+      <c r="AR299" t="n">
+        <v>28.69084739685059</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -41346,6 +42245,9 @@
       <c r="AQ300" t="n">
         <v>28.69346046447754</v>
       </c>
+      <c r="AR300" t="n">
+        <v>28.73892211914062</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -41483,6 +42385,9 @@
       <c r="AQ301" t="n">
         <v>28.81461715698242</v>
       </c>
+      <c r="AR301" t="n">
+        <v>28.81305503845215</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -41618,6 +42523,9 @@
       <c r="AQ302" t="n">
         <v>28.87404632568359</v>
       </c>
+      <c r="AR302" t="n">
+        <v>28.86668968200684</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -41757,6 +42665,9 @@
       <c r="AQ303" t="n">
         <v>15.12353038787842</v>
       </c>
+      <c r="AR303" t="n">
+        <v>14.45601177215576</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -41894,6 +42805,9 @@
       <c r="AQ304" t="n">
         <v>15.59210205078125</v>
       </c>
+      <c r="AR304" t="n">
+        <v>15.16129684448242</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -42033,6 +42947,9 @@
       <c r="AQ305" t="n">
         <v>16.80072784423828</v>
       </c>
+      <c r="AR305" t="n">
+        <v>16.3108959197998</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -42172,6 +43089,9 @@
       <c r="AQ306" t="n">
         <v>18.2678165435791</v>
       </c>
+      <c r="AR306" t="n">
+        <v>17.21743202209473</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -42309,6 +43229,9 @@
       <c r="AQ307" t="n">
         <v>19.83960342407227</v>
       </c>
+      <c r="AR307" t="n">
+        <v>19.64093399047852</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -42446,6 +43369,9 @@
       <c r="AQ308" t="n">
         <v>23.61900901794434</v>
       </c>
+      <c r="AR308" t="n">
+        <v>23.6927490234375</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -42583,6 +43509,9 @@
       <c r="AQ309" t="n">
         <v>25.39970588684082</v>
       </c>
+      <c r="AR309" t="n">
+        <v>26.32199859619141</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -42720,6 +43649,9 @@
       <c r="AQ310" t="n">
         <v>27.29756927490234</v>
       </c>
+      <c r="AR310" t="n">
+        <v>27.8627872467041</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -42857,6 +43789,9 @@
       <c r="AQ311" t="n">
         <v>27.7185230255127</v>
       </c>
+      <c r="AR311" t="n">
+        <v>28.08577156066895</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -42994,6 +43929,9 @@
       <c r="AQ312" t="n">
         <v>28.11559104919434</v>
       </c>
+      <c r="AR312" t="n">
+        <v>28.56172943115234</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -43131,6 +44069,9 @@
       <c r="AQ313" t="n">
         <v>28.48004341125488</v>
       </c>
+      <c r="AR313" t="n">
+        <v>28.6282958984375</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -43268,6 +44209,9 @@
       <c r="AQ314" t="n">
         <v>28.70376205444336</v>
       </c>
+      <c r="AR314" t="n">
+        <v>28.68697929382324</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -43405,6 +44349,9 @@
       <c r="AQ315" t="n">
         <v>28.7060489654541</v>
       </c>
+      <c r="AR315" t="n">
+        <v>28.70492172241211</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -43542,6 +44489,9 @@
       <c r="AQ316" t="n">
         <v>28.79061698913574</v>
       </c>
+      <c r="AR316" t="n">
+        <v>28.7951774597168</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -43679,6 +44629,9 @@
       <c r="AQ317" t="n">
         <v>28.93698120117188</v>
       </c>
+      <c r="AR317" t="n">
+        <v>28.94380378723145</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -43816,6 +44769,9 @@
       <c r="AQ318" t="n">
         <v>29.01161766052246</v>
       </c>
+      <c r="AR318" t="n">
+        <v>29.0140438079834</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -43955,6 +44911,9 @@
       <c r="AQ319" t="n">
         <v>19.76103973388672</v>
       </c>
+      <c r="AR319" t="n">
+        <v>18.96659469604492</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -44092,6 +45051,9 @@
       <c r="AQ320" t="n">
         <v>19.85703468322754</v>
       </c>
+      <c r="AR320" t="n">
+        <v>19.23771286010742</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -44231,6 +45193,9 @@
       <c r="AQ321" t="n">
         <v>20.55337905883789</v>
       </c>
+      <c r="AR321" t="n">
+        <v>20.20400238037109</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -44370,6 +45335,9 @@
       <c r="AQ322" t="n">
         <v>23.41160011291504</v>
       </c>
+      <c r="AR322" t="n">
+        <v>23.06835174560547</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -44507,6 +45475,9 @@
       <c r="AQ323" t="n">
         <v>24.28715133666992</v>
       </c>
+      <c r="AR323" t="n">
+        <v>24.6374454498291</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -44644,6 +45615,9 @@
       <c r="AQ324" t="n">
         <v>24.54206466674805</v>
       </c>
+      <c r="AR324" t="n">
+        <v>25.39281272888184</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -44781,6 +45755,9 @@
       <c r="AQ325" t="n">
         <v>24.90316390991211</v>
       </c>
+      <c r="AR325" t="n">
+        <v>26.07023048400879</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -44918,6 +45895,9 @@
       <c r="AQ326" t="n">
         <v>26.76376724243164</v>
       </c>
+      <c r="AR326" t="n">
+        <v>27.19024467468262</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -45055,6 +46035,9 @@
       <c r="AQ327" t="n">
         <v>27.78141593933105</v>
       </c>
+      <c r="AR327" t="n">
+        <v>27.94811058044434</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -45192,6 +46175,9 @@
       <c r="AQ328" t="n">
         <v>28.25734519958496</v>
       </c>
+      <c r="AR328" t="n">
+        <v>28.36277389526367</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -45329,6 +46315,9 @@
       <c r="AQ329" t="n">
         <v>28.73231315612793</v>
       </c>
+      <c r="AR329" t="n">
+        <v>28.70646667480469</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -45466,6 +46455,9 @@
       <c r="AQ330" t="n">
         <v>28.80237770080566</v>
       </c>
+      <c r="AR330" t="n">
+        <v>28.80977630615234</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -45605,6 +46597,9 @@
       <c r="AQ331" t="n">
         <v>21.30819320678711</v>
       </c>
+      <c r="AR331" t="n">
+        <v>18.87959861755371</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -45742,6 +46737,9 @@
       <c r="AQ332" t="n">
         <v>21.52836608886719</v>
       </c>
+      <c r="AR332" t="n">
+        <v>19.25693511962891</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -45881,6 +46879,9 @@
       <c r="AQ333" t="n">
         <v>22.06849479675293</v>
       </c>
+      <c r="AR333" t="n">
+        <v>20.2017765045166</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -46020,6 +47021,9 @@
       <c r="AQ334" t="n">
         <v>23.51060676574707</v>
       </c>
+      <c r="AR334" t="n">
+        <v>22.82941055297852</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -46157,6 +47161,9 @@
       <c r="AQ335" t="n">
         <v>25.19290733337402</v>
       </c>
+      <c r="AR335" t="n">
+        <v>24.53184700012207</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -46294,6 +47301,9 @@
       <c r="AQ336" t="n">
         <v>26.27070808410645</v>
       </c>
+      <c r="AR336" t="n">
+        <v>25.76028251647949</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -46431,6 +47441,9 @@
       <c r="AQ337" t="n">
         <v>26.85146903991699</v>
       </c>
+      <c r="AR337" t="n">
+        <v>26.27588844299316</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -46568,6 +47581,9 @@
       <c r="AQ338" t="n">
         <v>27.83628273010254</v>
       </c>
+      <c r="AR338" t="n">
+        <v>27.58823204040527</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -46705,6 +47721,9 @@
       <c r="AQ339" t="n">
         <v>28.26343154907227</v>
       </c>
+      <c r="AR339" t="n">
+        <v>28.1906623840332</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -46842,6 +47861,9 @@
       <c r="AQ340" t="n">
         <v>28.44806289672852</v>
       </c>
+      <c r="AR340" t="n">
+        <v>28.39788055419922</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -46979,6 +48001,9 @@
       <c r="AQ341" t="n">
         <v>28.63133430480957</v>
       </c>
+      <c r="AR341" t="n">
+        <v>28.59284400939941</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -47116,6 +48141,9 @@
       <c r="AQ342" t="n">
         <v>28.69498825073242</v>
       </c>
+      <c r="AR342" t="n">
+        <v>28.63343048095703</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -47253,6 +48281,9 @@
       <c r="AQ343" t="n">
         <v>28.65005683898926</v>
       </c>
+      <c r="AR343" t="n">
+        <v>28.59792518615723</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -47392,6 +48423,9 @@
       <c r="AQ344" t="n">
         <v>16.6060676574707</v>
       </c>
+      <c r="AR344" t="n">
+        <v>16.2004280090332</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -47529,6 +48563,9 @@
       <c r="AQ345" t="n">
         <v>17.06382179260254</v>
       </c>
+      <c r="AR345" t="n">
+        <v>17.1072883605957</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -47668,6 +48705,9 @@
       <c r="AQ346" t="n">
         <v>18.35939598083496</v>
       </c>
+      <c r="AR346" t="n">
+        <v>19.07699775695801</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -47807,6 +48847,9 @@
       <c r="AQ347" t="n">
         <v>21.87009239196777</v>
       </c>
+      <c r="AR347" t="n">
+        <v>24.07966423034668</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -47944,6 +48987,9 @@
       <c r="AQ348" t="n">
         <v>24.34609413146973</v>
       </c>
+      <c r="AR348" t="n">
+        <v>25.38030815124512</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -48081,6 +49127,9 @@
       <c r="AQ349" t="n">
         <v>26.26150894165039</v>
       </c>
+      <c r="AR349" t="n">
+        <v>26.28819274902344</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -48218,6 +49267,9 @@
       <c r="AQ350" t="n">
         <v>27.15086555480957</v>
       </c>
+      <c r="AR350" t="n">
+        <v>26.83244514465332</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -48355,6 +49407,9 @@
       <c r="AQ351" t="n">
         <v>27.89726638793945</v>
       </c>
+      <c r="AR351" t="n">
+        <v>27.88887786865234</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -48492,6 +49547,9 @@
       <c r="AQ352" t="n">
         <v>28.15860748291016</v>
       </c>
+      <c r="AR352" t="n">
+        <v>28.10621070861816</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -48629,6 +49687,9 @@
       <c r="AQ353" t="n">
         <v>28.08459281921387</v>
       </c>
+      <c r="AR353" t="n">
+        <v>27.95659637451172</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -48766,6 +49827,9 @@
       <c r="AQ354" t="n">
         <v>28.14052200317383</v>
       </c>
+      <c r="AR354" t="n">
+        <v>27.93139266967773</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -48903,6 +49967,9 @@
       <c r="AQ355" t="n">
         <v>28.56832313537598</v>
       </c>
+      <c r="AR355" t="n">
+        <v>28.43356895446777</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -49040,6 +50107,9 @@
       <c r="AQ356" t="n">
         <v>28.77165603637695</v>
       </c>
+      <c r="AR356" t="n">
+        <v>28.86938858032227</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -49177,6 +50247,9 @@
       <c r="AQ357" t="n">
         <v>29.00105476379395</v>
       </c>
+      <c r="AR357" t="n">
+        <v>29.00383949279785</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -49314,6 +50387,9 @@
       <c r="AQ358" t="n">
         <v>29.02371978759766</v>
       </c>
+      <c r="AR358" t="n">
+        <v>29.02508735656738</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -49449,6 +50525,9 @@
       <c r="AQ359" t="n">
         <v>29.02586364746094</v>
       </c>
+      <c r="AR359" t="n">
+        <v>29.02703094482422</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -49588,6 +50667,9 @@
       <c r="AQ360" t="n">
         <v>16.06431198120117</v>
       </c>
+      <c r="AR360" t="n">
+        <v>17.04874992370605</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -49725,6 +50807,9 @@
       <c r="AQ361" t="n">
         <v>19.26398277282715</v>
       </c>
+      <c r="AR361" t="n">
+        <v>20.09113883972168</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -49864,6 +50949,9 @@
       <c r="AQ362" t="n">
         <v>19.89260101318359</v>
       </c>
+      <c r="AR362" t="n">
+        <v>20.84122848510742</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -50003,6 +51091,9 @@
       <c r="AQ363" t="n">
         <v>21.24045944213867</v>
       </c>
+      <c r="AR363" t="n">
+        <v>22.10230827331543</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -50140,6 +51231,9 @@
       <c r="AQ364" t="n">
         <v>21.99817276000977</v>
       </c>
+      <c r="AR364" t="n">
+        <v>22.79217720031738</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -50277,6 +51371,9 @@
       <c r="AQ365" t="n">
         <v>22.59972190856934</v>
       </c>
+      <c r="AR365" t="n">
+        <v>23.39726066589355</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -50414,6 +51511,9 @@
       <c r="AQ366" t="n">
         <v>23.02152633666992</v>
       </c>
+      <c r="AR366" t="n">
+        <v>23.71831893920898</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -50548,6 +51648,9 @@
       </c>
       <c r="AQ367" t="n">
         <v>23.09042167663574</v>
+      </c>
+      <c r="AR367" t="n">
+        <v>23.74431991577148</v>
       </c>
     </row>
     <row r="368">
@@ -50668,6 +51771,9 @@
       <c r="AQ368" t="n">
         <v>14.13706874847412</v>
       </c>
+      <c r="AR368" t="n">
+        <v>15.52335357666016</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -50787,6 +51893,9 @@
       <c r="AQ369" t="n">
         <v>14.13706874847412</v>
       </c>
+      <c r="AR369" t="n">
+        <v>15.52335357666016</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -50906,6 +52015,9 @@
       <c r="AQ370" t="n">
         <v>14.13706874847412</v>
       </c>
+      <c r="AR370" t="n">
+        <v>15.52335357666016</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -51025,6 +52137,9 @@
       <c r="AQ371" t="n">
         <v>14.15426731109619</v>
       </c>
+      <c r="AR371" t="n">
+        <v>15.54142284393311</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -51144,6 +52259,9 @@
       <c r="AQ372" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR372" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -51263,6 +52381,9 @@
       <c r="AQ373" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR373" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -51382,6 +52503,9 @@
       <c r="AQ374" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR374" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -51501,6 +52625,9 @@
       <c r="AQ375" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR375" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -51620,6 +52747,9 @@
       <c r="AQ376" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR376" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -51739,6 +52869,9 @@
       <c r="AQ377" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR377" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -51858,6 +52991,9 @@
       <c r="AQ378" t="n">
         <v>14.17146587371826</v>
       </c>
+      <c r="AR378" t="n">
+        <v>15.55949306488037</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -51977,6 +53113,9 @@
       <c r="AQ379" t="n">
         <v>14.18866443634033</v>
       </c>
+      <c r="AR379" t="n">
+        <v>15.57756233215332</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -52116,6 +53255,9 @@
       <c r="AQ380" t="n">
         <v>9.604800224304199</v>
       </c>
+      <c r="AR380" t="n">
+        <v>10.70014667510986</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -52255,6 +53397,9 @@
       <c r="AQ381" t="n">
         <v>12.1819953918457</v>
       </c>
+      <c r="AR381" t="n">
+        <v>12.87887001037598</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -52394,6 +53539,9 @@
       <c r="AQ382" t="n">
         <v>13.88852596282959</v>
       </c>
+      <c r="AR382" t="n">
+        <v>14.41680145263672</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -52533,6 +53681,9 @@
       <c r="AQ383" t="n">
         <v>15.56790447235107</v>
       </c>
+      <c r="AR383" t="n">
+        <v>15.99544715881348</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -52672,6 +53823,9 @@
       <c r="AQ384" t="n">
         <v>17.05747222900391</v>
       </c>
+      <c r="AR384" t="n">
+        <v>17.0579662322998</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -52809,6 +53963,9 @@
       <c r="AQ385" t="n">
         <v>17.8901538848877</v>
       </c>
+      <c r="AR385" t="n">
+        <v>17.99087905883789</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -52946,6 +54103,9 @@
       <c r="AQ386" t="n">
         <v>19.11563110351562</v>
       </c>
+      <c r="AR386" t="n">
+        <v>19.17720413208008</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -53083,6 +54243,9 @@
       <c r="AQ387" t="n">
         <v>21.47417068481445</v>
       </c>
+      <c r="AR387" t="n">
+        <v>21.66913414001465</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -53220,6 +54383,9 @@
       <c r="AQ388" t="n">
         <v>22.98392677307129</v>
       </c>
+      <c r="AR388" t="n">
+        <v>23.20134544372559</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -53359,6 +54525,9 @@
       <c r="AQ389" t="n">
         <v>15.0770959854126</v>
       </c>
+      <c r="AR389" t="n">
+        <v>15.58652210235596</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -53498,6 +54667,9 @@
       <c r="AQ390" t="n">
         <v>16.12882232666016</v>
       </c>
+      <c r="AR390" t="n">
+        <v>16.99910354614258</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -53637,6 +54809,9 @@
       <c r="AQ391" t="n">
         <v>18.57272338867188</v>
       </c>
+      <c r="AR391" t="n">
+        <v>18.97658348083496</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -53776,6 +54951,9 @@
       <c r="AQ392" t="n">
         <v>20.38833236694336</v>
       </c>
+      <c r="AR392" t="n">
+        <v>20.27168273925781</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -53915,6 +55093,9 @@
       <c r="AQ393" t="n">
         <v>21.75552940368652</v>
       </c>
+      <c r="AR393" t="n">
+        <v>21.53654861450195</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -54052,6 +55233,9 @@
       <c r="AQ394" t="n">
         <v>23.43425559997559</v>
       </c>
+      <c r="AR394" t="n">
+        <v>23.35981178283691</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -54189,6 +55373,9 @@
       <c r="AQ395" t="n">
         <v>24.74841499328613</v>
       </c>
+      <c r="AR395" t="n">
+        <v>24.76812362670898</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -54326,6 +55513,9 @@
       <c r="AQ396" t="n">
         <v>28.4445686340332</v>
       </c>
+      <c r="AR396" t="n">
+        <v>28.44127082824707</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -54463,6 +55653,9 @@
       <c r="AQ397" t="n">
         <v>30.93518257141113</v>
       </c>
+      <c r="AR397" t="n">
+        <v>30.94807815551758</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -54598,6 +55791,9 @@
       <c r="AQ398" t="n">
         <v>32.26997375488281</v>
       </c>
+      <c r="AR398" t="n">
+        <v>32.25864028930664</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -54737,6 +55933,9 @@
       <c r="AQ399" t="n">
         <v>5.643265724182129</v>
       </c>
+      <c r="AR399" t="n">
+        <v>6.152563095092773</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -54876,6 +56075,9 @@
       <c r="AQ400" t="n">
         <v>9.443052291870117</v>
       </c>
+      <c r="AR400" t="n">
+        <v>9.917733192443848</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -55015,6 +56217,9 @@
       <c r="AQ401" t="n">
         <v>14.87159538269043</v>
       </c>
+      <c r="AR401" t="n">
+        <v>15.06414127349854</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -55154,6 +56359,9 @@
       <c r="AQ402" t="n">
         <v>20.3464412689209</v>
       </c>
+      <c r="AR402" t="n">
+        <v>20.13961410522461</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -55293,6 +56501,9 @@
       <c r="AQ403" t="n">
         <v>22.5659122467041</v>
       </c>
+      <c r="AR403" t="n">
+        <v>22.94080924987793</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -55430,6 +56641,9 @@
       <c r="AQ404" t="n">
         <v>23.93642807006836</v>
       </c>
+      <c r="AR404" t="n">
+        <v>24.19120025634766</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -55567,6 +56781,9 @@
       <c r="AQ405" t="n">
         <v>25.06189155578613</v>
       </c>
+      <c r="AR405" t="n">
+        <v>25.14518547058105</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -55704,6 +56921,9 @@
       <c r="AQ406" t="n">
         <v>26.63214874267578</v>
       </c>
+      <c r="AR406" t="n">
+        <v>26.63610649108887</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -55841,6 +57061,9 @@
       <c r="AQ407" t="n">
         <v>27.52316284179688</v>
       </c>
+      <c r="AR407" t="n">
+        <v>27.46872138977051</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -55978,6 +57201,9 @@
       <c r="AQ408" t="n">
         <v>28.11582374572754</v>
       </c>
+      <c r="AR408" t="n">
+        <v>28.12054252624512</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -56113,6 +57339,9 @@
       <c r="AQ409" t="n">
         <v>28.47067451477051</v>
       </c>
+      <c r="AR409" t="n">
+        <v>28.43145942687988</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -56246,6 +57475,9 @@
       <c r="AQ410" t="n">
         <v>5.105861663818359</v>
       </c>
+      <c r="AR410" t="n">
+        <v>10.13275527954102</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -56379,6 +57611,9 @@
       <c r="AQ411" t="n">
         <v>16.25967407226562</v>
       </c>
+      <c r="AR411" t="n">
+        <v>17.83008003234863</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -56512,6 +57747,9 @@
       <c r="AQ412" t="n">
         <v>20.33977508544922</v>
       </c>
+      <c r="AR412" t="n">
+        <v>20.81266784667969</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -56649,6 +57887,9 @@
       <c r="AQ413" t="n">
         <v>0.3946677148342133</v>
       </c>
+      <c r="AR413" t="n">
+        <v>0.3023096323013306</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -56786,6 +58027,9 @@
       <c r="AQ414" t="n">
         <v>1.949566602706909</v>
       </c>
+      <c r="AR414" t="n">
+        <v>1.395700097084045</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -56925,6 +58169,9 @@
       <c r="AQ415" t="n">
         <v>17.53315162658691</v>
       </c>
+      <c r="AR415" t="n">
+        <v>17.91772270202637</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -57064,6 +58311,9 @@
       <c r="AQ416" t="n">
         <v>29.38474273681641</v>
       </c>
+      <c r="AR416" t="n">
+        <v>29.41366195678711</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -57197,6 +58447,9 @@
       <c r="AQ417" t="n">
         <v>0.1949833482503891</v>
       </c>
+      <c r="AR417" t="n">
+        <v>0.2249882072210312</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -57328,6 +58581,9 @@
       <c r="AQ418" t="n">
         <v>0.3538044095039368</v>
       </c>
+      <c r="AR418" t="n">
+        <v>0.3474260568618774</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -57461,6 +58717,9 @@
       <c r="AQ419" t="n">
         <v>14.40653324127197</v>
       </c>
+      <c r="AR419" t="n">
+        <v>13.3824462890625</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -57594,6 +58853,9 @@
       <c r="AQ420" t="n">
         <v>0.2032881528139114</v>
       </c>
+      <c r="AR420" t="n">
+        <v>0.2876913845539093</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -57727,6 +58989,9 @@
       <c r="AQ421" t="n">
         <v>0.7063271403312683</v>
       </c>
+      <c r="AR421" t="n">
+        <v>1.19394052028656</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -57860,6 +59125,9 @@
       <c r="AQ422" t="n">
         <v>17.61746215820312</v>
       </c>
+      <c r="AR422" t="n">
+        <v>19.06899261474609</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -57993,6 +59261,9 @@
       <c r="AQ423" t="n">
         <v>0.6850104331970215</v>
       </c>
+      <c r="AR423" t="n">
+        <v>1.033852338790894</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -58126,6 +59397,9 @@
       <c r="AQ424" t="n">
         <v>0.9700517058372498</v>
       </c>
+      <c r="AR424" t="n">
+        <v>2.351666450500488</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -58259,6 +59533,9 @@
       <c r="AQ425" t="n">
         <v>17.10086059570312</v>
       </c>
+      <c r="AR425" t="n">
+        <v>18.86172866821289</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -58398,6 +59675,9 @@
       <c r="AQ426" t="n">
         <v>0.6844961643218994</v>
       </c>
+      <c r="AR426" t="n">
+        <v>0.8580089807510376</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -58537,6 +59817,9 @@
       <c r="AQ427" t="n">
         <v>0.3914735913276672</v>
       </c>
+      <c r="AR427" t="n">
+        <v>0.4030798077583313</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -58676,6 +59959,9 @@
       <c r="AQ428" t="n">
         <v>0.7893977165222168</v>
       </c>
+      <c r="AR428" t="n">
+        <v>0.9165483713150024</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -58815,6 +60101,9 @@
       <c r="AQ429" t="n">
         <v>17.53961944580078</v>
       </c>
+      <c r="AR429" t="n">
+        <v>17.27829360961914</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -58954,6 +60243,9 @@
       <c r="AQ430" t="n">
         <v>24.44275093078613</v>
       </c>
+      <c r="AR430" t="n">
+        <v>24.09222412109375</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -59091,6 +60383,9 @@
       <c r="AQ431" t="n">
         <v>26.28457069396973</v>
       </c>
+      <c r="AR431" t="n">
+        <v>26.55595207214355</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -59228,6 +60523,9 @@
       <c r="AQ432" t="n">
         <v>27.58999633789062</v>
       </c>
+      <c r="AR432" t="n">
+        <v>27.63315200805664</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -59365,6 +60663,9 @@
       <c r="AQ433" t="n">
         <v>28.79334259033203</v>
       </c>
+      <c r="AR433" t="n">
+        <v>28.99664688110352</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -59502,6 +60803,9 @@
       <c r="AQ434" t="n">
         <v>29.32671165466309</v>
       </c>
+      <c r="AR434" t="n">
+        <v>29.32023811340332</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -59639,6 +60943,9 @@
       <c r="AQ435" t="n">
         <v>28.69418716430664</v>
       </c>
+      <c r="AR435" t="n">
+        <v>28.7677173614502</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -59776,6 +61083,9 @@
       <c r="AQ436" t="n">
         <v>29.3402271270752</v>
       </c>
+      <c r="AR436" t="n">
+        <v>29.34172248840332</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -59909,6 +61219,9 @@
       <c r="AQ437" t="n">
         <v>1.51196277141571</v>
       </c>
+      <c r="AR437" t="n">
+        <v>1.514636754989624</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -60042,6 +61355,9 @@
       <c r="AQ438" t="n">
         <v>0.8891761302947998</v>
       </c>
+      <c r="AR438" t="n">
+        <v>0.4884027242660522</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -60175,6 +61491,9 @@
       <c r="AQ439" t="n">
         <v>17.14955711364746</v>
       </c>
+      <c r="AR439" t="n">
+        <v>16.6326732635498</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -60314,6 +61633,9 @@
       <c r="AQ440" t="n">
         <v>0.1923704594373703</v>
       </c>
+      <c r="AR440" t="n">
+        <v>0.2709740996360779</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -60453,6 +61775,9 @@
       <c r="AQ441" t="n">
         <v>0.292548656463623</v>
       </c>
+      <c r="AR441" t="n">
+        <v>0.3619612455368042</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -60592,6 +61917,9 @@
       <c r="AQ442" t="n">
         <v>3.363633155822754</v>
       </c>
+      <c r="AR442" t="n">
+        <v>3.30224871635437</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -60731,6 +62059,9 @@
       <c r="AQ443" t="n">
         <v>19.42997169494629</v>
       </c>
+      <c r="AR443" t="n">
+        <v>18.37238883972168</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -60870,6 +62201,9 @@
       <c r="AQ444" t="n">
         <v>23.83941841125488</v>
       </c>
+      <c r="AR444" t="n">
+        <v>23.98501205444336</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -61007,6 +62341,9 @@
       <c r="AQ445" t="n">
         <v>25.11545562744141</v>
       </c>
+      <c r="AR445" t="n">
+        <v>25.0378303527832</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -61144,6 +62481,9 @@
       <c r="AQ446" t="n">
         <v>25.79257583618164</v>
       </c>
+      <c r="AR446" t="n">
+        <v>25.75125694274902</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -61281,6 +62621,9 @@
       <c r="AQ447" t="n">
         <v>26.41888427734375</v>
       </c>
+      <c r="AR447" t="n">
+        <v>26.56953239440918</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -61418,6 +62761,9 @@
       <c r="AQ448" t="n">
         <v>26.60810279846191</v>
       </c>
+      <c r="AR448" t="n">
+        <v>26.85037994384766</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -61555,6 +62901,9 @@
       <c r="AQ449" t="n">
         <v>27.88360977172852</v>
       </c>
+      <c r="AR449" t="n">
+        <v>27.90474319458008</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -61692,6 +63041,9 @@
       <c r="AQ450" t="n">
         <v>29.15511703491211</v>
       </c>
+      <c r="AR450" t="n">
+        <v>29.17062759399414</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -61825,6 +63177,9 @@
       <c r="AQ451" t="n">
         <v>3.673985481262207</v>
       </c>
+      <c r="AR451" t="n">
+        <v>4.275015354156494</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -61958,6 +63313,9 @@
       <c r="AQ452" t="n">
         <v>1.468786954879761</v>
       </c>
+      <c r="AR452" t="n">
+        <v>1.844529747962952</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -62091,6 +63449,9 @@
       <c r="AQ453" t="n">
         <v>9.719404220581055</v>
       </c>
+      <c r="AR453" t="n">
+        <v>12.2647123336792</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -62220,6 +63581,9 @@
       <c r="AQ454" t="n">
         <v>3.370521068572998</v>
       </c>
+      <c r="AR454" t="n">
+        <v>2.18956184387207</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -62353,6 +63717,9 @@
       <c r="AQ455" t="n">
         <v>3.080264806747437</v>
       </c>
+      <c r="AR455" t="n">
+        <v>0.8641682267189026</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -62486,6 +63853,9 @@
       <c r="AQ456" t="n">
         <v>4.471447944641113</v>
       </c>
+      <c r="AR456" t="n">
+        <v>4.49933910369873</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -62619,6 +63989,9 @@
       <c r="AQ457" t="n">
         <v>13.07374000549316</v>
       </c>
+      <c r="AR457" t="n">
+        <v>13.80993556976318</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -62752,6 +64125,9 @@
       <c r="AQ458" t="n">
         <v>16.97361755371094</v>
       </c>
+      <c r="AR458" t="n">
+        <v>17.75274276733398</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -62883,6 +64259,9 @@
       <c r="AQ459" t="n">
         <v>19.97122573852539</v>
       </c>
+      <c r="AR459" t="n">
+        <v>19.97770309448242</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -63014,6 +64393,9 @@
       <c r="AQ460" t="n">
         <v>21.77870750427246</v>
       </c>
+      <c r="AR460" t="n">
+        <v>21.99974060058594</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -63145,6 +64527,9 @@
       <c r="AQ461" t="n">
         <v>23.29887771606445</v>
       </c>
+      <c r="AR461" t="n">
+        <v>23.74590492248535</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -63276,6 +64661,9 @@
       <c r="AQ462" t="n">
         <v>23.96614646911621</v>
       </c>
+      <c r="AR462" t="n">
+        <v>24.32577896118164</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -63407,6 +64795,9 @@
       <c r="AQ463" t="n">
         <v>26.34177017211914</v>
       </c>
+      <c r="AR463" t="n">
+        <v>26.39420127868652</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -63535,6 +64926,9 @@
       </c>
       <c r="AQ464" t="n">
         <v>26.24178504943848</v>
+      </c>
+      <c r="AR464" t="n">
+        <v>26.33153533935547</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
+++ b/notebooks/SHEM/tuning/eval_files/NO3_model_whole_v5.xlsx
@@ -773,9 +773,7 @@
       <c r="AQ2" t="n">
         <v>22.43636131286621</v>
       </c>
-      <c r="AR2" t="n">
-        <v>22.75328254699707</v>
-      </c>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,9 +907,7 @@
       <c r="AQ3" t="n">
         <v>22.43636131286621</v>
       </c>
-      <c r="AR3" t="n">
-        <v>22.75328254699707</v>
-      </c>
+      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,9 +1039,7 @@
       <c r="AQ4" t="n">
         <v>22.43636131286621</v>
       </c>
-      <c r="AR4" t="n">
-        <v>22.75328254699707</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1183,9 +1177,7 @@
       <c r="AQ5" t="n">
         <v>22.48161888122559</v>
       </c>
-      <c r="AR5" t="n">
-        <v>22.78958129882812</v>
-      </c>
+      <c r="AR5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,9 +1309,7 @@
       <c r="AQ6" t="n">
         <v>22.69892883300781</v>
       </c>
-      <c r="AR6" t="n">
-        <v>22.9162540435791</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1459,9 +1449,7 @@
       <c r="AQ7" t="n">
         <v>22.69892883300781</v>
       </c>
-      <c r="AR7" t="n">
-        <v>22.9162540435791</v>
-      </c>
+      <c r="AR7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1601,9 +1589,7 @@
       <c r="AQ8" t="n">
         <v>23.3166675567627</v>
       </c>
-      <c r="AR8" t="n">
-        <v>23.35495567321777</v>
-      </c>
+      <c r="AR8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1735,9 +1721,7 @@
       <c r="AQ9" t="n">
         <v>23.60137939453125</v>
       </c>
-      <c r="AR9" t="n">
-        <v>23.64489936828613</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1875,9 +1859,7 @@
       <c r="AQ10" t="n">
         <v>23.83181762695312</v>
       </c>
-      <c r="AR10" t="n">
-        <v>23.8386058807373</v>
-      </c>
+      <c r="AR10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2015,9 +1997,7 @@
       <c r="AQ11" t="n">
         <v>24.29356956481934</v>
       </c>
-      <c r="AR11" t="n">
-        <v>24.32829284667969</v>
-      </c>
+      <c r="AR11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2149,9 +2129,7 @@
       <c r="AQ12" t="n">
         <v>24.88991165161133</v>
       </c>
-      <c r="AR12" t="n">
-        <v>24.86928176879883</v>
-      </c>
+      <c r="AR12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2289,9 +2267,7 @@
       <c r="AQ13" t="n">
         <v>24.88991165161133</v>
       </c>
-      <c r="AR13" t="n">
-        <v>24.86928176879883</v>
-      </c>
+      <c r="AR13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2429,9 +2405,7 @@
       <c r="AQ14" t="n">
         <v>27.06662559509277</v>
       </c>
-      <c r="AR14" t="n">
-        <v>27.09538078308105</v>
-      </c>
+      <c r="AR14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2563,9 +2537,7 @@
       <c r="AQ15" t="n">
         <v>29.05513954162598</v>
       </c>
-      <c r="AR15" t="n">
-        <v>28.99318695068359</v>
-      </c>
+      <c r="AR15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2703,9 +2675,7 @@
       <c r="AQ16" t="n">
         <v>29.05513954162598</v>
       </c>
-      <c r="AR16" t="n">
-        <v>28.99318695068359</v>
-      </c>
+      <c r="AR16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2843,9 +2813,7 @@
       <c r="AQ17" t="n">
         <v>29.83145713806152</v>
       </c>
-      <c r="AR17" t="n">
-        <v>29.84993553161621</v>
-      </c>
+      <c r="AR17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2983,9 +2951,7 @@
       <c r="AQ18" t="n">
         <v>30.04994964599609</v>
       </c>
-      <c r="AR18" t="n">
-        <v>30.04936408996582</v>
-      </c>
+      <c r="AR18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3121,9 +3087,7 @@
       <c r="AQ19" t="n">
         <v>30.09794235229492</v>
       </c>
-      <c r="AR19" t="n">
-        <v>30.10688591003418</v>
-      </c>
+      <c r="AR19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3253,9 +3217,7 @@
       <c r="AQ20" t="n">
         <v>30.09794235229492</v>
       </c>
-      <c r="AR20" t="n">
-        <v>30.10688591003418</v>
-      </c>
+      <c r="AR20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3395,9 +3357,7 @@
       <c r="AQ21" t="n">
         <v>23.64029312133789</v>
       </c>
-      <c r="AR21" t="n">
-        <v>23.65010452270508</v>
-      </c>
+      <c r="AR21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3529,9 +3489,7 @@
       <c r="AQ22" t="n">
         <v>23.64029312133789</v>
       </c>
-      <c r="AR22" t="n">
-        <v>23.65010452270508</v>
-      </c>
+      <c r="AR22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3669,9 +3627,7 @@
       <c r="AQ23" t="n">
         <v>23.67545700073242</v>
       </c>
-      <c r="AR23" t="n">
-        <v>23.68566703796387</v>
-      </c>
+      <c r="AR23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3811,9 +3767,7 @@
       <c r="AQ24" t="n">
         <v>23.72985076904297</v>
       </c>
-      <c r="AR24" t="n">
-        <v>23.74444770812988</v>
-      </c>
+      <c r="AR24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3945,9 +3899,7 @@
       <c r="AQ25" t="n">
         <v>23.72985076904297</v>
       </c>
-      <c r="AR25" t="n">
-        <v>23.74444770812988</v>
-      </c>
+      <c r="AR25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4087,9 +4039,7 @@
       <c r="AQ26" t="n">
         <v>23.82114028930664</v>
       </c>
-      <c r="AR26" t="n">
-        <v>23.84149551391602</v>
-      </c>
+      <c r="AR26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4221,9 +4171,7 @@
       <c r="AQ27" t="n">
         <v>23.85807418823242</v>
       </c>
-      <c r="AR27" t="n">
-        <v>23.88356971740723</v>
-      </c>
+      <c r="AR27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4361,9 +4309,7 @@
       <c r="AQ28" t="n">
         <v>23.89603614807129</v>
       </c>
-      <c r="AR28" t="n">
-        <v>23.92388153076172</v>
-      </c>
+      <c r="AR28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4501,9 +4447,7 @@
       <c r="AQ29" t="n">
         <v>23.99274826049805</v>
       </c>
-      <c r="AR29" t="n">
-        <v>24.01241493225098</v>
-      </c>
+      <c r="AR29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4635,9 +4579,7 @@
       <c r="AQ30" t="n">
         <v>24.09142112731934</v>
       </c>
-      <c r="AR30" t="n">
-        <v>24.0989818572998</v>
-      </c>
+      <c r="AR30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4775,9 +4717,7 @@
       <c r="AQ31" t="n">
         <v>24.09142112731934</v>
       </c>
-      <c r="AR31" t="n">
-        <v>24.0989818572998</v>
-      </c>
+      <c r="AR31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4915,9 +4855,7 @@
       <c r="AQ32" t="n">
         <v>24.22990226745605</v>
       </c>
-      <c r="AR32" t="n">
-        <v>24.2551212310791</v>
-      </c>
+      <c r="AR32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5055,9 +4993,7 @@
       <c r="AQ33" t="n">
         <v>24.38776588439941</v>
       </c>
-      <c r="AR33" t="n">
-        <v>24.39021873474121</v>
-      </c>
+      <c r="AR33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5189,9 +5125,7 @@
       <c r="AQ34" t="n">
         <v>24.38850212097168</v>
       </c>
-      <c r="AR34" t="n">
-        <v>24.39094161987305</v>
-      </c>
+      <c r="AR34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5329,9 +5263,7 @@
       <c r="AQ35" t="n">
         <v>24.55635452270508</v>
       </c>
-      <c r="AR35" t="n">
-        <v>24.55882263183594</v>
-      </c>
+      <c r="AR35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5465,9 +5397,7 @@
       <c r="AQ36" t="n">
         <v>24.29000854492188</v>
       </c>
-      <c r="AR36" t="n">
-        <v>24.2704906463623</v>
-      </c>
+      <c r="AR36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5605,9 +5535,7 @@
       <c r="AQ37" t="n">
         <v>24.29000854492188</v>
       </c>
-      <c r="AR37" t="n">
-        <v>24.2704906463623</v>
-      </c>
+      <c r="AR37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5745,9 +5673,7 @@
       <c r="AQ38" t="n">
         <v>24.27465438842773</v>
       </c>
-      <c r="AR38" t="n">
-        <v>24.25820922851562</v>
-      </c>
+      <c r="AR38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5887,9 +5813,7 @@
       <c r="AQ39" t="n">
         <v>24.25114440917969</v>
       </c>
-      <c r="AR39" t="n">
-        <v>24.23410415649414</v>
-      </c>
+      <c r="AR39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6029,9 +5953,7 @@
       <c r="AQ40" t="n">
         <v>24.21247291564941</v>
       </c>
-      <c r="AR40" t="n">
-        <v>24.19211769104004</v>
-      </c>
+      <c r="AR40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6169,9 +6091,7 @@
       <c r="AQ41" t="n">
         <v>24.17782592773438</v>
       </c>
-      <c r="AR41" t="n">
-        <v>24.15837478637695</v>
-      </c>
+      <c r="AR41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6309,9 +6229,7 @@
       <c r="AQ42" t="n">
         <v>24.14359092712402</v>
       </c>
-      <c r="AR42" t="n">
-        <v>24.13364601135254</v>
-      </c>
+      <c r="AR42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6449,9 +6367,7 @@
       <c r="AQ43" t="n">
         <v>24.12019729614258</v>
       </c>
-      <c r="AR43" t="n">
-        <v>24.11920547485352</v>
-      </c>
+      <c r="AR43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6589,9 +6505,7 @@
       <c r="AQ44" t="n">
         <v>24.10380554199219</v>
       </c>
-      <c r="AR44" t="n">
-        <v>24.10041809082031</v>
-      </c>
+      <c r="AR44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6729,9 +6643,7 @@
       <c r="AQ45" t="n">
         <v>24.10420417785645</v>
       </c>
-      <c r="AR45" t="n">
-        <v>24.10660362243652</v>
-      </c>
+      <c r="AR45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6869,9 +6781,7 @@
       <c r="AQ46" t="n">
         <v>24.13065147399902</v>
       </c>
-      <c r="AR46" t="n">
-        <v>24.12936592102051</v>
-      </c>
+      <c r="AR46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7009,9 +6919,7 @@
       <c r="AQ47" t="n">
         <v>24.15222930908203</v>
       </c>
-      <c r="AR47" t="n">
-        <v>24.15985298156738</v>
-      </c>
+      <c r="AR47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7149,9 +7057,7 @@
       <c r="AQ48" t="n">
         <v>24.1871223449707</v>
       </c>
-      <c r="AR48" t="n">
-        <v>24.19430923461914</v>
-      </c>
+      <c r="AR48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7287,9 +7193,7 @@
       <c r="AQ49" t="n">
         <v>24.19433784484863</v>
       </c>
-      <c r="AR49" t="n">
-        <v>24.2006721496582</v>
-      </c>
+      <c r="AR49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7425,9 +7329,7 @@
       <c r="AQ50" t="n">
         <v>24.19433784484863</v>
       </c>
-      <c r="AR50" t="n">
-        <v>24.2006721496582</v>
-      </c>
+      <c r="AR50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7561,9 +7463,7 @@
       <c r="AQ51" t="n">
         <v>22.44287490844727</v>
       </c>
-      <c r="AR51" t="n">
-        <v>22.45943832397461</v>
-      </c>
+      <c r="AR51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7697,9 +7597,7 @@
       <c r="AQ52" t="n">
         <v>23.59730911254883</v>
       </c>
-      <c r="AR52" t="n">
-        <v>23.57793998718262</v>
-      </c>
+      <c r="AR52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7833,9 +7731,7 @@
       <c r="AQ53" t="n">
         <v>24.55478477478027</v>
       </c>
-      <c r="AR53" t="n">
-        <v>24.60188102722168</v>
-      </c>
+      <c r="AR53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7975,9 +7871,7 @@
       <c r="AQ54" t="n">
         <v>21.41876411437988</v>
       </c>
-      <c r="AR54" t="n">
-        <v>21.53346633911133</v>
-      </c>
+      <c r="AR54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8115,9 +8009,7 @@
       <c r="AQ55" t="n">
         <v>22.64809417724609</v>
       </c>
-      <c r="AR55" t="n">
-        <v>22.59612846374512</v>
-      </c>
+      <c r="AR55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8257,9 +8149,7 @@
       <c r="AQ56" t="n">
         <v>24.49677848815918</v>
       </c>
-      <c r="AR56" t="n">
-        <v>24.35014152526855</v>
-      </c>
+      <c r="AR56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8399,9 +8289,7 @@
       <c r="AQ57" t="n">
         <v>25.78945350646973</v>
       </c>
-      <c r="AR57" t="n">
-        <v>25.77002143859863</v>
-      </c>
+      <c r="AR57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8539,9 +8427,7 @@
       <c r="AQ58" t="n">
         <v>26.63006401062012</v>
       </c>
-      <c r="AR58" t="n">
-        <v>26.65719223022461</v>
-      </c>
+      <c r="AR58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8679,9 +8565,7 @@
       <c r="AQ59" t="n">
         <v>26.97157287597656</v>
       </c>
-      <c r="AR59" t="n">
-        <v>26.96162986755371</v>
-      </c>
+      <c r="AR59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8819,9 +8703,7 @@
       <c r="AQ60" t="n">
         <v>27.16524887084961</v>
       </c>
-      <c r="AR60" t="n">
-        <v>27.15011978149414</v>
-      </c>
+      <c r="AR60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8959,9 +8841,7 @@
       <c r="AQ61" t="n">
         <v>27.40969467163086</v>
       </c>
-      <c r="AR61" t="n">
-        <v>27.39953231811523</v>
-      </c>
+      <c r="AR61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9099,9 +8979,7 @@
       <c r="AQ62" t="n">
         <v>27.65495491027832</v>
       </c>
-      <c r="AR62" t="n">
-        <v>27.66019630432129</v>
-      </c>
+      <c r="AR62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9239,9 +9117,7 @@
       <c r="AQ63" t="n">
         <v>27.92228317260742</v>
       </c>
-      <c r="AR63" t="n">
-        <v>27.92310905456543</v>
-      </c>
+      <c r="AR63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9379,9 +9255,7 @@
       <c r="AQ64" t="n">
         <v>28.03413772583008</v>
       </c>
-      <c r="AR64" t="n">
-        <v>28.04186630249023</v>
-      </c>
+      <c r="AR64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9519,9 +9393,7 @@
       <c r="AQ65" t="n">
         <v>28.26225852966309</v>
       </c>
-      <c r="AR65" t="n">
-        <v>28.2727108001709</v>
-      </c>
+      <c r="AR65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9659,9 +9531,7 @@
       <c r="AQ66" t="n">
         <v>28.59826278686523</v>
       </c>
-      <c r="AR66" t="n">
-        <v>28.59513854980469</v>
-      </c>
+      <c r="AR66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9795,9 +9665,7 @@
       <c r="AQ67" t="n">
         <v>28.84344863891602</v>
       </c>
-      <c r="AR67" t="n">
-        <v>28.84404182434082</v>
-      </c>
+      <c r="AR67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9935,9 +9803,7 @@
       <c r="AQ68" t="n">
         <v>28.90419578552246</v>
       </c>
-      <c r="AR68" t="n">
-        <v>28.90424919128418</v>
-      </c>
+      <c r="AR68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10073,9 +9939,7 @@
       <c r="AQ69" t="n">
         <v>28.90805816650391</v>
       </c>
-      <c r="AR69" t="n">
-        <v>28.90841293334961</v>
-      </c>
+      <c r="AR69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10203,9 +10067,7 @@
       <c r="AQ70" t="n">
         <v>17.62956237792969</v>
       </c>
-      <c r="AR70" t="n">
-        <v>17.9348201751709</v>
-      </c>
+      <c r="AR70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10339,9 +10201,7 @@
       <c r="AQ71" t="n">
         <v>17.62956237792969</v>
       </c>
-      <c r="AR71" t="n">
-        <v>17.9348201751709</v>
-      </c>
+      <c r="AR71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10473,9 +10333,7 @@
       <c r="AQ72" t="n">
         <v>20.44615173339844</v>
       </c>
-      <c r="AR72" t="n">
-        <v>20.50504875183105</v>
-      </c>
+      <c r="AR72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10609,9 +10467,7 @@
       <c r="AQ73" t="n">
         <v>24.51637840270996</v>
       </c>
-      <c r="AR73" t="n">
-        <v>24.61410713195801</v>
-      </c>
+      <c r="AR73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10739,9 +10595,7 @@
       <c r="AQ74" t="n">
         <v>24.51637840270996</v>
       </c>
-      <c r="AR74" t="n">
-        <v>24.61410713195801</v>
-      </c>
+      <c r="AR74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10875,9 +10729,7 @@
       <c r="AQ75" t="n">
         <v>26.15978050231934</v>
       </c>
-      <c r="AR75" t="n">
-        <v>26.18566513061523</v>
-      </c>
+      <c r="AR75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11005,9 +10857,7 @@
       <c r="AQ76" t="n">
         <v>26.60834693908691</v>
       </c>
-      <c r="AR76" t="n">
-        <v>26.67647743225098</v>
-      </c>
+      <c r="AR76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11139,9 +10989,7 @@
       <c r="AQ77" t="n">
         <v>26.87260818481445</v>
       </c>
-      <c r="AR77" t="n">
-        <v>26.90222549438477</v>
-      </c>
+      <c r="AR77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11273,9 +11121,7 @@
       <c r="AQ78" t="n">
         <v>27.15390205383301</v>
       </c>
-      <c r="AR78" t="n">
-        <v>27.1345329284668</v>
-      </c>
+      <c r="AR78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11403,9 +11249,7 @@
       <c r="AQ79" t="n">
         <v>27.18051719665527</v>
       </c>
-      <c r="AR79" t="n">
-        <v>27.15632629394531</v>
-      </c>
+      <c r="AR79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11537,9 +11381,7 @@
       <c r="AQ80" t="n">
         <v>27.18051719665527</v>
       </c>
-      <c r="AR80" t="n">
-        <v>27.15632629394531</v>
-      </c>
+      <c r="AR80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11671,9 +11513,7 @@
       <c r="AQ81" t="n">
         <v>25.81042289733887</v>
       </c>
-      <c r="AR81" t="n">
-        <v>25.81165885925293</v>
-      </c>
+      <c r="AR81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11805,9 +11645,7 @@
       <c r="AQ82" t="n">
         <v>26.17525291442871</v>
       </c>
-      <c r="AR82" t="n">
-        <v>26.13022613525391</v>
-      </c>
+      <c r="AR82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11935,9 +11773,7 @@
       <c r="AQ83" t="n">
         <v>26.17525291442871</v>
       </c>
-      <c r="AR83" t="n">
-        <v>26.13022613525391</v>
-      </c>
+      <c r="AR83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12069,9 +11905,7 @@
       <c r="AQ84" t="n">
         <v>28.32012367248535</v>
       </c>
-      <c r="AR84" t="n">
-        <v>28.32633972167969</v>
-      </c>
+      <c r="AR84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12199,9 +12033,7 @@
       <c r="AQ85" t="n">
         <v>28.72781372070312</v>
       </c>
-      <c r="AR85" t="n">
-        <v>28.73254203796387</v>
-      </c>
+      <c r="AR85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12333,9 +12165,7 @@
       <c r="AQ86" t="n">
         <v>28.72869682312012</v>
       </c>
-      <c r="AR86" t="n">
-        <v>28.7333869934082</v>
-      </c>
+      <c r="AR86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12475,9 +12305,7 @@
       <c r="AQ87" t="n">
         <v>15.90183448791504</v>
       </c>
-      <c r="AR87" t="n">
-        <v>16.09998893737793</v>
-      </c>
+      <c r="AR87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12615,9 +12443,7 @@
       <c r="AQ88" t="n">
         <v>17.57133483886719</v>
       </c>
-      <c r="AR88" t="n">
-        <v>17.71602058410645</v>
-      </c>
+      <c r="AR88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12757,9 +12583,7 @@
       <c r="AQ89" t="n">
         <v>19.84147644042969</v>
       </c>
-      <c r="AR89" t="n">
-        <v>19.98680114746094</v>
-      </c>
+      <c r="AR89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12899,9 +12723,7 @@
       <c r="AQ90" t="n">
         <v>23.69522476196289</v>
       </c>
-      <c r="AR90" t="n">
-        <v>23.73740577697754</v>
-      </c>
+      <c r="AR90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13039,9 +12861,7 @@
       <c r="AQ91" t="n">
         <v>26.21978569030762</v>
       </c>
-      <c r="AR91" t="n">
-        <v>26.2108154296875</v>
-      </c>
+      <c r="AR91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13179,9 +12999,7 @@
       <c r="AQ92" t="n">
         <v>26.62049293518066</v>
       </c>
-      <c r="AR92" t="n">
-        <v>26.61051177978516</v>
-      </c>
+      <c r="AR92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13319,9 +13137,7 @@
       <c r="AQ93" t="n">
         <v>26.57134628295898</v>
       </c>
-      <c r="AR93" t="n">
-        <v>26.56083679199219</v>
-      </c>
+      <c r="AR93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13459,9 +13275,7 @@
       <c r="AQ94" t="n">
         <v>26.61965179443359</v>
       </c>
-      <c r="AR94" t="n">
-        <v>26.61358261108398</v>
-      </c>
+      <c r="AR94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13599,9 +13413,7 @@
       <c r="AQ95" t="n">
         <v>27.38665580749512</v>
       </c>
-      <c r="AR95" t="n">
-        <v>27.39115333557129</v>
-      </c>
+      <c r="AR95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13739,9 +13551,7 @@
       <c r="AQ96" t="n">
         <v>28.23541069030762</v>
       </c>
-      <c r="AR96" t="n">
-        <v>28.23690414428711</v>
-      </c>
+      <c r="AR96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13879,9 +13689,7 @@
       <c r="AQ97" t="n">
         <v>28.58251571655273</v>
       </c>
-      <c r="AR97" t="n">
-        <v>28.5811653137207</v>
-      </c>
+      <c r="AR97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14019,9 +13827,7 @@
       <c r="AQ98" t="n">
         <v>28.66877746582031</v>
       </c>
-      <c r="AR98" t="n">
-        <v>28.66858863830566</v>
-      </c>
+      <c r="AR98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14159,9 +13965,7 @@
       <c r="AQ99" t="n">
         <v>28.96045684814453</v>
       </c>
-      <c r="AR99" t="n">
-        <v>28.96082496643066</v>
-      </c>
+      <c r="AR99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14299,9 +14103,7 @@
       <c r="AQ100" t="n">
         <v>28.9649715423584</v>
       </c>
-      <c r="AR100" t="n">
-        <v>28.96495246887207</v>
-      </c>
+      <c r="AR100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14439,9 +14241,7 @@
       <c r="AQ101" t="n">
         <v>28.93512344360352</v>
       </c>
-      <c r="AR101" t="n">
-        <v>28.93520545959473</v>
-      </c>
+      <c r="AR101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14577,9 +14377,7 @@
       <c r="AQ102" t="n">
         <v>28.92127227783203</v>
       </c>
-      <c r="AR102" t="n">
-        <v>28.92132568359375</v>
-      </c>
+      <c r="AR102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14719,9 +14517,7 @@
       <c r="AQ103" t="n">
         <v>14.65914440155029</v>
       </c>
-      <c r="AR103" t="n">
-        <v>14.8942403793335</v>
-      </c>
+      <c r="AR103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14859,9 +14655,7 @@
       <c r="AQ104" t="n">
         <v>15.72530841827393</v>
       </c>
-      <c r="AR104" t="n">
-        <v>15.95005989074707</v>
-      </c>
+      <c r="AR104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15001,9 +14795,7 @@
       <c r="AQ105" t="n">
         <v>19.20228385925293</v>
       </c>
-      <c r="AR105" t="n">
-        <v>19.24592971801758</v>
-      </c>
+      <c r="AR105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -15143,9 +14935,7 @@
       <c r="AQ106" t="n">
         <v>25.07301712036133</v>
       </c>
-      <c r="AR106" t="n">
-        <v>25.07344055175781</v>
-      </c>
+      <c r="AR106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15283,9 +15073,7 @@
       <c r="AQ107" t="n">
         <v>26.65420532226562</v>
       </c>
-      <c r="AR107" t="n">
-        <v>26.65196228027344</v>
-      </c>
+      <c r="AR107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -15423,9 +15211,7 @@
       <c r="AQ108" t="n">
         <v>27.19811820983887</v>
       </c>
-      <c r="AR108" t="n">
-        <v>27.19455146789551</v>
-      </c>
+      <c r="AR108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15563,9 +15349,7 @@
       <c r="AQ109" t="n">
         <v>27.48202896118164</v>
       </c>
-      <c r="AR109" t="n">
-        <v>27.47851181030273</v>
-      </c>
+      <c r="AR109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15703,9 +15487,7 @@
       <c r="AQ110" t="n">
         <v>27.7675895690918</v>
       </c>
-      <c r="AR110" t="n">
-        <v>27.76840972900391</v>
-      </c>
+      <c r="AR110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15843,9 +15625,7 @@
       <c r="AQ111" t="n">
         <v>28.00334167480469</v>
       </c>
-      <c r="AR111" t="n">
-        <v>28.00324058532715</v>
-      </c>
+      <c r="AR111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15983,9 +15763,7 @@
       <c r="AQ112" t="n">
         <v>28.42632293701172</v>
       </c>
-      <c r="AR112" t="n">
-        <v>28.42557525634766</v>
-      </c>
+      <c r="AR112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16123,9 +15901,7 @@
       <c r="AQ113" t="n">
         <v>28.69116592407227</v>
       </c>
-      <c r="AR113" t="n">
-        <v>28.69045257568359</v>
-      </c>
+      <c r="AR113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16263,9 +16039,7 @@
       <c r="AQ114" t="n">
         <v>28.8226203918457</v>
       </c>
-      <c r="AR114" t="n">
-        <v>28.82217025756836</v>
-      </c>
+      <c r="AR114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16403,9 +16177,7 @@
       <c r="AQ115" t="n">
         <v>28.91921234130859</v>
       </c>
-      <c r="AR115" t="n">
-        <v>28.91896820068359</v>
-      </c>
+      <c r="AR115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16543,9 +16315,7 @@
       <c r="AQ116" t="n">
         <v>28.97601127624512</v>
       </c>
-      <c r="AR116" t="n">
-        <v>28.97578811645508</v>
-      </c>
+      <c r="AR116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16685,9 +16455,7 @@
       <c r="AQ117" t="n">
         <v>19.85209274291992</v>
       </c>
-      <c r="AR117" t="n">
-        <v>20.0175666809082</v>
-      </c>
+      <c r="AR117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16825,9 +16593,7 @@
       <c r="AQ118" t="n">
         <v>19.95232772827148</v>
       </c>
-      <c r="AR118" t="n">
-        <v>20.10251235961914</v>
-      </c>
+      <c r="AR118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16967,9 +16733,7 @@
       <c r="AQ119" t="n">
         <v>20.10055160522461</v>
       </c>
-      <c r="AR119" t="n">
-        <v>20.27568626403809</v>
-      </c>
+      <c r="AR119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17109,9 +16873,7 @@
       <c r="AQ120" t="n">
         <v>20.35651588439941</v>
       </c>
-      <c r="AR120" t="n">
-        <v>20.52360153198242</v>
-      </c>
+      <c r="AR120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17249,9 +17011,7 @@
       <c r="AQ121" t="n">
         <v>20.57992362976074</v>
       </c>
-      <c r="AR121" t="n">
-        <v>20.72831535339355</v>
-      </c>
+      <c r="AR121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17389,9 +17149,7 @@
       <c r="AQ122" t="n">
         <v>20.89484596252441</v>
       </c>
-      <c r="AR122" t="n">
-        <v>20.97711753845215</v>
-      </c>
+      <c r="AR122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -17529,9 +17287,7 @@
       <c r="AQ123" t="n">
         <v>21.16396331787109</v>
       </c>
-      <c r="AR123" t="n">
-        <v>21.23835182189941</v>
-      </c>
+      <c r="AR123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17669,9 +17425,7 @@
       <c r="AQ124" t="n">
         <v>21.69884300231934</v>
       </c>
-      <c r="AR124" t="n">
-        <v>21.79372596740723</v>
-      </c>
+      <c r="AR124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17809,9 +17563,7 @@
       <c r="AQ125" t="n">
         <v>22.07812690734863</v>
       </c>
-      <c r="AR125" t="n">
-        <v>22.14472961425781</v>
-      </c>
+      <c r="AR125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17949,9 +17701,7 @@
       <c r="AQ126" t="n">
         <v>22.37998962402344</v>
       </c>
-      <c r="AR126" t="n">
-        <v>22.43406677246094</v>
-      </c>
+      <c r="AR126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -18089,9 +17839,7 @@
       <c r="AQ127" t="n">
         <v>22.65036010742188</v>
       </c>
-      <c r="AR127" t="n">
-        <v>22.68891143798828</v>
-      </c>
+      <c r="AR127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -18229,9 +17977,7 @@
       <c r="AQ128" t="n">
         <v>22.84718894958496</v>
       </c>
-      <c r="AR128" t="n">
-        <v>22.94872856140137</v>
-      </c>
+      <c r="AR128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -18369,9 +18115,7 @@
       <c r="AQ129" t="n">
         <v>23.06948471069336</v>
       </c>
-      <c r="AR129" t="n">
-        <v>23.1647834777832</v>
-      </c>
+      <c r="AR129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -18511,9 +18255,7 @@
       <c r="AQ130" t="n">
         <v>21.49900245666504</v>
       </c>
-      <c r="AR130" t="n">
-        <v>21.59270668029785</v>
-      </c>
+      <c r="AR130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -18651,9 +18393,7 @@
       <c r="AQ131" t="n">
         <v>21.66473197937012</v>
       </c>
-      <c r="AR131" t="n">
-        <v>21.71119689941406</v>
-      </c>
+      <c r="AR131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18793,9 +18533,7 @@
       <c r="AQ132" t="n">
         <v>21.91749954223633</v>
       </c>
-      <c r="AR132" t="n">
-        <v>21.96151161193848</v>
-      </c>
+      <c r="AR132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18935,9 +18673,7 @@
       <c r="AQ133" t="n">
         <v>22.49143981933594</v>
       </c>
-      <c r="AR133" t="n">
-        <v>22.61440467834473</v>
-      </c>
+      <c r="AR133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -19075,9 +18811,7 @@
       <c r="AQ134" t="n">
         <v>22.97998428344727</v>
       </c>
-      <c r="AR134" t="n">
-        <v>23.17134094238281</v>
-      </c>
+      <c r="AR134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -19215,9 +18949,7 @@
       <c r="AQ135" t="n">
         <v>23.3029670715332</v>
       </c>
-      <c r="AR135" t="n">
-        <v>23.48544692993164</v>
-      </c>
+      <c r="AR135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -19355,9 +19087,7 @@
       <c r="AQ136" t="n">
         <v>23.73383331298828</v>
       </c>
-      <c r="AR136" t="n">
-        <v>23.88263702392578</v>
-      </c>
+      <c r="AR136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -19495,9 +19225,7 @@
       <c r="AQ137" t="n">
         <v>26.24082374572754</v>
       </c>
-      <c r="AR137" t="n">
-        <v>26.1425952911377</v>
-      </c>
+      <c r="AR137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -19635,9 +19363,7 @@
       <c r="AQ138" t="n">
         <v>29.25329399108887</v>
       </c>
-      <c r="AR138" t="n">
-        <v>29.11562538146973</v>
-      </c>
+      <c r="AR138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -19775,9 +19501,7 @@
       <c r="AQ139" t="n">
         <v>30.24240303039551</v>
       </c>
-      <c r="AR139" t="n">
-        <v>30.26792907714844</v>
-      </c>
+      <c r="AR139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19915,9 +19639,7 @@
       <c r="AQ140" t="n">
         <v>30.51158142089844</v>
       </c>
-      <c r="AR140" t="n">
-        <v>30.50845718383789</v>
-      </c>
+      <c r="AR140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -20053,9 +19775,7 @@
       <c r="AQ141" t="n">
         <v>30.59122848510742</v>
       </c>
-      <c r="AR141" t="n">
-        <v>30.57632637023926</v>
-      </c>
+      <c r="AR141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -20193,9 +19913,7 @@
       <c r="AQ142" t="n">
         <v>20.99753570556641</v>
       </c>
-      <c r="AR142" t="n">
-        <v>19.84826278686523</v>
-      </c>
+      <c r="AR142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -20333,9 +20051,7 @@
       <c r="AQ143" t="n">
         <v>20.99753570556641</v>
       </c>
-      <c r="AR143" t="n">
-        <v>19.84826278686523</v>
-      </c>
+      <c r="AR143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -20475,9 +20191,7 @@
       <c r="AQ144" t="n">
         <v>21.2316951751709</v>
       </c>
-      <c r="AR144" t="n">
-        <v>20.17424964904785</v>
-      </c>
+      <c r="AR144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -20617,9 +20331,7 @@
       <c r="AQ145" t="n">
         <v>21.65328788757324</v>
       </c>
-      <c r="AR145" t="n">
-        <v>20.78697967529297</v>
-      </c>
+      <c r="AR145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -20757,9 +20469,7 @@
       <c r="AQ146" t="n">
         <v>22.34049415588379</v>
       </c>
-      <c r="AR146" t="n">
-        <v>22.16703987121582</v>
-      </c>
+      <c r="AR146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -20897,9 +20607,7 @@
       <c r="AQ147" t="n">
         <v>22.76232528686523</v>
       </c>
-      <c r="AR147" t="n">
-        <v>22.6712818145752</v>
-      </c>
+      <c r="AR147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -21037,9 +20745,7 @@
       <c r="AQ148" t="n">
         <v>23.12858772277832</v>
       </c>
-      <c r="AR148" t="n">
-        <v>23.04530143737793</v>
-      </c>
+      <c r="AR148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -21177,9 +20883,7 @@
       <c r="AQ149" t="n">
         <v>23.64399337768555</v>
       </c>
-      <c r="AR149" t="n">
-        <v>23.73536109924316</v>
-      </c>
+      <c r="AR149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -21317,9 +21021,7 @@
       <c r="AQ150" t="n">
         <v>25.9908275604248</v>
       </c>
-      <c r="AR150" t="n">
-        <v>26.29140853881836</v>
-      </c>
+      <c r="AR150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -21457,9 +21159,7 @@
       <c r="AQ151" t="n">
         <v>28.84749412536621</v>
       </c>
-      <c r="AR151" t="n">
-        <v>28.98785018920898</v>
-      </c>
+      <c r="AR151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -21597,9 +21297,7 @@
       <c r="AQ152" t="n">
         <v>30.91207885742188</v>
       </c>
-      <c r="AR152" t="n">
-        <v>30.92365074157715</v>
-      </c>
+      <c r="AR152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -21737,9 +21435,7 @@
       <c r="AQ153" t="n">
         <v>31.43169975280762</v>
       </c>
-      <c r="AR153" t="n">
-        <v>31.40225028991699</v>
-      </c>
+      <c r="AR153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -21875,9 +21571,7 @@
       <c r="AQ154" t="n">
         <v>31.52877426147461</v>
       </c>
-      <c r="AR154" t="n">
-        <v>31.50172424316406</v>
-      </c>
+      <c r="AR154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -22013,9 +21707,7 @@
       <c r="AQ155" t="n">
         <v>31.52877426147461</v>
       </c>
-      <c r="AR155" t="n">
-        <v>31.50172424316406</v>
-      </c>
+      <c r="AR155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -22155,9 +21847,7 @@
       <c r="AQ156" t="n">
         <v>20.36337852478027</v>
       </c>
-      <c r="AR156" t="n">
-        <v>20.45420265197754</v>
-      </c>
+      <c r="AR156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -22295,9 +21985,7 @@
       <c r="AQ157" t="n">
         <v>20.5545825958252</v>
       </c>
-      <c r="AR157" t="n">
-        <v>20.61775207519531</v>
-      </c>
+      <c r="AR157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -22437,9 +22125,7 @@
       <c r="AQ158" t="n">
         <v>20.8983211517334</v>
       </c>
-      <c r="AR158" t="n">
-        <v>20.91645622253418</v>
-      </c>
+      <c r="AR158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -22579,9 +22265,7 @@
       <c r="AQ159" t="n">
         <v>21.50336456298828</v>
       </c>
-      <c r="AR159" t="n">
-        <v>21.58509826660156</v>
-      </c>
+      <c r="AR159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -22719,9 +22403,7 @@
       <c r="AQ160" t="n">
         <v>22.07012939453125</v>
       </c>
-      <c r="AR160" t="n">
-        <v>22.19605827331543</v>
-      </c>
+      <c r="AR160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -22853,9 +22535,7 @@
       <c r="AQ161" t="n">
         <v>23.15775871276855</v>
       </c>
-      <c r="AR161" t="n">
-        <v>23.31867027282715</v>
-      </c>
+      <c r="AR161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -22993,9 +22673,7 @@
       <c r="AQ162" t="n">
         <v>24.20733642578125</v>
       </c>
-      <c r="AR162" t="n">
-        <v>24.36017799377441</v>
-      </c>
+      <c r="AR162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -23133,9 +22811,7 @@
       <c r="AQ163" t="n">
         <v>26.51087760925293</v>
       </c>
-      <c r="AR163" t="n">
-        <v>26.63624000549316</v>
-      </c>
+      <c r="AR163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -23273,9 +22949,7 @@
       <c r="AQ164" t="n">
         <v>27.60127449035645</v>
       </c>
-      <c r="AR164" t="n">
-        <v>27.59258079528809</v>
-      </c>
+      <c r="AR164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -23409,9 +23083,7 @@
       <c r="AQ165" t="n">
         <v>27.67102432250977</v>
       </c>
-      <c r="AR165" t="n">
-        <v>27.70675849914551</v>
-      </c>
+      <c r="AR165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -23551,9 +23223,7 @@
       <c r="AQ166" t="n">
         <v>19.62225914001465</v>
       </c>
-      <c r="AR166" t="n">
-        <v>19.76165962219238</v>
-      </c>
+      <c r="AR166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -23691,9 +23361,7 @@
       <c r="AQ167" t="n">
         <v>19.66095733642578</v>
       </c>
-      <c r="AR167" t="n">
-        <v>19.80722808837891</v>
-      </c>
+      <c r="AR167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -23833,9 +23501,7 @@
       <c r="AQ168" t="n">
         <v>19.7941780090332</v>
       </c>
-      <c r="AR168" t="n">
-        <v>19.96520614624023</v>
-      </c>
+      <c r="AR168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -23975,9 +23641,7 @@
       <c r="AQ169" t="n">
         <v>20.51756477355957</v>
       </c>
-      <c r="AR169" t="n">
-        <v>20.64373397827148</v>
-      </c>
+      <c r="AR169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -24115,9 +23779,7 @@
       <c r="AQ170" t="n">
         <v>21.44605445861816</v>
       </c>
-      <c r="AR170" t="n">
-        <v>21.61241340637207</v>
-      </c>
+      <c r="AR170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -24255,9 +23917,7 @@
       <c r="AQ171" t="n">
         <v>22.34055519104004</v>
       </c>
-      <c r="AR171" t="n">
-        <v>22.4568042755127</v>
-      </c>
+      <c r="AR171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -24395,9 +24055,7 @@
       <c r="AQ172" t="n">
         <v>23.03812408447266</v>
       </c>
-      <c r="AR172" t="n">
-        <v>23.15120124816895</v>
-      </c>
+      <c r="AR172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -24535,9 +24193,7 @@
       <c r="AQ173" t="n">
         <v>25.35152816772461</v>
       </c>
-      <c r="AR173" t="n">
-        <v>25.381591796875</v>
-      </c>
+      <c r="AR173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -24675,9 +24331,7 @@
       <c r="AQ174" t="n">
         <v>26.70055389404297</v>
       </c>
-      <c r="AR174" t="n">
-        <v>26.74572563171387</v>
-      </c>
+      <c r="AR174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -24815,9 +24469,7 @@
       <c r="AQ175" t="n">
         <v>27.00031280517578</v>
       </c>
-      <c r="AR175" t="n">
-        <v>27.03853988647461</v>
-      </c>
+      <c r="AR175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -24957,9 +24609,7 @@
       <c r="AQ176" t="n">
         <v>20.63822937011719</v>
       </c>
-      <c r="AR176" t="n">
-        <v>20.77776527404785</v>
-      </c>
+      <c r="AR176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -25097,9 +24747,7 @@
       <c r="AQ177" t="n">
         <v>20.6913890838623</v>
       </c>
-      <c r="AR177" t="n">
-        <v>20.83094215393066</v>
-      </c>
+      <c r="AR177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -25239,9 +24887,7 @@
       <c r="AQ178" t="n">
         <v>20.77734565734863</v>
       </c>
-      <c r="AR178" t="n">
-        <v>20.95253372192383</v>
-      </c>
+      <c r="AR178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -25381,9 +25027,7 @@
       <c r="AQ179" t="n">
         <v>21.00918579101562</v>
       </c>
-      <c r="AR179" t="n">
-        <v>21.19582366943359</v>
-      </c>
+      <c r="AR179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -25521,9 +25165,7 @@
       <c r="AQ180" t="n">
         <v>21.16812515258789</v>
       </c>
-      <c r="AR180" t="n">
-        <v>21.36877059936523</v>
-      </c>
+      <c r="AR180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -25661,9 +25303,7 @@
       <c r="AQ181" t="n">
         <v>21.33024406433105</v>
       </c>
-      <c r="AR181" t="n">
-        <v>21.51827812194824</v>
-      </c>
+      <c r="AR181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -25801,9 +25441,7 @@
       <c r="AQ182" t="n">
         <v>21.47179412841797</v>
       </c>
-      <c r="AR182" t="n">
-        <v>21.63014602661133</v>
-      </c>
+      <c r="AR182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -25941,9 +25579,7 @@
       <c r="AQ183" t="n">
         <v>21.69080924987793</v>
       </c>
-      <c r="AR183" t="n">
-        <v>21.81686210632324</v>
-      </c>
+      <c r="AR183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -26081,9 +25717,7 @@
       <c r="AQ184" t="n">
         <v>21.96330642700195</v>
       </c>
-      <c r="AR184" t="n">
-        <v>22.10865783691406</v>
-      </c>
+      <c r="AR184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -26221,9 +25855,7 @@
       <c r="AQ185" t="n">
         <v>22.1417293548584</v>
       </c>
-      <c r="AR185" t="n">
-        <v>22.27150917053223</v>
-      </c>
+      <c r="AR185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -26355,9 +25987,7 @@
       <c r="AQ186" t="n">
         <v>22.31901741027832</v>
       </c>
-      <c r="AR186" t="n">
-        <v>22.44016647338867</v>
-      </c>
+      <c r="AR186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -26495,9 +26125,7 @@
       <c r="AQ187" t="n">
         <v>22.45622634887695</v>
       </c>
-      <c r="AR187" t="n">
-        <v>22.53686714172363</v>
-      </c>
+      <c r="AR187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -26633,9 +26261,7 @@
       <c r="AQ188" t="n">
         <v>22.48510932922363</v>
       </c>
-      <c r="AR188" t="n">
-        <v>22.55825042724609</v>
-      </c>
+      <c r="AR188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -26775,9 +26401,7 @@
       <c r="AQ189" t="n">
         <v>18.58720207214355</v>
       </c>
-      <c r="AR189" t="n">
-        <v>19.06708526611328</v>
-      </c>
+      <c r="AR189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -26915,9 +26539,7 @@
       <c r="AQ190" t="n">
         <v>18.80278778076172</v>
       </c>
-      <c r="AR190" t="n">
-        <v>19.08579444885254</v>
-      </c>
+      <c r="AR190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -27057,9 +26679,7 @@
       <c r="AQ191" t="n">
         <v>19.65059089660645</v>
       </c>
-      <c r="AR191" t="n">
-        <v>19.74838066101074</v>
-      </c>
+      <c r="AR191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -27199,9 +26819,7 @@
       <c r="AQ192" t="n">
         <v>20.81158256530762</v>
       </c>
-      <c r="AR192" t="n">
-        <v>21.35251998901367</v>
-      </c>
+      <c r="AR192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -27339,9 +26957,7 @@
       <c r="AQ193" t="n">
         <v>21.39556884765625</v>
       </c>
-      <c r="AR193" t="n">
-        <v>21.82449531555176</v>
-      </c>
+      <c r="AR193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -27479,9 +27095,7 @@
       <c r="AQ194" t="n">
         <v>21.94051933288574</v>
       </c>
-      <c r="AR194" t="n">
-        <v>22.11066627502441</v>
-      </c>
+      <c r="AR194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -27619,9 +27233,7 @@
       <c r="AQ195" t="n">
         <v>22.28800964355469</v>
       </c>
-      <c r="AR195" t="n">
-        <v>22.31545066833496</v>
-      </c>
+      <c r="AR195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -27759,9 +27371,7 @@
       <c r="AQ196" t="n">
         <v>22.92724418640137</v>
       </c>
-      <c r="AR196" t="n">
-        <v>22.93797874450684</v>
-      </c>
+      <c r="AR196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -27899,9 +27509,7 @@
       <c r="AQ197" t="n">
         <v>23.67417335510254</v>
       </c>
-      <c r="AR197" t="n">
-        <v>23.91695022583008</v>
-      </c>
+      <c r="AR197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -28039,9 +27647,7 @@
       <c r="AQ198" t="n">
         <v>24.85447311401367</v>
       </c>
-      <c r="AR198" t="n">
-        <v>25.14284706115723</v>
-      </c>
+      <c r="AR198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -28179,9 +27785,7 @@
       <c r="AQ199" t="n">
         <v>26.24236679077148</v>
       </c>
-      <c r="AR199" t="n">
-        <v>26.48683738708496</v>
-      </c>
+      <c r="AR199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -28317,9 +27921,7 @@
       <c r="AQ200" t="n">
         <v>26.66815376281738</v>
       </c>
-      <c r="AR200" t="n">
-        <v>26.8785285949707</v>
-      </c>
+      <c r="AR200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -28459,9 +28061,7 @@
       <c r="AQ201" t="n">
         <v>10.39869117736816</v>
       </c>
-      <c r="AR201" t="n">
-        <v>10.86268138885498</v>
-      </c>
+      <c r="AR201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -28599,9 +28199,7 @@
       <c r="AQ202" t="n">
         <v>10.61744785308838</v>
       </c>
-      <c r="AR202" t="n">
-        <v>10.89494037628174</v>
-      </c>
+      <c r="AR202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -28741,9 +28339,7 @@
       <c r="AQ203" t="n">
         <v>13.29244327545166</v>
       </c>
-      <c r="AR203" t="n">
-        <v>17.23537445068359</v>
-      </c>
+      <c r="AR203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -28883,9 +28479,7 @@
       <c r="AQ204" t="n">
         <v>23.46282005310059</v>
       </c>
-      <c r="AR204" t="n">
-        <v>23.75841331481934</v>
-      </c>
+      <c r="AR204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -29023,9 +28617,7 @@
       <c r="AQ205" t="n">
         <v>24.93439483642578</v>
       </c>
-      <c r="AR205" t="n">
-        <v>26.01395988464355</v>
-      </c>
+      <c r="AR205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -29163,9 +28755,7 @@
       <c r="AQ206" t="n">
         <v>25.15958786010742</v>
       </c>
-      <c r="AR206" t="n">
-        <v>26.16933059692383</v>
-      </c>
+      <c r="AR206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -29303,9 +28893,7 @@
       <c r="AQ207" t="n">
         <v>24.68145179748535</v>
       </c>
-      <c r="AR207" t="n">
-        <v>25.94502449035645</v>
-      </c>
+      <c r="AR207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -29443,9 +29031,7 @@
       <c r="AQ208" t="n">
         <v>23.91292572021484</v>
       </c>
-      <c r="AR208" t="n">
-        <v>24.92868995666504</v>
-      </c>
+      <c r="AR208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -29583,9 +29169,7 @@
       <c r="AQ209" t="n">
         <v>25.0840015411377</v>
       </c>
-      <c r="AR209" t="n">
-        <v>25.28367042541504</v>
-      </c>
+      <c r="AR209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -29723,9 +29307,7 @@
       <c r="AQ210" t="n">
         <v>26.19154167175293</v>
       </c>
-      <c r="AR210" t="n">
-        <v>26.1038990020752</v>
-      </c>
+      <c r="AR210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -29863,9 +29445,7 @@
       <c r="AQ211" t="n">
         <v>26.68475532531738</v>
       </c>
-      <c r="AR211" t="n">
-        <v>26.71178817749023</v>
-      </c>
+      <c r="AR211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -30001,9 +29581,7 @@
       <c r="AQ212" t="n">
         <v>27.39163970947266</v>
       </c>
-      <c r="AR212" t="n">
-        <v>27.4033031463623</v>
-      </c>
+      <c r="AR212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -30141,9 +29719,7 @@
       <c r="AQ213" t="n">
         <v>27.90624618530273</v>
       </c>
-      <c r="AR213" t="n">
-        <v>28.08604431152344</v>
-      </c>
+      <c r="AR213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -30281,9 +29857,7 @@
       <c r="AQ214" t="n">
         <v>28.46711540222168</v>
       </c>
-      <c r="AR214" t="n">
-        <v>28.61275672912598</v>
-      </c>
+      <c r="AR214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -30421,9 +29995,7 @@
       <c r="AQ215" t="n">
         <v>28.70810699462891</v>
       </c>
-      <c r="AR215" t="n">
-        <v>28.80655097961426</v>
-      </c>
+      <c r="AR215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -30559,9 +30131,7 @@
       <c r="AQ216" t="n">
         <v>28.73069000244141</v>
       </c>
-      <c r="AR216" t="n">
-        <v>28.82231521606445</v>
-      </c>
+      <c r="AR216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -30701,9 +30271,7 @@
       <c r="AQ217" t="n">
         <v>17.93804550170898</v>
       </c>
-      <c r="AR217" t="n">
-        <v>19.73898506164551</v>
-      </c>
+      <c r="AR217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -30841,9 +30409,7 @@
       <c r="AQ218" t="n">
         <v>19.88368797302246</v>
       </c>
-      <c r="AR218" t="n">
-        <v>20.83019638061523</v>
-      </c>
+      <c r="AR218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -30983,9 +30549,7 @@
       <c r="AQ219" t="n">
         <v>20.81304550170898</v>
       </c>
-      <c r="AR219" t="n">
-        <v>21.66334342956543</v>
-      </c>
+      <c r="AR219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -31125,9 +30689,7 @@
       <c r="AQ220" t="n">
         <v>23.39485740661621</v>
       </c>
-      <c r="AR220" t="n">
-        <v>22.94942283630371</v>
-      </c>
+      <c r="AR220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -31259,9 +30821,7 @@
       <c r="AQ221" t="n">
         <v>25.65460968017578</v>
       </c>
-      <c r="AR221" t="n">
-        <v>25.15693283081055</v>
-      </c>
+      <c r="AR221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -31399,9 +30959,7 @@
       <c r="AQ222" t="n">
         <v>26.42144584655762</v>
       </c>
-      <c r="AR222" t="n">
-        <v>26.29336547851562</v>
-      </c>
+      <c r="AR222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -31533,9 +31091,7 @@
       <c r="AQ223" t="n">
         <v>26.91451263427734</v>
       </c>
-      <c r="AR223" t="n">
-        <v>26.84167098999023</v>
-      </c>
+      <c r="AR223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -31673,9 +31229,7 @@
       <c r="AQ224" t="n">
         <v>26.88815307617188</v>
       </c>
-      <c r="AR224" t="n">
-        <v>26.94168853759766</v>
-      </c>
+      <c r="AR224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -31813,9 +31367,7 @@
       <c r="AQ225" t="n">
         <v>26.68624305725098</v>
       </c>
-      <c r="AR225" t="n">
-        <v>26.62338066101074</v>
-      </c>
+      <c r="AR225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -31953,9 +31505,7 @@
       <c r="AQ226" t="n">
         <v>26.4976921081543</v>
       </c>
-      <c r="AR226" t="n">
-        <v>26.45084571838379</v>
-      </c>
+      <c r="AR226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -32093,9 +31643,7 @@
       <c r="AQ227" t="n">
         <v>26.87140464782715</v>
       </c>
-      <c r="AR227" t="n">
-        <v>26.81219100952148</v>
-      </c>
+      <c r="AR227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -32233,9 +31781,7 @@
       <c r="AQ228" t="n">
         <v>27.08657073974609</v>
       </c>
-      <c r="AR228" t="n">
-        <v>27.05036163330078</v>
-      </c>
+      <c r="AR228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -32373,9 +31919,7 @@
       <c r="AQ229" t="n">
         <v>27.22974395751953</v>
       </c>
-      <c r="AR229" t="n">
-        <v>27.25403022766113</v>
-      </c>
+      <c r="AR229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -32513,9 +32057,7 @@
       <c r="AQ230" t="n">
         <v>28.10054206848145</v>
       </c>
-      <c r="AR230" t="n">
-        <v>27.85015869140625</v>
-      </c>
+      <c r="AR230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -32653,9 +32195,7 @@
       <c r="AQ231" t="n">
         <v>28.75100898742676</v>
       </c>
-      <c r="AR231" t="n">
-        <v>28.75038146972656</v>
-      </c>
+      <c r="AR231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -32793,9 +32333,7 @@
       <c r="AQ232" t="n">
         <v>28.92733383178711</v>
       </c>
-      <c r="AR232" t="n">
-        <v>28.93895530700684</v>
-      </c>
+      <c r="AR232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -32931,9 +32469,7 @@
       <c r="AQ233" t="n">
         <v>28.93276786804199</v>
       </c>
-      <c r="AR233" t="n">
-        <v>28.94395065307617</v>
-      </c>
+      <c r="AR233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -33059,9 +32595,7 @@
       <c r="AQ234" t="n">
         <v>8.281889915466309</v>
       </c>
-      <c r="AR234" t="n">
-        <v>7.085296630859375</v>
-      </c>
+      <c r="AR234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -33187,9 +32721,7 @@
       <c r="AQ235" t="n">
         <v>19.55489158630371</v>
       </c>
-      <c r="AR235" t="n">
-        <v>17.5417366027832</v>
-      </c>
+      <c r="AR235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -33315,9 +32847,7 @@
       <c r="AQ236" t="n">
         <v>23.53064346313477</v>
       </c>
-      <c r="AR236" t="n">
-        <v>25.04595947265625</v>
-      </c>
+      <c r="AR236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -33457,9 +32987,7 @@
       <c r="AQ237" t="n">
         <v>9.333398818969727</v>
       </c>
-      <c r="AR237" t="n">
-        <v>6.17535924911499</v>
-      </c>
+      <c r="AR237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -33597,9 +33125,7 @@
       <c r="AQ238" t="n">
         <v>10.81204605102539</v>
       </c>
-      <c r="AR238" t="n">
-        <v>6.308191299438477</v>
-      </c>
+      <c r="AR238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -33739,9 +33265,7 @@
       <c r="AQ239" t="n">
         <v>15.10553932189941</v>
       </c>
-      <c r="AR239" t="n">
-        <v>7.66474437713623</v>
-      </c>
+      <c r="AR239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -33881,9 +33405,7 @@
       <c r="AQ240" t="n">
         <v>24.05141830444336</v>
       </c>
-      <c r="AR240" t="n">
-        <v>22.06073570251465</v>
-      </c>
+      <c r="AR240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -34021,9 +33543,7 @@
       <c r="AQ241" t="n">
         <v>26.69393539428711</v>
       </c>
-      <c r="AR241" t="n">
-        <v>25.18575668334961</v>
-      </c>
+      <c r="AR241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -34161,9 +33681,7 @@
       <c r="AQ242" t="n">
         <v>27.26567840576172</v>
       </c>
-      <c r="AR242" t="n">
-        <v>26.61536026000977</v>
-      </c>
+      <c r="AR242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -34301,9 +33819,7 @@
       <c r="AQ243" t="n">
         <v>27.37546539306641</v>
       </c>
-      <c r="AR243" t="n">
-        <v>27.26764297485352</v>
-      </c>
+      <c r="AR243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -34441,9 +33957,7 @@
       <c r="AQ244" t="n">
         <v>27.17772674560547</v>
       </c>
-      <c r="AR244" t="n">
-        <v>27.38669586181641</v>
-      </c>
+      <c r="AR244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -34581,9 +34095,7 @@
       <c r="AQ245" t="n">
         <v>26.88192749023438</v>
       </c>
-      <c r="AR245" t="n">
-        <v>27.23006057739258</v>
-      </c>
+      <c r="AR245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -34721,9 +34233,7 @@
       <c r="AQ246" t="n">
         <v>26.95013236999512</v>
       </c>
-      <c r="AR246" t="n">
-        <v>27.35849571228027</v>
-      </c>
+      <c r="AR246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -34861,9 +34371,7 @@
       <c r="AQ247" t="n">
         <v>27.1968994140625</v>
       </c>
-      <c r="AR247" t="n">
-        <v>27.62787437438965</v>
-      </c>
+      <c r="AR247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -35001,9 +34509,7 @@
       <c r="AQ248" t="n">
         <v>27.80367279052734</v>
       </c>
-      <c r="AR248" t="n">
-        <v>28.23693656921387</v>
-      </c>
+      <c r="AR248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -35141,9 +34647,7 @@
       <c r="AQ249" t="n">
         <v>28.54760932922363</v>
       </c>
-      <c r="AR249" t="n">
-        <v>28.6979808807373</v>
-      </c>
+      <c r="AR249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -35281,9 +34785,7 @@
       <c r="AQ250" t="n">
         <v>28.95224571228027</v>
       </c>
-      <c r="AR250" t="n">
-        <v>28.9337329864502</v>
-      </c>
+      <c r="AR250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -35421,9 +34923,7 @@
       <c r="AQ251" t="n">
         <v>28.96767234802246</v>
       </c>
-      <c r="AR251" t="n">
-        <v>28.95605278015137</v>
-      </c>
+      <c r="AR251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -35561,9 +35061,7 @@
       <c r="AQ252" t="n">
         <v>28.95707321166992</v>
       </c>
-      <c r="AR252" t="n">
-        <v>28.9558048248291</v>
-      </c>
+      <c r="AR252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -35697,9 +35195,7 @@
       <c r="AQ253" t="n">
         <v>9.265677452087402</v>
       </c>
-      <c r="AR253" t="n">
-        <v>5.115707874298096</v>
-      </c>
+      <c r="AR253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -35833,9 +35329,7 @@
       <c r="AQ254" t="n">
         <v>15.26477527618408</v>
       </c>
-      <c r="AR254" t="n">
-        <v>9.41081714630127</v>
-      </c>
+      <c r="AR254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -35969,9 +35463,7 @@
       <c r="AQ255" t="n">
         <v>21.39492416381836</v>
       </c>
-      <c r="AR255" t="n">
-        <v>20.47307205200195</v>
-      </c>
+      <c r="AR255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -36111,9 +35603,7 @@
       <c r="AQ256" t="n">
         <v>13.58145523071289</v>
       </c>
-      <c r="AR256" t="n">
-        <v>9.162424087524414</v>
-      </c>
+      <c r="AR256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -36251,9 +35741,7 @@
       <c r="AQ257" t="n">
         <v>15.59268665313721</v>
       </c>
-      <c r="AR257" t="n">
-        <v>14.10024452209473</v>
-      </c>
+      <c r="AR257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -36393,9 +35881,7 @@
       <c r="AQ258" t="n">
         <v>17.70902442932129</v>
       </c>
-      <c r="AR258" t="n">
-        <v>20.58547973632812</v>
-      </c>
+      <c r="AR258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -36535,9 +36021,7 @@
       <c r="AQ259" t="n">
         <v>21.66425514221191</v>
       </c>
-      <c r="AR259" t="n">
-        <v>22.7480525970459</v>
-      </c>
+      <c r="AR259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -36675,9 +36159,7 @@
       <c r="AQ260" t="n">
         <v>24.70704078674316</v>
       </c>
-      <c r="AR260" t="n">
-        <v>23.88590812683105</v>
-      </c>
+      <c r="AR260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -36815,9 +36297,7 @@
       <c r="AQ261" t="n">
         <v>26.6652717590332</v>
       </c>
-      <c r="AR261" t="n">
-        <v>26.06771087646484</v>
-      </c>
+      <c r="AR261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -36955,9 +36435,7 @@
       <c r="AQ262" t="n">
         <v>27.64896392822266</v>
       </c>
-      <c r="AR262" t="n">
-        <v>27.49083137512207</v>
-      </c>
+      <c r="AR262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -37095,9 +36573,7 @@
       <c r="AQ263" t="n">
         <v>27.86395835876465</v>
       </c>
-      <c r="AR263" t="n">
-        <v>27.93557548522949</v>
-      </c>
+      <c r="AR263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -37235,9 +36711,7 @@
       <c r="AQ264" t="n">
         <v>27.66209983825684</v>
       </c>
-      <c r="AR264" t="n">
-        <v>27.69440460205078</v>
-      </c>
+      <c r="AR264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -37371,9 +36845,7 @@
       <c r="AQ265" t="n">
         <v>27.65321159362793</v>
       </c>
-      <c r="AR265" t="n">
-        <v>27.60641860961914</v>
-      </c>
+      <c r="AR265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -37511,9 +36983,7 @@
       <c r="AQ266" t="n">
         <v>27.88377952575684</v>
       </c>
-      <c r="AR266" t="n">
-        <v>27.97199821472168</v>
-      </c>
+      <c r="AR266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -37651,9 +37121,7 @@
       <c r="AQ267" t="n">
         <v>28.0670108795166</v>
       </c>
-      <c r="AR267" t="n">
-        <v>28.26223564147949</v>
-      </c>
+      <c r="AR267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -37791,9 +37259,7 @@
       <c r="AQ268" t="n">
         <v>28.5823917388916</v>
       </c>
-      <c r="AR268" t="n">
-        <v>28.57455635070801</v>
-      </c>
+      <c r="AR268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -37931,9 +37397,7 @@
       <c r="AQ269" t="n">
         <v>28.95543670654297</v>
       </c>
-      <c r="AR269" t="n">
-        <v>28.93342208862305</v>
-      </c>
+      <c r="AR269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -38071,9 +37535,7 @@
       <c r="AQ270" t="n">
         <v>28.99483489990234</v>
       </c>
-      <c r="AR270" t="n">
-        <v>28.98138236999512</v>
-      </c>
+      <c r="AR270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -38205,9 +37667,7 @@
       <c r="AQ271" t="n">
         <v>6.212727069854736</v>
       </c>
-      <c r="AR271" t="n">
-        <v>6.440130233764648</v>
-      </c>
+      <c r="AR271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -38339,9 +37799,7 @@
       <c r="AQ272" t="n">
         <v>8.400172233581543</v>
       </c>
-      <c r="AR272" t="n">
-        <v>8.592650413513184</v>
-      </c>
+      <c r="AR272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -38473,9 +37931,7 @@
       <c r="AQ273" t="n">
         <v>9.904959678649902</v>
       </c>
-      <c r="AR273" t="n">
-        <v>9.970112800598145</v>
-      </c>
+      <c r="AR273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -38609,9 +38065,7 @@
       <c r="AQ274" t="n">
         <v>17.74823188781738</v>
       </c>
-      <c r="AR274" t="n">
-        <v>16.80356407165527</v>
-      </c>
+      <c r="AR274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -38745,9 +38199,7 @@
       <c r="AQ275" t="n">
         <v>17.74395179748535</v>
       </c>
-      <c r="AR275" t="n">
-        <v>17.39723777770996</v>
-      </c>
+      <c r="AR275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -38881,9 +38333,7 @@
       <c r="AQ276" t="n">
         <v>19.35729598999023</v>
       </c>
-      <c r="AR276" t="n">
-        <v>19.20693206787109</v>
-      </c>
+      <c r="AR276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -39023,9 +38473,7 @@
       <c r="AQ277" t="n">
         <v>21.39465713500977</v>
       </c>
-      <c r="AR277" t="n">
-        <v>21.07559394836426</v>
-      </c>
+      <c r="AR277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -39161,9 +38609,7 @@
       <c r="AQ278" t="n">
         <v>21.49865913391113</v>
       </c>
-      <c r="AR278" t="n">
-        <v>20.90409088134766</v>
-      </c>
+      <c r="AR278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -39303,9 +38749,7 @@
       <c r="AQ279" t="n">
         <v>21.75945091247559</v>
       </c>
-      <c r="AR279" t="n">
-        <v>21.10702896118164</v>
-      </c>
+      <c r="AR279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -39443,9 +38887,7 @@
       <c r="AQ280" t="n">
         <v>22.24102973937988</v>
       </c>
-      <c r="AR280" t="n">
-        <v>22.11010360717773</v>
-      </c>
+      <c r="AR280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -39583,9 +39025,7 @@
       <c r="AQ281" t="n">
         <v>22.64977645874023</v>
       </c>
-      <c r="AR281" t="n">
-        <v>22.80722999572754</v>
-      </c>
+      <c r="AR281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -39723,9 +39163,7 @@
       <c r="AQ282" t="n">
         <v>23.11606216430664</v>
       </c>
-      <c r="AR282" t="n">
-        <v>23.3430347442627</v>
-      </c>
+      <c r="AR282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -39863,9 +39301,7 @@
       <c r="AQ283" t="n">
         <v>23.63935089111328</v>
       </c>
-      <c r="AR283" t="n">
-        <v>23.90115165710449</v>
-      </c>
+      <c r="AR283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -40003,9 +39439,7 @@
       <c r="AQ284" t="n">
         <v>25.32576370239258</v>
       </c>
-      <c r="AR284" t="n">
-        <v>25.30307960510254</v>
-      </c>
+      <c r="AR284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -40143,9 +39577,7 @@
       <c r="AQ285" t="n">
         <v>26.34713554382324</v>
       </c>
-      <c r="AR285" t="n">
-        <v>26.27021408081055</v>
-      </c>
+      <c r="AR285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -40283,9 +39715,7 @@
       <c r="AQ286" t="n">
         <v>27.6147575378418</v>
       </c>
-      <c r="AR286" t="n">
-        <v>27.59025764465332</v>
-      </c>
+      <c r="AR286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -40421,9 +39851,7 @@
       <c r="AQ287" t="n">
         <v>28.15756225585938</v>
       </c>
-      <c r="AR287" t="n">
-        <v>28.12608909606934</v>
-      </c>
+      <c r="AR287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -40563,9 +39991,7 @@
       <c r="AQ288" t="n">
         <v>21.02042770385742</v>
       </c>
-      <c r="AR288" t="n">
-        <v>18.41376113891602</v>
-      </c>
+      <c r="AR288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -40703,9 +40129,7 @@
       <c r="AQ289" t="n">
         <v>21.05565452575684</v>
       </c>
-      <c r="AR289" t="n">
-        <v>19.10119438171387</v>
-      </c>
+      <c r="AR289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -40845,9 +40269,7 @@
       <c r="AQ290" t="n">
         <v>21.13389015197754</v>
       </c>
-      <c r="AR290" t="n">
-        <v>20.28373908996582</v>
-      </c>
+      <c r="AR290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -40987,9 +40409,7 @@
       <c r="AQ291" t="n">
         <v>21.6538028717041</v>
       </c>
-      <c r="AR291" t="n">
-        <v>21.69460105895996</v>
-      </c>
+      <c r="AR291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -41127,9 +40547,7 @@
       <c r="AQ292" t="n">
         <v>22.43695259094238</v>
       </c>
-      <c r="AR292" t="n">
-        <v>22.65316009521484</v>
-      </c>
+      <c r="AR292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -41265,9 +40683,7 @@
       <c r="AQ293" t="n">
         <v>23.15833282470703</v>
       </c>
-      <c r="AR293" t="n">
-        <v>23.01544761657715</v>
-      </c>
+      <c r="AR293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -41405,9 +40821,7 @@
       <c r="AQ294" t="n">
         <v>23.67590713500977</v>
       </c>
-      <c r="AR294" t="n">
-        <v>23.40873527526855</v>
-      </c>
+      <c r="AR294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -41545,9 +40959,7 @@
       <c r="AQ295" t="n">
         <v>25.21731948852539</v>
       </c>
-      <c r="AR295" t="n">
-        <v>25.20565605163574</v>
-      </c>
+      <c r="AR295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -41685,9 +41097,7 @@
       <c r="AQ296" t="n">
         <v>27.73063468933105</v>
       </c>
-      <c r="AR296" t="n">
-        <v>27.77385520935059</v>
-      </c>
+      <c r="AR296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -41825,9 +41235,7 @@
       <c r="AQ297" t="n">
         <v>28.43346405029297</v>
       </c>
-      <c r="AR297" t="n">
-        <v>28.53417778015137</v>
-      </c>
+      <c r="AR297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -41965,9 +41373,7 @@
       <c r="AQ298" t="n">
         <v>28.53670501708984</v>
       </c>
-      <c r="AR298" t="n">
-        <v>28.68112564086914</v>
-      </c>
+      <c r="AR298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -42105,9 +41511,7 @@
       <c r="AQ299" t="n">
         <v>28.61967086791992</v>
       </c>
-      <c r="AR299" t="n">
-        <v>28.69084739685059</v>
-      </c>
+      <c r="AR299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -42245,9 +41649,7 @@
       <c r="AQ300" t="n">
         <v>28.69346046447754</v>
       </c>
-      <c r="AR300" t="n">
-        <v>28.73892211914062</v>
-      </c>
+      <c r="AR300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -42385,9 +41787,7 @@
       <c r="AQ301" t="n">
         <v>28.81461715698242</v>
       </c>
-      <c r="AR301" t="n">
-        <v>28.81305503845215</v>
-      </c>
+      <c r="AR301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -42523,9 +41923,7 @@
       <c r="AQ302" t="n">
         <v>28.87404632568359</v>
       </c>
-      <c r="AR302" t="n">
-        <v>28.86668968200684</v>
-      </c>
+      <c r="AR302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -42665,9 +42063,7 @@
       <c r="AQ303" t="n">
         <v>15.12353038787842</v>
       </c>
-      <c r="AR303" t="n">
-        <v>14.45601177215576</v>
-      </c>
+      <c r="AR303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -42805,9 +42201,7 @@
       <c r="AQ304" t="n">
         <v>15.59210205078125</v>
       </c>
-      <c r="AR304" t="n">
-        <v>15.16129684448242</v>
-      </c>
+      <c r="AR304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -42947,9 +42341,7 @@
       <c r="AQ305" t="n">
         <v>16.80072784423828</v>
       </c>
-      <c r="AR305" t="n">
-        <v>16.3108959197998</v>
-      </c>
+      <c r="AR305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -43089,9 +42481,7 @@
       <c r="AQ306" t="n">
         <v>18.2678165435791</v>
       </c>
-      <c r="AR306" t="n">
-        <v>17.21743202209473</v>
-      </c>
+      <c r="AR306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -43229,9 +42619,7 @@
       <c r="AQ307" t="n">
         <v>19.83960342407227</v>
       </c>
-      <c r="AR307" t="n">
-        <v>19.64093399047852</v>
-      </c>
+      <c r="AR307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -43369,9 +42757,7 @@
       <c r="AQ308" t="n">
         <v>23.61900901794434</v>
       </c>
-      <c r="AR308" t="n">
-        <v>23.6927490234375</v>
-      </c>
+      <c r="AR308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -43509,9 +42895,7 @@
       <c r="AQ309" t="n">
         <v>25.39970588684082</v>
       </c>
-      <c r="AR309" t="n">
-        <v>26.32199859619141</v>
-      </c>
+      <c r="AR309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -43649,9 +43033,7 @@
       <c r="AQ310" t="n">
         <v>27.29756927490234</v>
       </c>
-      <c r="AR310" t="n">
-        <v>27.8627872467041</v>
-      </c>
+      <c r="AR310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -43789,9 +43171,7 @@
       <c r="AQ311" t="n">
         <v>27.7185230255127</v>
       </c>
-      <c r="AR311" t="n">
-        <v>28.08577156066895</v>
-      </c>
+      <c r="AR311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -43929,9 +43309,7 @@
       <c r="AQ312" t="n">
         <v>28.11559104919434</v>
       </c>
-      <c r="AR312" t="n">
-        <v>28.56172943115234</v>
-      </c>
+      <c r="AR312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -44069,9 +43447,7 @@
       <c r="AQ313" t="n">
         <v>28.48004341125488</v>
       </c>
-      <c r="AR313" t="n">
-        <v>28.6282958984375</v>
-      </c>
+      <c r="AR313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -44209,9 +43585,7 @@
       <c r="AQ314" t="n">
         <v>28.70376205444336</v>
       </c>
-      <c r="AR314" t="n">
-        <v>28.68697929382324</v>
-      </c>
+      <c r="AR314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -44349,9 +43723,7 @@
       <c r="AQ315" t="n">
         <v>28.7060489654541</v>
       </c>
-      <c r="AR315" t="n">
-        <v>28.70492172241211</v>
-      </c>
+      <c r="AR315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -44489,9 +43861,7 @@
       <c r="AQ316" t="n">
         <v>28.79061698913574</v>
       </c>
-      <c r="AR316" t="n">
-        <v>28.7951774597168</v>
-      </c>
+      <c r="AR316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -44629,9 +43999,7 @@
       <c r="AQ317" t="n">
         <v>28.93698120117188</v>
       </c>
-      <c r="AR317" t="n">
-        <v>28.94380378723145</v>
-      </c>
+      <c r="AR317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -44769,9 +44137,7 @@
       <c r="AQ318" t="n">
         <v>29.01161766052246</v>
       </c>
-      <c r="AR318" t="n">
-        <v>29.0140438079834</v>
-      </c>
+      <c r="AR318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -44911,9 +44277,7 @@
       <c r="AQ319" t="n">
         <v>19.76103973388672</v>
       </c>
-      <c r="AR319" t="n">
-        <v>18.96659469604492</v>
-      </c>
+      <c r="AR319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -45051,9 +44415,7 @@
       <c r="AQ320" t="n">
         <v>19.85703468322754</v>
       </c>
-      <c r="AR320" t="n">
-        <v>19.23771286010742</v>
-      </c>
+      <c r="AR320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -45193,9 +44555,7 @@
       <c r="AQ321" t="n">
         <v>20.55337905883789</v>
       </c>
-      <c r="AR321" t="n">
-        <v>20.20400238037109</v>
-      </c>
+      <c r="AR321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -45335,9 +44695,7 @@
       <c r="AQ322" t="n">
         <v>23.41160011291504</v>
       </c>
-      <c r="AR322" t="n">
-        <v>23.06835174560547</v>
-      </c>
+      <c r="AR322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -45475,9 +44833,7 @@
       <c r="AQ323" t="n">
         <v>24.28715133666992</v>
       </c>
-      <c r="AR323" t="n">
-        <v>24.6374454498291</v>
-      </c>
+      <c r="AR323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -45615,9 +44971,7 @@
       <c r="AQ324" t="n">
         <v>24.54206466674805</v>
       </c>
-      <c r="AR324" t="n">
-        <v>25.39281272888184</v>
-      </c>
+      <c r="AR324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -45755,9 +45109,7 @@
       <c r="AQ325" t="n">
         <v>24.90316390991211</v>
       </c>
-      <c r="AR325" t="n">
-        <v>26.07023048400879</v>
-      </c>
+      <c r="AR325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -45895,9 +45247,7 @@
       <c r="AQ326" t="n">
         <v>26.76376724243164</v>
       </c>
-      <c r="AR326" t="n">
-        <v>27.19024467468262</v>
-      </c>
+      <c r="AR326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -46035,9 +45385,7 @@
       <c r="AQ327" t="n">
         <v>27.78141593933105</v>
       </c>
-      <c r="AR327" t="n">
-        <v>27.94811058044434</v>
-      </c>
+      <c r="AR327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -46175,9 +45523,7 @@
       <c r="AQ328" t="n">
         <v>28.25734519958496</v>
       </c>
-      <c r="AR328" t="n">
-        <v>28.36277389526367</v>
-      </c>
+      <c r="AR328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -46315,9 +45661,7 @@
       <c r="AQ329" t="n">
         <v>28.73231315612793</v>
       </c>
-      <c r="AR329" t="n">
-        <v>28.70646667480469</v>
-      </c>
+      <c r="AR329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -46455,9 +45799,7 @@
       <c r="AQ330" t="n">
         <v>28.80237770080566</v>
       </c>
-      <c r="AR330" t="n">
-        <v>28.80977630615234</v>
-      </c>
+      <c r="AR330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -46597,9 +45939,7 @@
       <c r="AQ331" t="n">
         <v>21.30819320678711</v>
       </c>
-      <c r="AR331" t="n">
-        <v>18.87959861755371</v>
-      </c>
+      <c r="AR331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -46737,9 +46077,7 @@
       <c r="AQ332" t="n">
         <v>21.52836608886719</v>
       </c>
-      <c r="AR332" t="n">
-        <v>19.25693511962891</v>
-      </c>
+      <c r="AR332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -46879,9 +46217,7 @@
       <c r="AQ333" t="n">
         <v>22.06849479675293</v>
       </c>
-      <c r="AR333" t="n">
-        <v>20.2017765045166</v>
-      </c>
+      <c r="AR333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -47021,9 +46357,7 @@
       <c r="AQ334" t="n">
         <v>23.51060676574707</v>
       </c>
-      <c r="AR334" t="n">
-        <v>22.82941055297852</v>
-      </c>
+      <c r="AR334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -47161,9 +46495,7 @@
       <c r="AQ335" t="n">
         <v>25.19290733337402</v>
       </c>
-      <c r="AR335" t="n">
-        <v>24.53184700012207</v>
-      </c>
+      <c r="AR335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -47301,9 +46633,7 @@
       <c r="AQ336" t="n">
         <v>26.27070808410645</v>
       </c>
-      <c r="AR336" t="n">
-        <v>25.76028251647949</v>
-      </c>
+      <c r="AR336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -47441,9 +46771,7 @@
       <c r="AQ337" t="n">
         <v>26.85146903991699</v>
       </c>
-      <c r="AR337" t="n">
-        <v>26.27588844299316</v>
-      </c>
+      <c r="AR337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -47581,9 +46909,7 @@
       <c r="AQ338" t="n">
         <v>27.83628273010254</v>
       </c>
-      <c r="AR338" t="n">
-        <v>27.58823204040527</v>
-      </c>
+      <c r="AR338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -47721,9 +47047,7 @@
       <c r="AQ339" t="n">
         <v>28.26343154907227</v>
       </c>
-      <c r="AR339" t="n">
-        <v>28.1906623840332</v>
-      </c>
+      <c r="AR339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -47861,9 +47185,7 @@
       <c r="AQ340" t="n">
         <v>28.44806289672852</v>
       </c>
-      <c r="AR340" t="n">
-        <v>28.39788055419922</v>
-      </c>
+      <c r="AR340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -48001,9 +47323,7 @@
       <c r="AQ341" t="n">
         <v>28.63133430480957</v>
       </c>
-      <c r="AR341" t="n">
-        <v>28.59284400939941</v>
-      </c>
+      <c r="AR341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -48141,9 +47461,7 @@
       <c r="AQ342" t="n">
         <v>28.69498825073242</v>
       </c>
-      <c r="AR342" t="n">
-        <v>28.63343048095703</v>
-      </c>
+      <c r="AR342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -48281,9 +47599,7 @@
       <c r="AQ343" t="n">
         <v>28.65005683898926</v>
       </c>
-      <c r="AR343" t="n">
-        <v>28.59792518615723</v>
-      </c>
+      <c r="AR343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -48423,9 +47739,7 @@
       <c r="AQ344" t="n">
         <v>16.6060676574707</v>
       </c>
-      <c r="AR344" t="n">
-        <v>16.2004280090332</v>
-      </c>
+      <c r="AR344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -48563,9 +47877,7 @@
       <c r="AQ345" t="n">
         <v>17.06382179260254</v>
       </c>
-      <c r="AR345" t="n">
-        <v>17.1072883605957</v>
-      </c>
+      <c r="AR345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -48705,9 +48017,7 @@
       <c r="AQ346" t="n">
         <v>18.35939598083496</v>
       </c>
-      <c r="AR346" t="n">
-        <v>19.07699775695801</v>
-      </c>
+      <c r="AR346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -48847,9 +48157,7 @@
       <c r="AQ347" t="n">
         <v>21.87009239196777</v>
       </c>
-      <c r="AR347" t="n">
-        <v>24.07966423034668</v>
-      </c>
+      <c r="AR347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -48987,9 +48295,7 @@
       <c r="AQ348" t="n">
         <v>24.34609413146973</v>
       </c>
-      <c r="AR348" t="n">
-        <v>25.38030815124512</v>
-      </c>
+      <c r="AR348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -49127,9 +48433,7 @@
       <c r="AQ349" t="n">
         <v>26.26150894165039</v>
       </c>
-      <c r="AR349" t="n">
-        <v>26.28819274902344</v>
-      </c>
+      <c r="AR349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -49267,9 +48571,7 @@
       <c r="AQ350" t="n">
         <v>27.15086555480957</v>
       </c>
-      <c r="AR350" t="n">
-        <v>26.83244514465332</v>
-      </c>
+      <c r="AR350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -49407,9 +48709,7 @@
       <c r="AQ351" t="n">
         <v>27.89726638793945</v>
       </c>
-      <c r="AR351" t="n">
-        <v>27.88887786865234</v>
-      </c>
+      <c r="AR351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -49547,9 +48847,7 @@
       <c r="AQ352" t="n">
         <v>28.15860748291016</v>
       </c>
-      <c r="AR352" t="n">
-        <v>28.10621070861816</v>
-      </c>
+      <c r="AR352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -49687,9 +48985,7 @@
       <c r="AQ353" t="n">
         <v>28.08459281921387</v>
       </c>
-      <c r="AR353" t="n">
-        <v>27.95659637451172</v>
-      </c>
+      <c r="AR353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -49827,9 +49123,7 @@
       <c r="AQ354" t="n">
         <v>28.14052200317383</v>
       </c>
-      <c r="AR354" t="n">
-        <v>27.93139266967773</v>
-      </c>
+      <c r="AR354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -49967,9 +49261,7 @@
       <c r="AQ355" t="n">
         <v>28.56832313537598</v>
       </c>
-      <c r="AR355" t="n">
-        <v>28.43356895446777</v>
-      </c>
+      <c r="AR355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -50107,9 +49399,7 @@
       <c r="AQ356" t="n">
         <v>28.77165603637695</v>
       </c>
-      <c r="AR356" t="n">
-        <v>28.86938858032227</v>
-      </c>
+      <c r="AR356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -50247,9 +49537,7 @@
       <c r="AQ357" t="n">
         <v>29.00105476379395</v>
       </c>
-      <c r="AR357" t="n">
-        <v>29.00383949279785</v>
-      </c>
+      <c r="AR357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -50387,9 +49675,7 @@
       <c r="AQ358" t="n">
         <v>29.02371978759766</v>
       </c>
-      <c r="AR358" t="n">
-        <v>29.02508735656738</v>
-      </c>
+      <c r="AR358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -50525,9 +49811,7 @@
       <c r="AQ359" t="n">
         <v>29.02586364746094</v>
       </c>
-      <c r="AR359" t="n">
-        <v>29.02703094482422</v>
-      </c>
+      <c r="AR359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -50667,9 +49951,7 @@
       <c r="AQ360" t="n">
         <v>16.06431198120117</v>
       </c>
-      <c r="AR360" t="n">
-        <v>17.04874992370605</v>
-      </c>
+      <c r="AR360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -50807,9 +50089,7 @@
       <c r="AQ361" t="n">
         <v>19.26398277282715</v>
       </c>
-      <c r="AR361" t="n">
-        <v>20.09113883972168</v>
-      </c>
+      <c r="AR361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -50949,9 +50229,7 @@
       <c r="AQ362" t="n">
         <v>19.89260101318359</v>
       </c>
-      <c r="AR362" t="n">
-        <v>20.84122848510742</v>
-      </c>
+      <c r="AR362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -51091,9 +50369,7 @@
       <c r="AQ363" t="n">
         <v>21.24045944213867</v>
       </c>
-      <c r="AR363" t="n">
-        <v>22.10230827331543</v>
-      </c>
+      <c r="AR363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -51231,9 +50507,7 @@
       <c r="AQ364" t="n">
         <v>21.99817276000977</v>
       </c>
-      <c r="AR364" t="n">
-        <v>22.79217720031738</v>
-      </c>
+      <c r="AR364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -51371,9 +50645,7 @@
       <c r="AQ365" t="n">
         <v>22.59972190856934</v>
       </c>
-      <c r="AR365" t="n">
-        <v>23.39726066589355</v>
-      </c>
+      <c r="AR365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -51511,9 +50783,7 @@
       <c r="AQ366" t="n">
         <v>23.02152633666992</v>
       </c>
-      <c r="AR366" t="n">
-        <v>23.71831893920898</v>
-      </c>
+      <c r="AR366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -51649,9 +50919,7 @@
       <c r="AQ367" t="n">
         <v>23.09042167663574</v>
       </c>
-      <c r="AR367" t="n">
-        <v>23.74431991577148</v>
-      </c>
+      <c r="AR367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -51771,9 +51039,7 @@
       <c r="AQ368" t="n">
         <v>14.13706874847412</v>
       </c>
-      <c r="AR368" t="n">
-        <v>15.52335357666016</v>
-      </c>
+      <c r="AR368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -51893,9 +51159,7 @@
       <c r="AQ369" t="n">
         <v>14.13706874847412</v>
       </c>
-      <c r="AR369" t="n">
-        <v>15.52335357666016</v>
-      </c>
+      <c r="AR369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -52015,9 +51279,7 @@
       <c r="AQ370" t="n">
         <v>14.13706874847412</v>
       </c>
-      <c r="AR370" t="n">
-        <v>15.52335357666016</v>
-      </c>
+      <c r="AR370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -52137,9 +51399,7 @@
       <c r="AQ371" t="n">
         <v>14.15426731109619</v>
       </c>
-      <c r="AR371" t="n">
-        <v>15.54142284393311</v>
-      </c>
+      <c r="AR371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -52259,9 +51519,7 @@
       <c r="AQ372" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR372" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -52381,9 +51639,7 @@
       <c r="AQ373" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR373" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -52503,9 +51759,7 @@
       <c r="AQ374" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR374" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -52625,9 +51879,7 @@
       <c r="AQ375" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR375" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -52747,9 +51999,7 @@
       <c r="AQ376" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR376" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -52869,9 +52119,7 @@
       <c r="AQ377" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR377" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -52991,9 +52239,7 @@
       <c r="AQ378" t="n">
         <v>14.17146587371826</v>
       </c>
-      <c r="AR378" t="n">
-        <v>15.55949306488037</v>
-      </c>
+      <c r="AR378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -53113,9 +52359,7 @@
       <c r="AQ379" t="n">
         <v>14.18866443634033</v>
       </c>
-      <c r="AR379" t="n">
-        <v>15.57756233215332</v>
-      </c>
+      <c r="AR379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -53255,9 +52499,7 @@
       <c r="AQ380" t="n">
         <v>9.604800224304199</v>
       </c>
-      <c r="AR380" t="n">
-        <v>10.70014667510986</v>
-      </c>
+      <c r="AR380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -53397,9 +52639,7 @@
       <c r="AQ381" t="n">
         <v>12.1819953918457</v>
       </c>
-      <c r="AR381" t="n">
-        <v>12.87887001037598</v>
-      </c>
+      <c r="AR381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -53539,9 +52779,7 @@
       <c r="AQ382" t="n">
         <v>13.88852596282959</v>
       </c>
-      <c r="AR382" t="n">
-        <v>14.41680145263672</v>
-      </c>
+      <c r="AR382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -53681,9 +52919,7 @@
       <c r="AQ383" t="n">
         <v>15.56790447235107</v>
       </c>
-      <c r="AR383" t="n">
-        <v>15.99544715881348</v>
-      </c>
+      <c r="AR383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -53823,9 +53059,7 @@
       <c r="AQ384" t="n">
         <v>17.05747222900391</v>
       </c>
-      <c r="AR384" t="n">
-        <v>17.0579662322998</v>
-      </c>
+      <c r="AR384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -53963,9 +53197,7 @@
       <c r="AQ385" t="n">
         <v>17.8901538848877</v>
       </c>
-      <c r="AR385" t="n">
-        <v>17.99087905883789</v>
-      </c>
+      <c r="AR385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -54103,9 +53335,7 @@
       <c r="AQ386" t="n">
         <v>19.11563110351562</v>
       </c>
-      <c r="AR386" t="n">
-        <v>19.17720413208008</v>
-      </c>
+      <c r="AR386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -54243,9 +53473,7 @@
       <c r="AQ387" t="n">
         <v>21.47417068481445</v>
       </c>
-      <c r="AR387" t="n">
-        <v>21.66913414001465</v>
-      </c>
+      <c r="AR387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -54383,9 +53611,7 @@
       <c r="AQ388" t="n">
         <v>22.98392677307129</v>
       </c>
-      <c r="AR388" t="n">
-        <v>23.20134544372559</v>
-      </c>
+      <c r="AR388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -54525,9 +53751,7 @@
       <c r="AQ389" t="n">
         <v>15.0770959854126</v>
       </c>
-      <c r="AR389" t="n">
-        <v>15.58652210235596</v>
-      </c>
+      <c r="AR389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -54667,9 +53891,7 @@
       <c r="AQ390" t="n">
         <v>16.12882232666016</v>
       </c>
-      <c r="AR390" t="n">
-        <v>16.99910354614258</v>
-      </c>
+      <c r="AR390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -54809,9 +54031,7 @@
       <c r="AQ391" t="n">
         <v>18.57272338867188</v>
       </c>
-      <c r="AR391" t="n">
-        <v>18.97658348083496</v>
-      </c>
+      <c r="AR391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -54951,9 +54171,7 @@
       <c r="AQ392" t="n">
         <v>20.38833236694336</v>
       </c>
-      <c r="AR392" t="n">
-        <v>20.27168273925781</v>
-      </c>
+      <c r="AR392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -55093,9 +54311,7 @@
       <c r="AQ393" t="n">
         <v>21.75552940368652</v>
       </c>
-      <c r="AR393" t="n">
-        <v>21.53654861450195</v>
-      </c>
+      <c r="AR393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -55233,9 +54449,7 @@
       <c r="AQ394" t="n">
         <v>23.43425559997559</v>
       </c>
-      <c r="AR394" t="n">
-        <v>23.35981178283691</v>
-      </c>
+      <c r="AR394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -55373,9 +54587,7 @@
       <c r="AQ395" t="n">
         <v>24.74841499328613</v>
       </c>
-      <c r="AR395" t="n">
-        <v>24.76812362670898</v>
-      </c>
+      <c r="AR395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -55513,9 +54725,7 @@
       <c r="AQ396" t="n">
         <v>28.4445686340332</v>
       </c>
-      <c r="AR396" t="n">
-        <v>28.44127082824707</v>
-      </c>
+      <c r="AR396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -55653,9 +54863,7 @@
       <c r="AQ397" t="n">
         <v>30.93518257141113</v>
       </c>
-      <c r="AR397" t="n">
-        <v>30.94807815551758</v>
-      </c>
+      <c r="AR397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -55791,9 +54999,7 @@
       <c r="AQ398" t="n">
         <v>32.26997375488281</v>
       </c>
-      <c r="AR398" t="n">
-        <v>32.25864028930664</v>
-      </c>
+      <c r="AR398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -55933,9 +55139,7 @@
       <c r="AQ399" t="n">
         <v>5.643265724182129</v>
       </c>
-      <c r="AR399" t="n">
-        <v>6.152563095092773</v>
-      </c>
+      <c r="AR399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -56075,9 +55279,7 @@
       <c r="AQ400" t="n">
         <v>9.443052291870117</v>
       </c>
-      <c r="AR400" t="n">
-        <v>9.917733192443848</v>
-      </c>
+      <c r="AR400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -56217,9 +55419,7 @@
       <c r="AQ401" t="n">
         <v>14.87159538269043</v>
       </c>
-      <c r="AR401" t="n">
-        <v>15.06414127349854</v>
-      </c>
+      <c r="AR401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -56359,9 +55559,7 @@
       <c r="AQ402" t="n">
         <v>20.3464412689209</v>
       </c>
-      <c r="AR402" t="n">
-        <v>20.13961410522461</v>
-      </c>
+      <c r="AR402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -56501,9 +55699,7 @@
       <c r="AQ403" t="n">
         <v>22.5659122467041</v>
       </c>
-      <c r="AR403" t="n">
-        <v>22.94080924987793</v>
-      </c>
+      <c r="AR403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -56641,9 +55837,7 @@
       <c r="AQ404" t="n">
         <v>23.93642807006836</v>
       </c>
-      <c r="AR404" t="n">
-        <v>24.19120025634766</v>
-      </c>
+      <c r="AR404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -56781,9 +55975,7 @@
       <c r="AQ405" t="n">
         <v>25.06189155578613</v>
       </c>
-      <c r="AR405" t="n">
-        <v>25.14518547058105</v>
-      </c>
+      <c r="AR405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -56921,9 +56113,7 @@
       <c r="AQ406" t="n">
         <v>26.63214874267578</v>
       </c>
-      <c r="AR406" t="n">
-        <v>26.63610649108887</v>
-      </c>
+      <c r="AR406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -57061,9 +56251,7 @@
       <c r="AQ407" t="n">
         <v>27.52316284179688</v>
       </c>
-      <c r="AR407" t="n">
-        <v>27.46872138977051</v>
-      </c>
+      <c r="AR407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -57201,9 +56389,7 @@
       <c r="AQ408" t="n">
         <v>28.11582374572754</v>
       </c>
-      <c r="AR408" t="n">
-        <v>28.12054252624512</v>
-      </c>
+      <c r="AR408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -57339,9 +56525,7 @@
       <c r="AQ409" t="n">
         <v>28.47067451477051</v>
       </c>
-      <c r="AR409" t="n">
-        <v>28.43145942687988</v>
-      </c>
+      <c r="AR409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -57475,9 +56659,7 @@
       <c r="AQ410" t="n">
         <v>5.105861663818359</v>
       </c>
-      <c r="AR410" t="n">
-        <v>10.13275527954102</v>
-      </c>
+      <c r="AR410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -57611,9 +56793,7 @@
       <c r="AQ411" t="n">
         <v>16.25967407226562</v>
       </c>
-      <c r="AR411" t="n">
-        <v>17.83008003234863</v>
-      </c>
+      <c r="AR411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -57747,9 +56927,7 @@
       <c r="AQ412" t="n">
         <v>20.33977508544922</v>
       </c>
-      <c r="AR412" t="n">
-        <v>20.81266784667969</v>
-      </c>
+      <c r="AR412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -57887,9 +57065,7 @@
       <c r="AQ413" t="n">
         <v>0.3946677148342133</v>
       </c>
-      <c r="AR413" t="n">
-        <v>0.3023096323013306</v>
-      </c>
+      <c r="AR413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -58027,9 +57203,7 @@
       <c r="AQ414" t="n">
         <v>1.949566602706909</v>
       </c>
-      <c r="AR414" t="n">
-        <v>1.395700097084045</v>
-      </c>
+      <c r="AR414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -58169,9 +57343,7 @@
       <c r="AQ415" t="n">
         <v>17.53315162658691</v>
       </c>
-      <c r="AR415" t="n">
-        <v>17.91772270202637</v>
-      </c>
+      <c r="AR415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -58311,9 +57483,7 @@
       <c r="AQ416" t="n">
         <v>29.38474273681641</v>
       </c>
-      <c r="AR416" t="n">
-        <v>29.41366195678711</v>
-      </c>
+      <c r="AR416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -58447,9 +57617,7 @@
       <c r="AQ417" t="n">
         <v>0.1949833482503891</v>
       </c>
-      <c r="AR417" t="n">
-        <v>0.2249882072210312</v>
-      </c>
+      <c r="AR417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -58581,9 +57749,7 @@
       <c r="AQ418" t="n">
         <v>0.3538044095039368</v>
       </c>
-      <c r="AR418" t="n">
-        <v>0.3474260568618774</v>
-      </c>
+      <c r="AR418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -58717,9 +57883,7 @@
       <c r="AQ419" t="n">
         <v>14.40653324127197</v>
       </c>
-      <c r="AR419" t="n">
-        <v>13.3824462890625</v>
-      </c>
+      <c r="AR419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -58853,9 +58017,7 @@
       <c r="AQ420" t="n">
         <v>0.2032881528139114</v>
       </c>
-      <c r="AR420" t="n">
-        <v>0.2876913845539093</v>
-      </c>
+      <c r="AR420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -58989,9 +58151,7 @@
       <c r="AQ421" t="n">
         <v>0.7063271403312683</v>
       </c>
-      <c r="AR421" t="n">
-        <v>1.19394052028656</v>
-      </c>
+      <c r="AR421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -59125,9 +58285,7 @@
       <c r="AQ422" t="n">
         <v>17.61746215820312</v>
       </c>
-      <c r="AR422" t="n">
-        <v>19.06899261474609</v>
-      </c>
+      <c r="AR422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -59261,9 +58419,7 @@
       <c r="AQ423" t="n">
         <v>0.6850104331970215</v>
       </c>
-      <c r="AR423" t="n">
-        <v>1.033852338790894</v>
-      </c>
+      <c r="AR423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -59397,9 +58553,7 @@
       <c r="AQ424" t="n">
         <v>0.9700517058372498</v>
       </c>
-      <c r="AR424" t="n">
-        <v>2.351666450500488</v>
-      </c>
+      <c r="AR424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -59533,9 +58687,7 @@
       <c r="AQ425" t="n">
         <v>17.10086059570312</v>
       </c>
-      <c r="AR425" t="n">
-        <v>18.86172866821289</v>
-      </c>
+      <c r="AR425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -59675,9 +58827,7 @@
       <c r="AQ426" t="n">
         <v>0.6844961643218994</v>
       </c>
-      <c r="AR426" t="n">
-        <v>0.8580089807510376</v>
-      </c>
+      <c r="AR426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -59817,9 +58967,7 @@
       <c r="AQ427" t="n">
         <v>0.3914735913276672</v>
       </c>
-      <c r="AR427" t="n">
-        <v>0.4030798077583313</v>
-      </c>
+      <c r="AR427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -59959,9 +59107,7 @@
       <c r="AQ428" t="n">
         <v>0.7893977165222168</v>
       </c>
-      <c r="AR428" t="n">
-        <v>0.9165483713150024</v>
-      </c>
+      <c r="AR428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -60101,9 +59247,7 @@
       <c r="AQ429" t="n">
         <v>17.53961944580078</v>
       </c>
-      <c r="AR429" t="n">
-        <v>17.27829360961914</v>
-      </c>
+      <c r="AR429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -60243,9 +59387,7 @@
       <c r="AQ430" t="n">
         <v>24.44275093078613</v>
       </c>
-      <c r="AR430" t="n">
-        <v>24.09222412109375</v>
-      </c>
+      <c r="AR430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -60383,9 +59525,7 @@
       <c r="AQ431" t="n">
         <v>26.28457069396973</v>
       </c>
-      <c r="AR431" t="n">
-        <v>26.55595207214355</v>
-      </c>
+      <c r="AR431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -60523,9 +59663,7 @@
       <c r="AQ432" t="n">
         <v>27.58999633789062</v>
       </c>
-      <c r="AR432" t="n">
-        <v>27.63315200805664</v>
-      </c>
+      <c r="AR432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -60663,9 +59801,7 @@
       <c r="AQ433" t="n">
         <v>28.79334259033203</v>
       </c>
-      <c r="AR433" t="n">
-        <v>28.99664688110352</v>
-      </c>
+      <c r="AR433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -60803,9 +59939,7 @@
       <c r="AQ434" t="n">
         <v>29.32671165466309</v>
       </c>
-      <c r="AR434" t="n">
-        <v>29.32023811340332</v>
-      </c>
+      <c r="AR434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -60943,9 +60077,7 @@
       <c r="AQ435" t="n">
         <v>28.69418716430664</v>
       </c>
-      <c r="AR435" t="n">
-        <v>28.7677173614502</v>
-      </c>
+      <c r="AR435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -61083,9 +60215,7 @@
       <c r="AQ436" t="n">
         <v>29.3402271270752</v>
       </c>
-      <c r="AR436" t="n">
-        <v>29.34172248840332</v>
-      </c>
+      <c r="AR436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -61219,9 +60349,7 @@
       <c r="AQ437" t="n">
         <v>1.51196277141571</v>
       </c>
-      <c r="AR437" t="n">
-        <v>1.514636754989624</v>
-      </c>
+      <c r="AR437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -61355,9 +60483,7 @@
       <c r="AQ438" t="n">
         <v>0.8891761302947998</v>
       </c>
-      <c r="AR438" t="n">
-        <v>0.4884027242660522</v>
-      </c>
+      <c r="AR438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -61491,9 +60617,7 @@
       <c r="AQ439" t="n">
         <v>17.14955711364746</v>
       </c>
-      <c r="AR439" t="n">
-        <v>16.6326732635498</v>
-      </c>
+      <c r="AR439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -61633,9 +60757,7 @@
       <c r="AQ440" t="n">
         <v>0.1923704594373703</v>
       </c>
-      <c r="AR440" t="n">
-        <v>0.2709740996360779</v>
-      </c>
+      <c r="AR440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -61775,9 +60897,7 @@
       <c r="AQ441" t="n">
         <v>0.292548656463623</v>
       </c>
-      <c r="AR441" t="n">
-        <v>0.3619612455368042</v>
-      </c>
+      <c r="AR441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -61917,9 +61037,7 @@
       <c r="AQ442" t="n">
         <v>3.363633155822754</v>
       </c>
-      <c r="AR442" t="n">
-        <v>3.30224871635437</v>
-      </c>
+      <c r="AR442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -62059,9 +61177,7 @@
       <c r="AQ443" t="n">
         <v>19.42997169494629</v>
       </c>
-      <c r="AR443" t="n">
-        <v>18.37238883972168</v>
-      </c>
+      <c r="AR443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -62201,9 +61317,7 @@
       <c r="AQ444" t="n">
         <v>23.83941841125488</v>
       </c>
-      <c r="AR444" t="n">
-        <v>23.98501205444336</v>
-      </c>
+      <c r="AR444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -62341,9 +61455,7 @@
       <c r="AQ445" t="n">
         <v>25.11545562744141</v>
       </c>
-      <c r="AR445" t="n">
-        <v>25.0378303527832</v>
-      </c>
+      <c r="AR445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -62481,9 +61593,7 @@
       <c r="AQ446" t="n">
         <v>25.79257583618164</v>
       </c>
-      <c r="AR446" t="n">
-        <v>25.75125694274902</v>
-      </c>
+      <c r="AR446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -62621,9 +61731,7 @@
       <c r="AQ447" t="n">
         <v>26.41888427734375</v>
       </c>
-      <c r="AR447" t="n">
-        <v>26.56953239440918</v>
-      </c>
+      <c r="AR447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -62761,9 +61869,7 @@
       <c r="AQ448" t="n">
         <v>26.60810279846191</v>
       </c>
-      <c r="AR448" t="n">
-        <v>26.85037994384766</v>
-      </c>
+      <c r="AR448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -62901,9 +62007,7 @@
       <c r="AQ449" t="n">
         <v>27.88360977172852</v>
       </c>
-      <c r="AR449" t="n">
-        <v>27.90474319458008</v>
-      </c>
+      <c r="AR449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -63041,9 +62145,7 @@
       <c r="AQ450" t="n">
         <v>29.15511703491211</v>
       </c>
-      <c r="AR450" t="n">
-        <v>29.17062759399414</v>
-      </c>
+      <c r="AR450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -63177,9 +62279,7 @@
       <c r="AQ451" t="n">
         <v>3.673985481262207</v>
       </c>
-      <c r="AR451" t="n">
-        <v>4.275015354156494</v>
-      </c>
+      <c r="AR451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -63313,9 +62413,7 @@
       <c r="AQ452" t="n">
         <v>1.468786954879761</v>
       </c>
-      <c r="AR452" t="n">
-        <v>1.844529747962952</v>
-      </c>
+      <c r="AR452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -63449,9 +62547,7 @@
       <c r="AQ453" t="n">
         <v>9.719404220581055</v>
       </c>
-      <c r="AR453" t="n">
-        <v>12.2647123336792</v>
-      </c>
+      <c r="AR453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -63581,9 +62677,7 @@
       <c r="AQ454" t="n">
         <v>3.370521068572998</v>
       </c>
-      <c r="AR454" t="n">
-        <v>2.18956184387207</v>
-      </c>
+      <c r="AR454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -63717,9 +62811,7 @@
       <c r="AQ455" t="n">
         <v>3.080264806747437</v>
       </c>
-      <c r="AR455" t="n">
-        <v>0.8641682267189026</v>
-      </c>
+      <c r="AR455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -63853,9 +62945,7 @@
       <c r="AQ456" t="n">
         <v>4.471447944641113</v>
       </c>
-      <c r="AR456" t="n">
-        <v>4.49933910369873</v>
-      </c>
+      <c r="AR456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -63989,9 +63079,7 @@
       <c r="AQ457" t="n">
         <v>13.07374000549316</v>
       </c>
-      <c r="AR457" t="n">
-        <v>13.80993556976318</v>
-      </c>
+      <c r="AR457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -64125,9 +63213,7 @@
       <c r="AQ458" t="n">
         <v>16.97361755371094</v>
       </c>
-      <c r="AR458" t="n">
-        <v>17.75274276733398</v>
-      </c>
+      <c r="AR458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -64259,9 +63345,7 @@
       <c r="AQ459" t="n">
         <v>19.97122573852539</v>
       </c>
-      <c r="AR459" t="n">
-        <v>19.97770309448242</v>
-      </c>
+      <c r="AR459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -64393,9 +63477,7 @@
       <c r="AQ460" t="n">
         <v>21.77870750427246</v>
       </c>
-      <c r="AR460" t="n">
-        <v>21.99974060058594</v>
-      </c>
+      <c r="AR460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -64527,9 +63609,7 @@
       <c r="AQ461" t="n">
         <v>23.29887771606445</v>
       </c>
-      <c r="AR461" t="n">
-        <v>23.74590492248535</v>
-      </c>
+      <c r="AR461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -64661,9 +63741,7 @@
       <c r="AQ462" t="n">
         <v>23.96614646911621</v>
       </c>
-      <c r="AR462" t="n">
-        <v>24.32577896118164</v>
-      </c>
+      <c r="AR462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -64795,9 +63873,7 @@
       <c r="AQ463" t="n">
         <v>26.34177017211914</v>
       </c>
-      <c r="AR463" t="n">
-        <v>26.39420127868652</v>
-      </c>
+      <c r="AR463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -64927,9 +64003,7 @@
       <c r="AQ464" t="n">
         <v>26.24178504943848</v>
       </c>
-      <c r="AR464" t="n">
-        <v>26.33153533935547</v>
-      </c>
+      <c r="AR464" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
